--- a/FCF_K13/PFCF_GETIRI.xlsx
+++ b/FCF_K13/PFCF_GETIRI.xlsx
@@ -159,165 +159,168 @@
     <t xml:space="preserve">FCF_STD</t>
   </si>
   <si>
+    <t xml:space="preserve">KESİN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVO (belgeyle teyitli)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05.05.2026 ×10.899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAGYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ağaoğlu Avrasya Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIER 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acıselsan Acıpayam Selüloz Sanayi ve Ticaret A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kimya-Plastik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adel Kalemcilik Ticaret ve Sanayi A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İmalat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.10.2026 16:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADESE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adese Gayrimenkul Yatırım A.Ş</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADGYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adra Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AEFES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anadolu Efes Biracılık ve Malt Sanayii A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gıda-İçecek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFYON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afyon Çimento Sanayi T.A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taş-Toprak-Çimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGESA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agesa Hayat ve Emeklilik A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIER 0 — STANDART DIŞI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGHOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AG Anadolu Grubu Holding A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.10.2026 16:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGROT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agrotech Yüksek Teknoloji ve Yatırım A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atakule Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.10.2026 16:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHGAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahlatcı Doğal Gaz Dağıtım Enerji ve Yatırım A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHSGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHES Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKBNK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akbank T.A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.10.2026 16:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKCNS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akçansa Çimento Sanayi ve Ticaret A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKENR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akenerji Elektrik Üretim A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKFGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akfen Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKFIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akfen İnşaat Turizm ve Ticaret A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İnşaat</t>
+  </si>
+  <si>
     <t xml:space="preserve">TÜRETİLMİŞ</t>
   </si>
   <si>
-    <t xml:space="preserve">EVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.05.2026 ×10.899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAGYO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ağaoğlu Avrasya Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIER 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acıselsan Acıpayam Selüloz Sanayi ve Ticaret A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kimya-Plastik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KESİN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adel Kalemcilik Ticaret ve Sanayi A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">İmalat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.10.2026 16:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADESE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adese Gayrimenkul Yatırım A.Ş</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADGYO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adra Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AEFES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anadolu Efes Biracılık ve Malt Sanayii A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gıda-İçecek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFYON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afyon Çimento Sanayi T.A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taş-Toprak-Çimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BELGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGESA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agesa Hayat ve Emeklilik A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIER 0 — STANDART DIŞI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGHOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AG Anadolu Grubu Holding A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.10.2026 16:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGROT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agrotech Yüksek Teknoloji ve Yatırım A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGYO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atakule Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.10.2026 16:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHGAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahlatcı Doğal Gaz Dağıtım Enerji ve Yatırım A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHSGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHES Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKBNK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akbank T.A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.10.2026 16:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKCNS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akçansa Çimento Sanayi ve Ticaret A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKENR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akenerji Elektrik Üretim A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKFGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akfen Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKFIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akfen İnşaat Turizm ve Ticaret A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">İnşaat</t>
-  </si>
-  <si>
     <t xml:space="preserve">16.08.2026 ×6.128</t>
   </si>
   <si>
@@ -418,9 +421,6 @@
   </si>
   <si>
     <t xml:space="preserve">06.10.2026 16:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVO (belgeyle teyitli)</t>
   </si>
   <si>
     <t xml:space="preserve">ALCTL</t>
@@ -4953,7 +4953,7 @@
         <v>1056</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-217.126</v>
+        <v>-217.232</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>32</v>
@@ -5081,10 +5081,10 @@
         <v>32</v>
       </c>
       <c r="K8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M8" s="8" t="n">
         <f aca="false">IF(OR(H8="",I8=""),"",IF(I8&gt;0,H8/I8,""))</f>
@@ -5148,10 +5148,10 @@
         <v>32</v>
       </c>
       <c r="K9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M9" s="8" t="str">
         <f aca="false">IF(OR(H9="",I9=""),"",IF(I9&gt;0,H9/I9,""))</f>
@@ -5325,10 +5325,10 @@
         <v>32</v>
       </c>
       <c r="K12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M12" s="8" t="n">
         <f aca="false">IF(OR(H12="",I12=""),"",IF(I12&gt;0,H12/I12,""))</f>
@@ -5392,7 +5392,7 @@
         <v>32</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>57</v>
@@ -5514,10 +5514,10 @@
         <v>32</v>
       </c>
       <c r="K15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M15" s="8" t="n">
         <f aca="false">IF(OR(H15="",I15=""),"",IF(I15&gt;0,H15/I15,""))</f>
@@ -5581,7 +5581,7 @@
         <v>32</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>57</v>
@@ -5703,10 +5703,10 @@
         <v>32</v>
       </c>
       <c r="K18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M18" s="8" t="n">
         <f aca="false">IF(OR(H18="",I18=""),"",IF(I18&gt;0,H18/I18,""))</f>
@@ -5880,10 +5880,10 @@
         <v>32</v>
       </c>
       <c r="K21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M21" s="8" t="n">
         <f aca="false">IF(OR(H21="",I21=""),"",IF(I21&gt;0,H21/I21,""))</f>
@@ -5947,10 +5947,10 @@
         <v>32</v>
       </c>
       <c r="K22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M22" s="8" t="str">
         <f aca="false">IF(OR(H22="",I22=""),"",IF(I22&gt;0,H22/I22,""))</f>
@@ -6069,10 +6069,10 @@
         <v>32</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M24" s="8" t="n">
         <f aca="false">IF(OR(H24="",I24=""),"",IF(I24&gt;0,H24/I24,""))</f>
@@ -6103,15 +6103,15 @@
         <v>1</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>29</v>
@@ -6138,10 +6138,10 @@
         <v>32</v>
       </c>
       <c r="K25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M25" s="8" t="n">
         <f aca="false">IF(OR(H25="",I25=""),"",IF(I25&gt;0,H25/I25,""))</f>
@@ -6172,15 +6172,15 @@
         <v>1</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>60</v>
@@ -6232,10 +6232,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>29</v>
@@ -6262,7 +6262,7 @@
         <v>32</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>57</v>
@@ -6297,10 +6297,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>38</v>
@@ -6352,10 +6352,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>29</v>
@@ -6382,10 +6382,10 @@
         <v>32</v>
       </c>
       <c r="K29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M29" s="8" t="n">
         <f aca="false">IF(OR(H29="",I29=""),"",IF(I29&gt;0,H29/I29,""))</f>
@@ -6419,10 +6419,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>29</v>
@@ -6449,10 +6449,10 @@
         <v>32</v>
       </c>
       <c r="K30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M30" s="8" t="str">
         <f aca="false">IF(OR(H30="",I30=""),"",IF(I30&gt;0,H30/I30,""))</f>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>38</v>
@@ -6541,10 +6541,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>29</v>
@@ -6571,10 +6571,10 @@
         <v>32</v>
       </c>
       <c r="K32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M32" s="8" t="str">
         <f aca="false">IF(OR(H32="",I32=""),"",IF(I32&gt;0,H32/I32,""))</f>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>29</v>
@@ -6620,13 +6620,13 @@
         <v>30</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>1.58</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>392.1402</v>
@@ -6638,10 +6638,10 @@
         <v>32</v>
       </c>
       <c r="K33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M33" s="8" t="n">
         <f aca="false">IF(OR(H33="",I33=""),"",IF(I33&gt;0,H33/I33,""))</f>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>29</v>
@@ -6702,13 +6702,13 @@
         <v>-3331.831</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K34" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M34" s="8" t="str">
         <f aca="false">IF(OR(H34="",I34=""),"",IF(I34&gt;0,H34/I34,""))</f>
@@ -6742,10 +6742,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>60</v>
@@ -6797,10 +6797,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>29</v>
@@ -6825,10 +6825,10 @@
         <v>32</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M36" s="8" t="str">
         <f aca="false">IF(OR(H36="",I36=""),"",IF(I36&gt;0,H36/I36,""))</f>
@@ -6860,10 +6860,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>29</v>
@@ -6872,13 +6872,13 @@
         <v>30</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>601.5</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>6496.2</v>
@@ -6890,10 +6890,10 @@
         <v>32</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M37" s="8" t="str">
         <f aca="false">IF(OR(H37="",I37=""),"",IF(I37&gt;0,H37/I37,""))</f>
@@ -6957,10 +6957,10 @@
         <v>32</v>
       </c>
       <c r="K38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M38" s="8" t="n">
         <f aca="false">IF(OR(H38="",I38=""),"",IF(I38&gt;0,H38/I38,""))</f>
@@ -7024,7 +7024,7 @@
         <v>32</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>57</v>
@@ -7134,7 +7134,7 @@
         <v>6.17</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>4534.95</v>
@@ -7146,10 +7146,10 @@
         <v>32</v>
       </c>
       <c r="K41" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L41" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M41" s="8" t="str">
         <f aca="false">IF(OR(H41="",I41=""),"",IF(I41&gt;0,H41/I41,""))</f>
@@ -7213,10 +7213,10 @@
         <v>32</v>
       </c>
       <c r="K42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M42" s="8" t="n">
         <f aca="false">IF(OR(H42="",I42=""),"",IF(I42&gt;0,H42/I42,""))</f>
@@ -7268,7 +7268,7 @@
         <v>107.5</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>12040</v>
@@ -7280,10 +7280,10 @@
         <v>32</v>
       </c>
       <c r="K43" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L43" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M43" s="8" t="str">
         <f aca="false">IF(OR(H43="",I43=""),"",IF(I43&gt;0,H43/I43,""))</f>
@@ -7347,7 +7347,7 @@
         <v>32</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>57</v>
@@ -7414,10 +7414,10 @@
         <v>32</v>
       </c>
       <c r="K45" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M45" s="8" t="str">
         <f aca="false">IF(OR(H45="",I45=""),"",IF(I45&gt;0,H45/I45,""))</f>
@@ -7481,10 +7481,10 @@
         <v>32</v>
       </c>
       <c r="K46" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M46" s="8" t="str">
         <f aca="false">IF(OR(H46="",I46=""),"",IF(I46&gt;0,H46/I46,""))</f>
@@ -7548,10 +7548,10 @@
         <v>32</v>
       </c>
       <c r="K47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M47" s="8" t="str">
         <f aca="false">IF(OR(H47="",I47=""),"",IF(I47&gt;0,H47/I47,""))</f>
@@ -7728,7 +7728,7 @@
         <v>154</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M50" s="8" t="n">
         <f aca="false">IF(OR(H50="",I50=""),"",IF(I50&gt;0,H50/I50,""))</f>
@@ -7774,7 +7774,7 @@
         <v>30</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>81.5</v>
@@ -7792,10 +7792,10 @@
         <v>32</v>
       </c>
       <c r="K51" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L51" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M51" s="8" t="n">
         <f aca="false">IF(OR(H51="",I51=""),"",IF(I51&gt;0,H51/I51,""))</f>
@@ -7859,10 +7859,10 @@
         <v>32</v>
       </c>
       <c r="K52" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L52" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M52" s="8" t="str">
         <f aca="false">IF(OR(H52="",I52=""),"",IF(I52&gt;0,H52/I52,""))</f>
@@ -7926,10 +7926,10 @@
         <v>32</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M53" s="8" t="n">
         <f aca="false">IF(OR(H53="",I53=""),"",IF(I53&gt;0,H53/I53,""))</f>
@@ -7993,7 +7993,7 @@
         <v>32</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>57</v>
@@ -8058,10 +8058,10 @@
         <v>32</v>
       </c>
       <c r="K55" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M55" s="8" t="str">
         <f aca="false">IF(OR(H55="",I55=""),"",IF(I55&gt;0,H55/I55,""))</f>
@@ -8122,10 +8122,10 @@
         <v>245.2192512</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L56" s="4" t="s">
         <v>57</v>
@@ -8192,7 +8192,7 @@
         <v>32</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L57" s="4" t="s">
         <v>57</v>
@@ -8241,7 +8241,7 @@
         <v>30</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>1.19</v>
@@ -8259,7 +8259,7 @@
         <v>32</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>57</v>
@@ -8326,10 +8326,10 @@
         <v>32</v>
       </c>
       <c r="K59" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M59" s="8" t="str">
         <f aca="false">IF(OR(H59="",I59=""),"",IF(I59&gt;0,H59/I59,""))</f>
@@ -8451,7 +8451,7 @@
         <v>154</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M61" s="8" t="str">
         <f aca="false">IF(OR(H61="",I61=""),"",IF(I61&gt;0,H61/I61,""))</f>
@@ -8515,10 +8515,10 @@
         <v>32</v>
       </c>
       <c r="K62" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L62" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M62" s="8" t="str">
         <f aca="false">IF(OR(H62="",I62=""),"",IF(I62&gt;0,H62/I62,""))</f>
@@ -8637,10 +8637,10 @@
         <v>32</v>
       </c>
       <c r="K64" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L64" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M64" s="8" t="n">
         <f aca="false">IF(OR(H64="",I64=""),"",IF(I64&gt;0,H64/I64,""))</f>
@@ -8707,7 +8707,7 @@
         <v>154</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M65" s="8" t="str">
         <f aca="false">IF(OR(H65="",I65=""),"",IF(I65&gt;0,H65/I65,""))</f>
@@ -8771,7 +8771,7 @@
         <v>32</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L66" s="4" t="s">
         <v>57</v>
@@ -8836,10 +8836,10 @@
         <v>32</v>
       </c>
       <c r="K67" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L67" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M67" s="8" t="n">
         <f aca="false">IF(OR(H67="",I67=""),"",IF(I67&gt;0,H67/I67,""))</f>
@@ -8958,10 +8958,10 @@
         <v>32</v>
       </c>
       <c r="K69" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L69" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M69" s="8" t="str">
         <f aca="false">IF(OR(H69="",I69=""),"",IF(I69&gt;0,H69/I69,""))</f>
@@ -9080,10 +9080,10 @@
         <v>32</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M71" s="8" t="n">
         <f aca="false">IF(OR(H71="",I71=""),"",IF(I71&gt;0,H71/I71,""))</f>
@@ -9147,10 +9147,10 @@
         <v>32</v>
       </c>
       <c r="K72" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L72" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M72" s="8" t="n">
         <f aca="false">IF(OR(H72="",I72=""),"",IF(I72&gt;0,H72/I72,""))</f>
@@ -9269,10 +9269,10 @@
         <v>32</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M74" s="8" t="str">
         <f aca="false">IF(OR(H74="",I74=""),"",IF(I74&gt;0,H74/I74,""))</f>
@@ -9336,10 +9336,10 @@
         <v>32</v>
       </c>
       <c r="K75" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L75" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M75" s="8" t="str">
         <f aca="false">IF(OR(H75="",I75=""),"",IF(I75&gt;0,H75/I75,""))</f>
@@ -9403,10 +9403,10 @@
         <v>32</v>
       </c>
       <c r="K76" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L76" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M76" s="8" t="n">
         <f aca="false">IF(OR(H76="",I76=""),"",IF(I76&gt;0,H76/I76,""))</f>
@@ -9470,10 +9470,10 @@
         <v>32</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M77" s="8" t="n">
         <f aca="false">IF(OR(H77="",I77=""),"",IF(I77&gt;0,H77/I77,""))</f>
@@ -9537,10 +9537,10 @@
         <v>32</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M78" s="8" t="str">
         <f aca="false">IF(OR(H78="",I78=""),"",IF(I78&gt;0,H78/I78,""))</f>
@@ -9606,10 +9606,10 @@
         <v>32</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M79" s="8" t="str">
         <f aca="false">IF(OR(H79="",I79=""),"",IF(I79&gt;0,H79/I79,""))</f>
@@ -9673,10 +9673,10 @@
         <v>32</v>
       </c>
       <c r="K80" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L80" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M80" s="8" t="str">
         <f aca="false">IF(OR(H80="",I80=""),"",IF(I80&gt;0,H80/I80,""))</f>
@@ -9740,10 +9740,10 @@
         <v>32</v>
       </c>
       <c r="K81" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L81" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L81" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M81" s="8" t="n">
         <f aca="false">IF(OR(H81="",I81=""),"",IF(I81&gt;0,H81/I81,""))</f>
@@ -9807,7 +9807,7 @@
         <v>32</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L82" s="4" t="s">
         <v>57</v>
@@ -9874,10 +9874,10 @@
         <v>32</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M83" s="8" t="n">
         <f aca="false">IF(OR(H83="",I83=""),"",IF(I83&gt;0,H83/I83,""))</f>
@@ -9941,7 +9941,7 @@
         <v>32</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L84" s="4" t="s">
         <v>57</v>
@@ -10006,10 +10006,10 @@
         <v>32</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M85" s="8" t="str">
         <f aca="false">IF(OR(H85="",I85=""),"",IF(I85&gt;0,H85/I85,""))</f>
@@ -10073,10 +10073,10 @@
         <v>32</v>
       </c>
       <c r="K86" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L86" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L86" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M86" s="8" t="str">
         <f aca="false">IF(OR(H86="",I86=""),"",IF(I86&gt;0,H86/I86,""))</f>
@@ -10140,10 +10140,10 @@
         <v>32</v>
       </c>
       <c r="K87" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L87" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L87" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M87" s="8" t="str">
         <f aca="false">IF(OR(H87="",I87=""),"",IF(I87&gt;0,H87/I87,""))</f>
@@ -10207,7 +10207,7 @@
         <v>32</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L88" s="4" t="s">
         <v>57</v>
@@ -10274,10 +10274,10 @@
         <v>32</v>
       </c>
       <c r="K89" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L89" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L89" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M89" s="8" t="n">
         <f aca="false">IF(OR(H89="",I89=""),"",IF(I89&gt;0,H89/I89,""))</f>
@@ -10341,10 +10341,10 @@
         <v>32</v>
       </c>
       <c r="K90" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L90" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M90" s="8" t="str">
         <f aca="false">IF(OR(H90="",I90=""),"",IF(I90&gt;0,H90/I90,""))</f>
@@ -10457,13 +10457,13 @@
         <v>8273.552</v>
       </c>
       <c r="I92" s="7" t="n">
-        <v>-396.1902656</v>
+        <v>-200.6769664</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L92" s="4" t="s">
         <v>57</v>
@@ -10533,7 +10533,7 @@
         <v>154</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M93" s="8" t="str">
         <f aca="false">IF(OR(H93="",I93=""),"",IF(I93&gt;0,H93/I93,""))</f>
@@ -10597,7 +10597,7 @@
         <v>32</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L94" s="4" t="s">
         <v>57</v>
@@ -10660,10 +10660,10 @@
         <v>32</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M95" s="8" t="str">
         <f aca="false">IF(OR(H95="",I95=""),"",IF(I95&gt;0,H95/I95,""))</f>
@@ -10707,7 +10707,7 @@
         <v>30</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>17.33</v>
@@ -10725,10 +10725,10 @@
         <v>32</v>
       </c>
       <c r="K96" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L96" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L96" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M96" s="8" t="str">
         <f aca="false">IF(OR(H96="",I96=""),"",IF(I96&gt;0,H96/I96,""))</f>
@@ -10792,7 +10792,7 @@
         <v>32</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L97" s="4" t="s">
         <v>57</v>
@@ -10859,10 +10859,10 @@
         <v>32</v>
       </c>
       <c r="K98" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L98" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M98" s="8" t="str">
         <f aca="false">IF(OR(H98="",I98=""),"",IF(I98&gt;0,H98/I98,""))</f>
@@ -10926,10 +10926,10 @@
         <v>32</v>
       </c>
       <c r="K99" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L99" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M99" s="8" t="n">
         <f aca="false">IF(OR(H99="",I99=""),"",IF(I99&gt;0,H99/I99,""))</f>
@@ -10993,10 +10993,10 @@
         <v>32</v>
       </c>
       <c r="K100" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L100" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M100" s="8" t="str">
         <f aca="false">IF(OR(H100="",I100=""),"",IF(I100&gt;0,H100/I100,""))</f>
@@ -11042,7 +11042,7 @@
         <v>30</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F101" s="5" t="n">
         <v>63.35</v>
@@ -11060,10 +11060,10 @@
         <v>32</v>
       </c>
       <c r="K101" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L101" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L101" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M101" s="8" t="str">
         <f aca="false">IF(OR(H101="",I101=""),"",IF(I101&gt;0,H101/I101,""))</f>
@@ -11127,10 +11127,10 @@
         <v>32</v>
       </c>
       <c r="K102" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L102" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L102" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M102" s="8" t="n">
         <f aca="false">IF(OR(H102="",I102=""),"",IF(I102&gt;0,H102/I102,""))</f>
@@ -11196,7 +11196,7 @@
         <v>32</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L103" s="4" t="s">
         <v>57</v>
@@ -11263,10 +11263,10 @@
         <v>32</v>
       </c>
       <c r="K104" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L104" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M104" s="8" t="str">
         <f aca="false">IF(OR(H104="",I104=""),"",IF(I104&gt;0,H104/I104,""))</f>
@@ -11330,7 +11330,7 @@
         <v>32</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L105" s="4" t="s">
         <v>57</v>
@@ -11397,7 +11397,7 @@
         <v>32</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L106" s="4" t="s">
         <v>57</v>
@@ -11462,10 +11462,10 @@
         <v>32</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M107" s="8" t="str">
         <f aca="false">IF(OR(H107="",I107=""),"",IF(I107&gt;0,H107/I107,""))</f>
@@ -11579,10 +11579,10 @@
         <v>67.9991567999999</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L109" s="4" t="s">
         <v>57</v>
@@ -11651,10 +11651,10 @@
         <v>32</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M110" s="8" t="str">
         <f aca="false">IF(OR(H110="",I110=""),"",IF(I110&gt;0,H110/I110,""))</f>
@@ -11718,10 +11718,10 @@
         <v>32</v>
       </c>
       <c r="K111" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L111" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L111" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M111" s="8" t="str">
         <f aca="false">IF(OR(H111="",I111=""),"",IF(I111&gt;0,H111/I111,""))</f>
@@ -11785,10 +11785,10 @@
         <v>32</v>
       </c>
       <c r="K112" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L112" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L112" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M112" s="8" t="n">
         <f aca="false">IF(OR(H112="",I112=""),"",IF(I112&gt;0,H112/I112,""))</f>
@@ -11854,10 +11854,10 @@
         <v>32</v>
       </c>
       <c r="K113" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L113" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L113" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M113" s="8" t="n">
         <f aca="false">IF(OR(H113="",I113=""),"",IF(I113&gt;0,H113/I113,""))</f>
@@ -11924,7 +11924,7 @@
         <v>154</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M114" s="8" t="str">
         <f aca="false">IF(OR(H114="",I114=""),"",IF(I114&gt;0,H114/I114,""))</f>
@@ -11988,10 +11988,10 @@
         <v>32</v>
       </c>
       <c r="K115" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L115" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L115" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M115" s="8" t="str">
         <f aca="false">IF(OR(H115="",I115=""),"",IF(I115&gt;0,H115/I115,""))</f>
@@ -12055,10 +12055,10 @@
         <v>32</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M116" s="8" t="str">
         <f aca="false">IF(OR(H116="",I116=""),"",IF(I116&gt;0,H116/I116,""))</f>
@@ -12122,7 +12122,7 @@
         <v>32</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L117" s="4" t="s">
         <v>57</v>
@@ -12189,10 +12189,10 @@
         <v>32</v>
       </c>
       <c r="K118" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L118" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L118" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M118" s="8" t="n">
         <f aca="false">IF(OR(H118="",I118=""),"",IF(I118&gt;0,H118/I118,""))</f>
@@ -12256,10 +12256,10 @@
         <v>32</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M119" s="8" t="str">
         <f aca="false">IF(OR(H119="",I119=""),"",IF(I119&gt;0,H119/I119,""))</f>
@@ -12323,10 +12323,10 @@
         <v>32</v>
       </c>
       <c r="K120" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L120" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L120" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M120" s="8" t="n">
         <f aca="false">IF(OR(H120="",I120=""),"",IF(I120&gt;0,H120/I120,""))</f>
@@ -12439,16 +12439,16 @@
         <v>2369.92</v>
       </c>
       <c r="I122" s="7" t="n">
-        <v>-83.703</v>
+        <v>-94.1805744</v>
       </c>
       <c r="J122" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="M122" s="8" t="str">
         <f aca="false">IF(OR(H122="",I122=""),"",IF(I122&gt;0,H122/I122,""))</f>
@@ -12512,7 +12512,7 @@
         <v>32</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L123" s="4" t="s">
         <v>57</v>
@@ -12579,10 +12579,10 @@
         <v>32</v>
       </c>
       <c r="K124" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L124" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L124" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M124" s="8" t="n">
         <f aca="false">IF(OR(H124="",I124=""),"",IF(I124&gt;0,H124/I124,""))</f>
@@ -12643,13 +12643,13 @@
         <v>48.5979999999999</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K125" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L125" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L125" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M125" s="8" t="n">
         <f aca="false">IF(OR(H125="",I125=""),"",IF(I125&gt;0,H125/I125,""))</f>
@@ -12713,7 +12713,7 @@
         <v>32</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L126" s="4" t="s">
         <v>57</v>
@@ -12780,7 +12780,7 @@
         <v>32</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L127" s="4" t="s">
         <v>57</v>
@@ -12847,7 +12847,7 @@
         <v>32</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L128" s="4" t="s">
         <v>57</v>
@@ -12969,7 +12969,7 @@
         <v>32</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L130" s="4" t="s">
         <v>57</v>
@@ -13036,7 +13036,7 @@
         <v>32</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L131" s="4" t="s">
         <v>57</v>
@@ -13103,10 +13103,10 @@
         <v>32</v>
       </c>
       <c r="K132" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L132" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L132" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M132" s="8" t="str">
         <f aca="false">IF(OR(H132="",I132=""),"",IF(I132&gt;0,H132/I132,""))</f>
@@ -13170,7 +13170,7 @@
         <v>32</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L133" s="4" t="s">
         <v>57</v>
@@ -13240,7 +13240,7 @@
         <v>154</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M134" s="8" t="str">
         <f aca="false">IF(OR(H134="",I134=""),"",IF(I134&gt;0,H134/I134,""))</f>
@@ -13304,10 +13304,10 @@
         <v>32</v>
       </c>
       <c r="K135" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L135" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L135" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M135" s="8" t="str">
         <f aca="false">IF(OR(H135="",I135=""),"",IF(I135&gt;0,H135/I135,""))</f>
@@ -13371,10 +13371,10 @@
         <v>32</v>
       </c>
       <c r="K136" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L136" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L136" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M136" s="8" t="n">
         <f aca="false">IF(OR(H136="",I136=""),"",IF(I136&gt;0,H136/I136,""))</f>
@@ -13438,10 +13438,10 @@
         <v>32</v>
       </c>
       <c r="K137" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L137" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L137" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M137" s="8" t="n">
         <f aca="false">IF(OR(H137="",I137=""),"",IF(I137&gt;0,H137/I137,""))</f>
@@ -13505,10 +13505,10 @@
         <v>32</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M138" s="8" t="str">
         <f aca="false">IF(OR(H138="",I138=""),"",IF(I138&gt;0,H138/I138,""))</f>
@@ -13572,10 +13572,10 @@
         <v>32</v>
       </c>
       <c r="K139" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L139" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L139" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M139" s="8" t="str">
         <f aca="false">IF(OR(H139="",I139=""),"",IF(I139&gt;0,H139/I139,""))</f>
@@ -13639,10 +13639,10 @@
         <v>32</v>
       </c>
       <c r="K140" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L140" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L140" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M140" s="8" t="str">
         <f aca="false">IF(OR(H140="",I140=""),"",IF(I140&gt;0,H140/I140,""))</f>
@@ -13706,10 +13706,10 @@
         <v>32</v>
       </c>
       <c r="K141" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L141" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L141" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M141" s="8" t="n">
         <f aca="false">IF(OR(H141="",I141=""),"",IF(I141&gt;0,H141/I141,""))</f>
@@ -13757,7 +13757,7 @@
         <v>30</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F142" s="5" t="n">
         <v>19.83</v>
@@ -13775,10 +13775,10 @@
         <v>32</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M142" s="8" t="n">
         <f aca="false">IF(OR(H142="",I142=""),"",IF(I142&gt;0,H142/I142,""))</f>
@@ -13842,10 +13842,10 @@
         <v>32</v>
       </c>
       <c r="K143" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L143" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L143" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M143" s="8" t="str">
         <f aca="false">IF(OR(H143="",I143=""),"",IF(I143&gt;0,H143/I143,""))</f>
@@ -13909,10 +13909,10 @@
         <v>32</v>
       </c>
       <c r="K144" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L144" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L144" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M144" s="8" t="n">
         <f aca="false">IF(OR(H144="",I144=""),"",IF(I144&gt;0,H144/I144,""))</f>
@@ -13974,10 +13974,10 @@
         <v>32</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M145" s="8" t="str">
         <f aca="false">IF(OR(H145="",I145=""),"",IF(I145&gt;0,H145/I145,""))</f>
@@ -14039,10 +14039,10 @@
         <v>32</v>
       </c>
       <c r="K146" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L146" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L146" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M146" s="8" t="n">
         <f aca="false">IF(OR(H146="",I146=""),"",IF(I146&gt;0,H146/I146,""))</f>
@@ -14106,10 +14106,10 @@
         <v>32</v>
       </c>
       <c r="K147" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L147" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L147" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M147" s="8" t="n">
         <f aca="false">IF(OR(H147="",I147=""),"",IF(I147&gt;0,H147/I147,""))</f>
@@ -14173,10 +14173,10 @@
         <v>32</v>
       </c>
       <c r="K148" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L148" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L148" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M148" s="8" t="n">
         <f aca="false">IF(OR(H148="",I148=""),"",IF(I148&gt;0,H148/I148,""))</f>
@@ -14240,10 +14240,10 @@
         <v>32</v>
       </c>
       <c r="K149" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L149" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L149" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M149" s="8" t="str">
         <f aca="false">IF(OR(H149="",I149=""),"",IF(I149&gt;0,H149/I149,""))</f>
@@ -14307,10 +14307,10 @@
         <v>32</v>
       </c>
       <c r="K150" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L150" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L150" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M150" s="8" t="str">
         <f aca="false">IF(OR(H150="",I150=""),"",IF(I150&gt;0,H150/I150,""))</f>
@@ -14429,10 +14429,10 @@
         <v>32</v>
       </c>
       <c r="K152" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L152" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L152" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M152" s="8" t="str">
         <f aca="false">IF(OR(H152="",I152=""),"",IF(I152&gt;0,H152/I152,""))</f>
@@ -14496,10 +14496,10 @@
         <v>32</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M153" s="8" t="str">
         <f aca="false">IF(OR(H153="",I153=""),"",IF(I153&gt;0,H153/I153,""))</f>
@@ -14563,10 +14563,10 @@
         <v>32</v>
       </c>
       <c r="K154" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L154" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L154" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M154" s="8" t="str">
         <f aca="false">IF(OR(H154="",I154=""),"",IF(I154&gt;0,H154/I154,""))</f>
@@ -14632,10 +14632,10 @@
         <v>32</v>
       </c>
       <c r="K155" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L155" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L155" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M155" s="8" t="str">
         <f aca="false">IF(OR(H155="",I155=""),"",IF(I155&gt;0,H155/I155,""))</f>
@@ -14699,10 +14699,10 @@
         <v>32</v>
       </c>
       <c r="K156" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L156" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L156" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M156" s="8" t="n">
         <f aca="false">IF(OR(H156="",I156=""),"",IF(I156&gt;0,H156/I156,""))</f>
@@ -14821,10 +14821,10 @@
         <v>32</v>
       </c>
       <c r="K158" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L158" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L158" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M158" s="8" t="str">
         <f aca="false">IF(OR(H158="",I158=""),"",IF(I158&gt;0,H158/I158,""))</f>
@@ -14888,10 +14888,10 @@
         <v>32</v>
       </c>
       <c r="K159" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M159" s="8" t="n">
         <f aca="false">IF(OR(H159="",I159=""),"",IF(I159&gt;0,H159/I159,""))</f>
@@ -14949,13 +14949,13 @@
         <v>1092</v>
       </c>
       <c r="I160" s="7" t="n">
-        <v>-439.0077086</v>
+        <v>-439.3776624</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L160" s="4" t="s">
         <v>57</v>
@@ -15022,7 +15022,7 @@
         <v>32</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L161" s="4" t="s">
         <v>57</v>
@@ -15091,10 +15091,10 @@
         <v>32</v>
       </c>
       <c r="K162" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L162" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L162" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M162" s="8" t="n">
         <f aca="false">IF(OR(H162="",I162=""),"",IF(I162&gt;0,H162/I162,""))</f>
@@ -15158,7 +15158,7 @@
         <v>32</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L163" s="4" t="s">
         <v>57</v>
@@ -15225,10 +15225,10 @@
         <v>32</v>
       </c>
       <c r="K164" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L164" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L164" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M164" s="8" t="n">
         <f aca="false">IF(OR(H164="",I164=""),"",IF(I164&gt;0,H164/I164,""))</f>
@@ -15292,10 +15292,10 @@
         <v>32</v>
       </c>
       <c r="K165" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L165" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L165" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M165" s="8" t="str">
         <f aca="false">IF(OR(H165="",I165=""),"",IF(I165&gt;0,H165/I165,""))</f>
@@ -15359,10 +15359,10 @@
         <v>32</v>
       </c>
       <c r="K166" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L166" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L166" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M166" s="8" t="n">
         <f aca="false">IF(OR(H166="",I166=""),"",IF(I166&gt;0,H166/I166,""))</f>
@@ -15481,10 +15481,10 @@
         <v>32</v>
       </c>
       <c r="K168" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M168" s="8" t="n">
         <f aca="false">IF(OR(H168="",I168=""),"",IF(I168&gt;0,H168/I168,""))</f>
@@ -15548,10 +15548,10 @@
         <v>32</v>
       </c>
       <c r="K169" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L169" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L169" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M169" s="8" t="n">
         <f aca="false">IF(OR(H169="",I169=""),"",IF(I169&gt;0,H169/I169,""))</f>
@@ -15615,10 +15615,10 @@
         <v>32</v>
       </c>
       <c r="K170" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M170" s="8" t="n">
         <f aca="false">IF(OR(H170="",I170=""),"",IF(I170&gt;0,H170/I170,""))</f>
@@ -15682,10 +15682,10 @@
         <v>32</v>
       </c>
       <c r="K171" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L171" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L171" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M171" s="8" t="n">
         <f aca="false">IF(OR(H171="",I171=""),"",IF(I171&gt;0,H171/I171,""))</f>
@@ -15749,7 +15749,7 @@
         <v>32</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L172" s="4" t="s">
         <v>57</v>
@@ -15816,10 +15816,10 @@
         <v>32</v>
       </c>
       <c r="K173" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L173" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L173" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M173" s="8" t="n">
         <f aca="false">IF(OR(H173="",I173=""),"",IF(I173&gt;0,H173/I173,""))</f>
@@ -15885,10 +15885,10 @@
         <v>32</v>
       </c>
       <c r="K174" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L174" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L174" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M174" s="8" t="str">
         <f aca="false">IF(OR(H174="",I174=""),"",IF(I174&gt;0,H174/I174,""))</f>
@@ -16007,10 +16007,10 @@
         <v>32</v>
       </c>
       <c r="K176" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L176" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L176" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M176" s="8" t="str">
         <f aca="false">IF(OR(H176="",I176=""),"",IF(I176&gt;0,H176/I176,""))</f>
@@ -16074,7 +16074,7 @@
         <v>32</v>
       </c>
       <c r="K177" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L177" s="4" t="s">
         <v>57</v>
@@ -16141,10 +16141,10 @@
         <v>32</v>
       </c>
       <c r="K178" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L178" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L178" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M178" s="8" t="n">
         <f aca="false">IF(OR(H178="",I178=""),"",IF(I178&gt;0,H178/I178,""))</f>
@@ -16205,10 +16205,10 @@
         <v>22316.9203936</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K179" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L179" s="4" t="s">
         <v>57</v>
@@ -16275,10 +16275,10 @@
         <v>32</v>
       </c>
       <c r="K180" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M180" s="8" t="n">
         <f aca="false">IF(OR(H180="",I180=""),"",IF(I180&gt;0,H180/I180,""))</f>
@@ -16385,7 +16385,7 @@
         <v>27.5</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H182" s="6" t="n">
         <v>1010.1382225</v>
@@ -16397,7 +16397,7 @@
         <v>32</v>
       </c>
       <c r="K182" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L182" s="4" t="s">
         <v>57</v>
@@ -16464,10 +16464,10 @@
         <v>32</v>
       </c>
       <c r="K183" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L183" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L183" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M183" s="8" t="n">
         <f aca="false">IF(OR(H183="",I183=""),"",IF(I183&gt;0,H183/I183,""))</f>
@@ -16531,10 +16531,10 @@
         <v>32</v>
       </c>
       <c r="K184" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L184" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L184" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M184" s="8" t="str">
         <f aca="false">IF(OR(H184="",I184=""),"",IF(I184&gt;0,H184/I184,""))</f>
@@ -16598,10 +16598,10 @@
         <v>32</v>
       </c>
       <c r="K185" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L185" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L185" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M185" s="8" t="n">
         <f aca="false">IF(OR(H185="",I185=""),"",IF(I185&gt;0,H185/I185,""))</f>
@@ -16720,10 +16720,10 @@
         <v>32</v>
       </c>
       <c r="K187" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L187" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L187" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M187" s="8" t="n">
         <f aca="false">IF(OR(H187="",I187=""),"",IF(I187&gt;0,H187/I187,""))</f>
@@ -16787,10 +16787,10 @@
         <v>32</v>
       </c>
       <c r="K188" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L188" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L188" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M188" s="8" t="n">
         <f aca="false">IF(OR(H188="",I188=""),"",IF(I188&gt;0,H188/I188,""))</f>
@@ -16854,7 +16854,7 @@
         <v>32</v>
       </c>
       <c r="K189" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L189" s="4" t="s">
         <v>57</v>
@@ -16916,10 +16916,10 @@
         <v>652.1179792</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K190" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L190" s="4" t="s">
         <v>57</v>
@@ -16986,10 +16986,10 @@
         <v>32</v>
       </c>
       <c r="K191" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L191" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L191" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M191" s="8" t="str">
         <f aca="false">IF(OR(H191="",I191=""),"",IF(I191&gt;0,H191/I191,""))</f>
@@ -17108,10 +17108,10 @@
         <v>32</v>
       </c>
       <c r="K193" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L193" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L193" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M193" s="8" t="str">
         <f aca="false">IF(OR(H193="",I193=""),"",IF(I193&gt;0,H193/I193,""))</f>
@@ -17178,7 +17178,7 @@
         <v>154</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M194" s="8" t="n">
         <f aca="false">IF(OR(H194="",I194=""),"",IF(I194&gt;0,H194/I194,""))</f>
@@ -17297,7 +17297,7 @@
         <v>32</v>
       </c>
       <c r="K196" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L196" s="4" t="s">
         <v>57</v>
@@ -17364,10 +17364,10 @@
         <v>32</v>
       </c>
       <c r="K197" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L197" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L197" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M197" s="8" t="n">
         <f aca="false">IF(OR(H197="",I197=""),"",IF(I197&gt;0,H197/I197,""))</f>
@@ -17431,10 +17431,10 @@
         <v>32</v>
       </c>
       <c r="K198" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L198" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L198" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M198" s="8" t="n">
         <f aca="false">IF(OR(H198="",I198=""),"",IF(I198&gt;0,H198/I198,""))</f>
@@ -17486,7 +17486,7 @@
         <v>2.65</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H199" s="6" t="n">
         <v>1908</v>
@@ -17498,10 +17498,10 @@
         <v>32</v>
       </c>
       <c r="K199" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M199" s="8" t="str">
         <f aca="false">IF(OR(H199="",I199=""),"",IF(I199&gt;0,H199/I199,""))</f>
@@ -17563,10 +17563,10 @@
         <v>32</v>
       </c>
       <c r="K200" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L200" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M200" s="8" t="str">
         <f aca="false">IF(OR(H200="",I200=""),"",IF(I200&gt;0,H200/I200,""))</f>
@@ -17681,10 +17681,10 @@
         <v>32</v>
       </c>
       <c r="K202" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L202" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M202" s="8" t="str">
         <f aca="false">IF(OR(H202="",I202=""),"",IF(I202&gt;0,H202/I202,""))</f>
@@ -17746,10 +17746,10 @@
         <v>32</v>
       </c>
       <c r="K203" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L203" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L203" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M203" s="8" t="str">
         <f aca="false">IF(OR(H203="",I203=""),"",IF(I203&gt;0,H203/I203,""))</f>
@@ -17813,10 +17813,10 @@
         <v>32</v>
       </c>
       <c r="K204" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L204" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M204" s="8" t="str">
         <f aca="false">IF(OR(H204="",I204=""),"",IF(I204&gt;0,H204/I204,""))</f>
@@ -17880,10 +17880,10 @@
         <v>32</v>
       </c>
       <c r="K205" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L205" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L205" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M205" s="8" t="str">
         <f aca="false">IF(OR(H205="",I205=""),"",IF(I205&gt;0,H205/I205,""))</f>
@@ -17947,10 +17947,10 @@
         <v>32</v>
       </c>
       <c r="K206" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L206" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L206" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M206" s="8" t="str">
         <f aca="false">IF(OR(H206="",I206=""),"",IF(I206&gt;0,H206/I206,""))</f>
@@ -18014,10 +18014,10 @@
         <v>32</v>
       </c>
       <c r="K207" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M207" s="8" t="n">
         <f aca="false">IF(OR(H207="",I207=""),"",IF(I207&gt;0,H207/I207,""))</f>
@@ -18081,10 +18081,10 @@
         <v>32</v>
       </c>
       <c r="K208" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L208" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L208" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M208" s="8" t="n">
         <f aca="false">IF(OR(H208="",I208=""),"",IF(I208&gt;0,H208/I208,""))</f>
@@ -18148,7 +18148,7 @@
         <v>32</v>
       </c>
       <c r="K209" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L209" s="4" t="s">
         <v>57</v>
@@ -18216,7 +18216,7 @@
         <v>154</v>
       </c>
       <c r="L210" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M210" s="8" t="str">
         <f aca="false">IF(OR(H210="",I210=""),"",IF(I210&gt;0,H210/I210,""))</f>
@@ -18280,10 +18280,10 @@
         <v>32</v>
       </c>
       <c r="K211" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L211" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L211" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M211" s="8" t="n">
         <f aca="false">IF(OR(H211="",I211=""),"",IF(I211&gt;0,H211/I211,""))</f>
@@ -18347,10 +18347,10 @@
         <v>32</v>
       </c>
       <c r="K212" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L212" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M212" s="8" t="n">
         <f aca="false">IF(OR(H212="",I212=""),"",IF(I212&gt;0,H212/I212,""))</f>
@@ -18414,10 +18414,10 @@
         <v>32</v>
       </c>
       <c r="K213" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L213" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L213" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M213" s="8" t="n">
         <f aca="false">IF(OR(H213="",I213=""),"",IF(I213&gt;0,H213/I213,""))</f>
@@ -18534,7 +18534,7 @@
         <v>32</v>
       </c>
       <c r="K215" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L215" s="4" t="s">
         <v>57</v>
@@ -18601,10 +18601,10 @@
         <v>32</v>
       </c>
       <c r="K216" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L216" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L216" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M216" s="8" t="n">
         <f aca="false">IF(OR(H216="",I216=""),"",IF(I216&gt;0,H216/I216,""))</f>
@@ -18670,7 +18670,7 @@
         <v>32</v>
       </c>
       <c r="K217" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L217" s="4" t="s">
         <v>57</v>
@@ -18737,10 +18737,10 @@
         <v>32</v>
       </c>
       <c r="K218" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L218" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L218" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M218" s="8" t="n">
         <f aca="false">IF(OR(H218="",I218=""),"",IF(I218&gt;0,H218/I218,""))</f>
@@ -18804,10 +18804,10 @@
         <v>32</v>
       </c>
       <c r="K219" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L219" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L219" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M219" s="8" t="str">
         <f aca="false">IF(OR(H219="",I219=""),"",IF(I219&gt;0,H219/I219,""))</f>
@@ -18871,10 +18871,10 @@
         <v>32</v>
       </c>
       <c r="K220" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L220" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L220" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M220" s="8" t="n">
         <f aca="false">IF(OR(H220="",I220=""),"",IF(I220&gt;0,H220/I220,""))</f>
@@ -18938,10 +18938,10 @@
         <v>32</v>
       </c>
       <c r="K221" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L221" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L221" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M221" s="8" t="str">
         <f aca="false">IF(OR(H221="",I221=""),"",IF(I221&gt;0,H221/I221,""))</f>
@@ -19005,10 +19005,10 @@
         <v>32</v>
       </c>
       <c r="K222" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L222" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L222" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M222" s="8" t="str">
         <f aca="false">IF(OR(H222="",I222=""),"",IF(I222&gt;0,H222/I222,""))</f>
@@ -19072,10 +19072,10 @@
         <v>32</v>
       </c>
       <c r="K223" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L223" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L223" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M223" s="8" t="str">
         <f aca="false">IF(OR(H223="",I223=""),"",IF(I223&gt;0,H223/I223,""))</f>
@@ -19139,10 +19139,10 @@
         <v>32</v>
       </c>
       <c r="K224" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L224" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L224" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M224" s="8" t="n">
         <f aca="false">IF(OR(H224="",I224=""),"",IF(I224&gt;0,H224/I224,""))</f>
@@ -19206,10 +19206,10 @@
         <v>32</v>
       </c>
       <c r="K225" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L225" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L225" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M225" s="8" t="str">
         <f aca="false">IF(OR(H225="",I225=""),"",IF(I225&gt;0,H225/I225,""))</f>
@@ -19324,7 +19324,7 @@
         <v>1305</v>
       </c>
       <c r="I227" s="7" t="n">
-        <v>-3653.08</v>
+        <v>-3652.7197888</v>
       </c>
       <c r="J227" s="4" t="s">
         <v>32</v>
@@ -19454,10 +19454,10 @@
         <v>32</v>
       </c>
       <c r="K229" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L229" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M229" s="8" t="str">
         <f aca="false">IF(OR(H229="",I229=""),"",IF(I229&gt;0,H229/I229,""))</f>
@@ -19521,7 +19521,7 @@
         <v>32</v>
       </c>
       <c r="K230" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L230" s="4" t="s">
         <v>57</v>
@@ -19700,7 +19700,7 @@
         <v>32</v>
       </c>
       <c r="K233" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L233" s="4" t="s">
         <v>57</v>
@@ -19765,10 +19765,10 @@
         <v>32</v>
       </c>
       <c r="K234" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L234" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M234" s="8" t="str">
         <f aca="false">IF(OR(H234="",I234=""),"",IF(I234&gt;0,H234/I234,""))</f>
@@ -19814,7 +19814,7 @@
         <v>30</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F235" s="5" t="n">
         <v>11.85</v>
@@ -19832,7 +19832,7 @@
         <v>32</v>
       </c>
       <c r="K235" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L235" s="4" t="s">
         <v>57</v>
@@ -19899,10 +19899,10 @@
         <v>32</v>
       </c>
       <c r="K236" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L236" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L236" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M236" s="8" t="n">
         <f aca="false">IF(OR(H236="",I236=""),"",IF(I236&gt;0,H236/I236,""))</f>
@@ -19954,7 +19954,7 @@
         <v>4.29</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H237" s="6" t="n">
         <v>4015.44</v>
@@ -19966,10 +19966,10 @@
         <v>32</v>
       </c>
       <c r="K237" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L237" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L237" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M237" s="8" t="n">
         <f aca="false">IF(OR(H237="",I237=""),"",IF(I237&gt;0,H237/I237,""))</f>
@@ -20027,13 +20027,13 @@
         <v>1117.78406922</v>
       </c>
       <c r="I238" s="7" t="n">
-        <v>-234.297</v>
+        <v>-234.2978176</v>
       </c>
       <c r="J238" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K238" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L238" s="4" t="s">
         <v>34</v>
@@ -20100,10 +20100,10 @@
         <v>32</v>
       </c>
       <c r="K239" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M239" s="8" t="n">
         <f aca="false">IF(OR(H239="",I239=""),"",IF(I239&gt;0,H239/I239,""))</f>
@@ -20167,10 +20167,10 @@
         <v>32</v>
       </c>
       <c r="K240" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L240" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L240" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M240" s="8" t="n">
         <f aca="false">IF(OR(H240="",I240=""),"",IF(I240&gt;0,H240/I240,""))</f>
@@ -20236,10 +20236,10 @@
         <v>32</v>
       </c>
       <c r="K241" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L241" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L241" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M241" s="8" t="n">
         <f aca="false">IF(OR(H241="",I241=""),"",IF(I241&gt;0,H241/I241,""))</f>
@@ -20301,10 +20301,10 @@
         <v>32</v>
       </c>
       <c r="K242" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L242" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L242" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M242" s="8" t="n">
         <f aca="false">IF(OR(H242="",I242=""),"",IF(I242&gt;0,H242/I242,""))</f>
@@ -20515,7 +20515,7 @@
         <v>30</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F246" s="5" t="n">
         <v>115</v>
@@ -20533,10 +20533,10 @@
         <v>32</v>
       </c>
       <c r="K246" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L246" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L246" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M246" s="8" t="n">
         <f aca="false">IF(OR(H246="",I246=""),"",IF(I246&gt;0,H246/I246,""))</f>
@@ -20655,7 +20655,7 @@
         <v>32</v>
       </c>
       <c r="K248" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L248" s="4" t="s">
         <v>57</v>
@@ -20725,7 +20725,7 @@
         <v>154</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M249" s="8" t="n">
         <f aca="false">IF(OR(H249="",I249=""),"",IF(I249&gt;0,H249/I249,""))</f>
@@ -20789,10 +20789,10 @@
         <v>32</v>
       </c>
       <c r="K250" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L250" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L250" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M250" s="8" t="n">
         <f aca="false">IF(OR(H250="",I250=""),"",IF(I250&gt;0,H250/I250,""))</f>
@@ -20854,10 +20854,10 @@
         <v>32</v>
       </c>
       <c r="K251" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L251" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M251" s="8" t="n">
         <f aca="false">IF(OR(H251="",I251=""),"",IF(I251&gt;0,H251/I251,""))</f>
@@ -20915,13 +20915,13 @@
         <v>7334.04056693</v>
       </c>
       <c r="I252" s="7" t="n">
-        <v>-2527.004</v>
+        <v>-2527.0057248</v>
       </c>
       <c r="J252" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K252" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L252" s="4" t="s">
         <v>34</v>
@@ -20988,10 +20988,10 @@
         <v>32</v>
       </c>
       <c r="K253" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L253" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M253" s="8" t="str">
         <f aca="false">IF(OR(H253="",I253=""),"",IF(I253&gt;0,H253/I253,""))</f>
@@ -21232,10 +21232,10 @@
         <v>32</v>
       </c>
       <c r="K257" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L257" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L257" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M257" s="8" t="n">
         <f aca="false">IF(OR(H257="",I257=""),"",IF(I257&gt;0,H257/I257,""))</f>
@@ -21283,7 +21283,7 @@
         <v>1.88</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H258" s="6" t="n">
         <v>1128</v>
@@ -21354,10 +21354,10 @@
         <v>32</v>
       </c>
       <c r="K259" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L259" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M259" s="8" t="str">
         <f aca="false">IF(OR(H259="",I259=""),"",IF(I259&gt;0,H259/I259,""))</f>
@@ -21421,7 +21421,7 @@
         <v>32</v>
       </c>
       <c r="K260" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L260" s="4" t="s">
         <v>57</v>
@@ -21491,7 +21491,7 @@
         <v>154</v>
       </c>
       <c r="L261" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M261" s="8" t="n">
         <f aca="false">IF(OR(H261="",I261=""),"",IF(I261&gt;0,H261/I261,""))</f>
@@ -21553,10 +21553,10 @@
         <v>32</v>
       </c>
       <c r="K262" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L262" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M262" s="8" t="str">
         <f aca="false">IF(OR(H262="",I262=""),"",IF(I262&gt;0,H262/I262,""))</f>
@@ -21618,10 +21618,10 @@
         <v>32</v>
       </c>
       <c r="K263" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L263" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L263" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M263" s="8" t="n">
         <f aca="false">IF(OR(H263="",I263=""),"",IF(I263&gt;0,H263/I263,""))</f>
@@ -21685,10 +21685,10 @@
         <v>32</v>
       </c>
       <c r="K264" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L264" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L264" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M264" s="8" t="n">
         <f aca="false">IF(OR(H264="",I264=""),"",IF(I264&gt;0,H264/I264,""))</f>
@@ -21864,10 +21864,10 @@
         <v>32</v>
       </c>
       <c r="K267" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L267" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L267" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M267" s="8" t="n">
         <f aca="false">IF(OR(H267="",I267=""),"",IF(I267&gt;0,H267/I267,""))</f>
@@ -21931,10 +21931,10 @@
         <v>32</v>
       </c>
       <c r="K268" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L268" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M268" s="8" t="str">
         <f aca="false">IF(OR(H268="",I268=""),"",IF(I268&gt;0,H268/I268,""))</f>
@@ -21998,10 +21998,10 @@
         <v>32</v>
       </c>
       <c r="K269" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L269" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M269" s="8" t="str">
         <f aca="false">IF(OR(H269="",I269=""),"",IF(I269&gt;0,H269/I269,""))</f>
@@ -22065,10 +22065,10 @@
         <v>32</v>
       </c>
       <c r="K270" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L270" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L270" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M270" s="8" t="n">
         <f aca="false">IF(OR(H270="",I270=""),"",IF(I270&gt;0,H270/I270,""))</f>
@@ -22130,10 +22130,10 @@
         <v>32</v>
       </c>
       <c r="K271" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L271" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M271" s="8" t="str">
         <f aca="false">IF(OR(H271="",I271=""),"",IF(I271&gt;0,H271/I271,""))</f>
@@ -22197,10 +22197,10 @@
         <v>32</v>
       </c>
       <c r="K272" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L272" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L272" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M272" s="8" t="n">
         <f aca="false">IF(OR(H272="",I272=""),"",IF(I272&gt;0,H272/I272,""))</f>
@@ -22264,10 +22264,10 @@
         <v>32</v>
       </c>
       <c r="K273" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L273" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L273" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M273" s="8" t="str">
         <f aca="false">IF(OR(H273="",I273=""),"",IF(I273&gt;0,H273/I273,""))</f>
@@ -22331,7 +22331,7 @@
         <v>32</v>
       </c>
       <c r="K274" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L274" s="4" t="s">
         <v>57</v>
@@ -22398,10 +22398,10 @@
         <v>32</v>
       </c>
       <c r="K275" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L275" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L275" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M275" s="8" t="str">
         <f aca="false">IF(OR(H275="",I275=""),"",IF(I275&gt;0,H275/I275,""))</f>
@@ -22508,7 +22508,7 @@
         <v>7.96</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H277" s="6" t="n">
         <v>501.48</v>
@@ -22520,10 +22520,10 @@
         <v>32</v>
       </c>
       <c r="K277" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L277" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L277" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M277" s="8" t="n">
         <f aca="false">IF(OR(H277="",I277=""),"",IF(I277&gt;0,H277/I277,""))</f>
@@ -22587,10 +22587,10 @@
         <v>32</v>
       </c>
       <c r="K278" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L278" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L278" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M278" s="8" t="n">
         <f aca="false">IF(OR(H278="",I278=""),"",IF(I278&gt;0,H278/I278,""))</f>
@@ -22766,10 +22766,10 @@
         <v>32</v>
       </c>
       <c r="K281" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L281" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L281" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M281" s="8" t="str">
         <f aca="false">IF(OR(H281="",I281=""),"",IF(I281&gt;0,H281/I281,""))</f>
@@ -22833,10 +22833,10 @@
         <v>32</v>
       </c>
       <c r="K282" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L282" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M282" s="8" t="str">
         <f aca="false">IF(OR(H282="",I282=""),"",IF(I282&gt;0,H282/I282,""))</f>
@@ -22955,10 +22955,10 @@
         <v>32</v>
       </c>
       <c r="K284" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L284" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L284" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M284" s="8" t="str">
         <f aca="false">IF(OR(H284="",I284=""),"",IF(I284&gt;0,H284/I284,""))</f>
@@ -23004,7 +23004,7 @@
         <v>30</v>
       </c>
       <c r="E285" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F285" s="5" t="n">
         <v>8.43</v>
@@ -23022,10 +23022,10 @@
         <v>32</v>
       </c>
       <c r="K285" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L285" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L285" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M285" s="8" t="str">
         <f aca="false">IF(OR(H285="",I285=""),"",IF(I285&gt;0,H285/I285,""))</f>
@@ -23091,10 +23091,10 @@
         <v>32</v>
       </c>
       <c r="K286" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L286" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L286" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M286" s="8" t="str">
         <f aca="false">IF(OR(H286="",I286=""),"",IF(I286&gt;0,H286/I286,""))</f>
@@ -23213,10 +23213,10 @@
         <v>32</v>
       </c>
       <c r="K288" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L288" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L288" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M288" s="8" t="str">
         <f aca="false">IF(OR(H288="",I288=""),"",IF(I288&gt;0,H288/I288,""))</f>
@@ -23280,10 +23280,10 @@
         <v>32</v>
       </c>
       <c r="K289" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L289" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L289" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M289" s="8" t="str">
         <f aca="false">IF(OR(H289="",I289=""),"",IF(I289&gt;0,H289/I289,""))</f>
@@ -23506,20 +23506,20 @@
         <v>25864.28497614</v>
       </c>
       <c r="I293" s="7" t="n">
-        <v>1170.573</v>
+        <v>1170.5732704</v>
       </c>
       <c r="J293" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K293" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L293" s="4" t="s">
         <v>34</v>
       </c>
       <c r="M293" s="8" t="n">
         <f aca="false">IF(OR(H293="",I293=""),"",IF(I293&gt;0,H293/I293,""))</f>
-        <v>22.0954053921797</v>
+        <v>22.0954002881869</v>
       </c>
       <c r="N293" s="4" t="str">
         <f aca="false">IF(I293="",IF(K293="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I293&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K293="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -23579,10 +23579,10 @@
         <v>32</v>
       </c>
       <c r="K294" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L294" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L294" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M294" s="8" t="str">
         <f aca="false">IF(OR(H294="",I294=""),"",IF(I294&gt;0,H294/I294,""))</f>
@@ -23628,7 +23628,7 @@
         <v>30</v>
       </c>
       <c r="E295" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F295" s="5" t="n">
         <v>1.64</v>
@@ -23646,10 +23646,10 @@
         <v>32</v>
       </c>
       <c r="K295" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L295" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L295" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M295" s="8" t="str">
         <f aca="false">IF(OR(H295="",I295=""),"",IF(I295&gt;0,H295/I295,""))</f>
@@ -23713,7 +23713,7 @@
         <v>32</v>
       </c>
       <c r="K296" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L296" s="4" t="s">
         <v>57</v>
@@ -23780,10 +23780,10 @@
         <v>32</v>
       </c>
       <c r="K297" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L297" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L297" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M297" s="8" t="str">
         <f aca="false">IF(OR(H297="",I297=""),"",IF(I297&gt;0,H297/I297,""))</f>
@@ -23833,7 +23833,7 @@
         <v>1.2</v>
       </c>
       <c r="G298" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H298" s="6" t="n">
         <v>1200</v>
@@ -23892,7 +23892,7 @@
         <v>1.03</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H299" s="6" t="n">
         <v>463.5</v>
@@ -23901,10 +23901,10 @@
         <v>-414.291248</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K299" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L299" s="4" t="s">
         <v>57</v>
@@ -23971,10 +23971,10 @@
         <v>32</v>
       </c>
       <c r="K300" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L300" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M300" s="8" t="str">
         <f aca="false">IF(OR(H300="",I300=""),"",IF(I300&gt;0,H300/I300,""))</f>
@@ -24038,10 +24038,10 @@
         <v>32</v>
       </c>
       <c r="K301" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L301" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L301" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M301" s="8" t="n">
         <f aca="false">IF(OR(H301="",I301=""),"",IF(I301&gt;0,H301/I301,""))</f>
@@ -24150,7 +24150,7 @@
         <v>305.75</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H303" s="6" t="n">
         <v>7338</v>
@@ -24162,10 +24162,10 @@
         <v>32</v>
       </c>
       <c r="K303" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L303" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L303" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M303" s="8" t="str">
         <f aca="false">IF(OR(H303="",I303=""),"",IF(I303&gt;0,H303/I303,""))</f>
@@ -24229,7 +24229,7 @@
         <v>32</v>
       </c>
       <c r="K304" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L304" s="4" t="s">
         <v>57</v>
@@ -24296,10 +24296,10 @@
         <v>32</v>
       </c>
       <c r="K305" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L305" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L305" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M305" s="8" t="str">
         <f aca="false">IF(OR(H305="",I305=""),"",IF(I305&gt;0,H305/I305,""))</f>
@@ -24361,10 +24361,10 @@
         <v>32</v>
       </c>
       <c r="K306" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L306" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M306" s="8" t="str">
         <f aca="false">IF(OR(H306="",I306=""),"",IF(I306&gt;0,H306/I306,""))</f>
@@ -24478,10 +24478,10 @@
         <v>-12.4285744</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K308" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L308" s="4" t="s">
         <v>57</v>
@@ -24598,10 +24598,10 @@
         <v>-645.322704</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K310" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L310" s="4" t="s">
         <v>57</v>
@@ -24778,10 +24778,10 @@
         <v>32</v>
       </c>
       <c r="K313" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L313" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L313" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M313" s="8" t="n">
         <f aca="false">IF(OR(H313="",I313=""),"",IF(I313&gt;0,H313/I313,""))</f>
@@ -25012,10 +25012,10 @@
         <v>32</v>
       </c>
       <c r="K317" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L317" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L317" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M317" s="8" t="n">
         <f aca="false">IF(OR(H317="",I317=""),"",IF(I317&gt;0,H317/I317,""))</f>
@@ -25187,10 +25187,10 @@
         <v>32</v>
       </c>
       <c r="K320" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L320" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L320" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M320" s="8" t="str">
         <f aca="false">IF(OR(H320="",I320=""),"",IF(I320&gt;0,H320/I320,""))</f>
@@ -25252,10 +25252,10 @@
         <v>32</v>
       </c>
       <c r="K321" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L321" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M321" s="8" t="str">
         <f aca="false">IF(OR(H321="",I321=""),"",IF(I321&gt;0,H321/I321,""))</f>
@@ -25372,10 +25372,10 @@
         <v>32</v>
       </c>
       <c r="K323" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L323" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L323" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M323" s="8" t="n">
         <f aca="false">IF(OR(H323="",I323=""),"",IF(I323&gt;0,H323/I323,""))</f>
@@ -25439,10 +25439,10 @@
         <v>32</v>
       </c>
       <c r="K324" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L324" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M324" s="8" t="str">
         <f aca="false">IF(OR(H324="",I324=""),"",IF(I324&gt;0,H324/I324,""))</f>
@@ -25506,10 +25506,10 @@
         <v>32</v>
       </c>
       <c r="K325" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L325" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L325" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M325" s="8" t="str">
         <f aca="false">IF(OR(H325="",I325=""),"",IF(I325&gt;0,H325/I325,""))</f>
@@ -25573,10 +25573,10 @@
         <v>32</v>
       </c>
       <c r="K326" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L326" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L326" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M326" s="8" t="n">
         <f aca="false">IF(OR(H326="",I326=""),"",IF(I326&gt;0,H326/I326,""))</f>
@@ -25640,10 +25640,10 @@
         <v>32</v>
       </c>
       <c r="K327" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L327" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L327" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M327" s="8" t="n">
         <f aca="false">IF(OR(H327="",I327=""),"",IF(I327&gt;0,H327/I327,""))</f>
@@ -25707,10 +25707,10 @@
         <v>32</v>
       </c>
       <c r="K328" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L328" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L328" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M328" s="8" t="str">
         <f aca="false">IF(OR(H328="",I328=""),"",IF(I328&gt;0,H328/I328,""))</f>
@@ -25777,7 +25777,7 @@
         <v>154</v>
       </c>
       <c r="L329" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M329" s="8" t="n">
         <f aca="false">IF(OR(H329="",I329=""),"",IF(I329&gt;0,H329/I329,""))</f>
@@ -25839,10 +25839,10 @@
         <v>32</v>
       </c>
       <c r="K330" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L330" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L330" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M330" s="8" t="n">
         <f aca="false">IF(OR(H330="",I330=""),"",IF(I330&gt;0,H330/I330,""))</f>
@@ -25906,7 +25906,7 @@
         <v>32</v>
       </c>
       <c r="K331" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L331" s="4" t="s">
         <v>57</v>
@@ -25973,10 +25973,10 @@
         <v>32</v>
       </c>
       <c r="K332" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L332" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M332" s="8" t="str">
         <f aca="false">IF(OR(H332="",I332=""),"",IF(I332&gt;0,H332/I332,""))</f>
@@ -26040,10 +26040,10 @@
         <v>32</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L333" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M333" s="8" t="str">
         <f aca="false">IF(OR(H333="",I333=""),"",IF(I333&gt;0,H333/I333,""))</f>
@@ -26105,10 +26105,10 @@
         <v>32</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L334" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M334" s="8" t="str">
         <f aca="false">IF(OR(H334="",I334=""),"",IF(I334&gt;0,H334/I334,""))</f>
@@ -26172,10 +26172,10 @@
         <v>32</v>
       </c>
       <c r="K335" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L335" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M335" s="8" t="str">
         <f aca="false">IF(OR(H335="",I335=""),"",IF(I335&gt;0,H335/I335,""))</f>
@@ -26239,7 +26239,7 @@
         <v>32</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L336" s="4" t="s">
         <v>57</v>
@@ -26303,13 +26303,13 @@
         <v>-192410.4928</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K337" s="4" t="s">
         <v>154</v>
       </c>
       <c r="L337" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M337" s="8" t="str">
         <f aca="false">IF(OR(H337="",I337=""),"",IF(I337&gt;0,H337/I337,""))</f>
@@ -26373,10 +26373,10 @@
         <v>32</v>
       </c>
       <c r="K338" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L338" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L338" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M338" s="8" t="n">
         <f aca="false">IF(OR(H338="",I338=""),"",IF(I338&gt;0,H338/I338,""))</f>
@@ -26440,10 +26440,10 @@
         <v>32</v>
       </c>
       <c r="K339" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L339" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L339" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M339" s="8" t="str">
         <f aca="false">IF(OR(H339="",I339=""),"",IF(I339&gt;0,H339/I339,""))</f>
@@ -26507,7 +26507,7 @@
         <v>32</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L340" s="4" t="s">
         <v>57</v>
@@ -26629,7 +26629,7 @@
         <v>32</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L342" s="4" t="s">
         <v>57</v>
@@ -26751,10 +26751,10 @@
         <v>32</v>
       </c>
       <c r="K344" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L344" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L344" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M344" s="8" t="n">
         <f aca="false">IF(OR(H344="",I344=""),"",IF(I344&gt;0,H344/I344,""))</f>
@@ -26800,7 +26800,7 @@
         <v>30</v>
       </c>
       <c r="E345" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F345" s="5" t="n">
         <v>22.44</v>
@@ -26818,10 +26818,10 @@
         <v>32</v>
       </c>
       <c r="K345" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L345" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L345" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M345" s="8" t="n">
         <f aca="false">IF(OR(H345="",I345=""),"",IF(I345&gt;0,H345/I345,""))</f>
@@ -26928,7 +26928,7 @@
         <v>13.62</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H347" s="6" t="n">
         <v>39838.5</v>
@@ -26937,10 +26937,10 @@
         <v>-2948.232856</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L347" s="4" t="s">
         <v>57</v>
@@ -27009,7 +27009,7 @@
         <v>32</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L348" s="4" t="s">
         <v>57</v>
@@ -27064,7 +27064,7 @@
         <v>14.24</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H349" s="6" t="n">
         <v>6143.41817984</v>
@@ -27076,7 +27076,7 @@
         <v>32</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L349" s="4" t="s">
         <v>57</v>
@@ -27143,10 +27143,10 @@
         <v>32</v>
       </c>
       <c r="K350" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L350" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L350" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M350" s="8" t="str">
         <f aca="false">IF(OR(H350="",I350=""),"",IF(I350&gt;0,H350/I350,""))</f>
@@ -27210,10 +27210,10 @@
         <v>32</v>
       </c>
       <c r="K351" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L351" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L351" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M351" s="8" t="str">
         <f aca="false">IF(OR(H351="",I351=""),"",IF(I351&gt;0,H351/I351,""))</f>
@@ -27277,10 +27277,10 @@
         <v>32</v>
       </c>
       <c r="K352" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L352" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L352" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M352" s="8" t="n">
         <f aca="false">IF(OR(H352="",I352=""),"",IF(I352&gt;0,H352/I352,""))</f>
@@ -27344,10 +27344,10 @@
         <v>32</v>
       </c>
       <c r="K353" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L353" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L353" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M353" s="8" t="n">
         <f aca="false">IF(OR(H353="",I353=""),"",IF(I353&gt;0,H353/I353,""))</f>
@@ -27411,7 +27411,7 @@
         <v>32</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L354" s="4" t="s">
         <v>57</v>
@@ -27478,10 +27478,10 @@
         <v>32</v>
       </c>
       <c r="K355" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L355" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L355" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M355" s="8" t="n">
         <f aca="false">IF(OR(H355="",I355=""),"",IF(I355&gt;0,H355/I355,""))</f>
@@ -27545,10 +27545,10 @@
         <v>32</v>
       </c>
       <c r="K356" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L356" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L356" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M356" s="8" t="str">
         <f aca="false">IF(OR(H356="",I356=""),"",IF(I356&gt;0,H356/I356,""))</f>
@@ -27612,10 +27612,10 @@
         <v>32</v>
       </c>
       <c r="K357" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L357" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L357" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M357" s="8" t="str">
         <f aca="false">IF(OR(H357="",I357=""),"",IF(I357&gt;0,H357/I357,""))</f>
@@ -27679,7 +27679,7 @@
         <v>32</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L358" s="4" t="s">
         <v>57</v>
@@ -27748,10 +27748,10 @@
         <v>32</v>
       </c>
       <c r="K359" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L359" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L359" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M359" s="8" t="n">
         <f aca="false">IF(OR(H359="",I359=""),"",IF(I359&gt;0,H359/I359,""))</f>
@@ -27813,10 +27813,10 @@
         <v>32</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L360" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M360" s="8" t="str">
         <f aca="false">IF(OR(H360="",I360=""),"",IF(I360&gt;0,H360/I360,""))</f>
@@ -27878,7 +27878,7 @@
         <v>32</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L361" s="4" t="s">
         <v>57</v>
@@ -27945,7 +27945,7 @@
         <v>32</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L362" s="4" t="s">
         <v>57</v>
@@ -28012,7 +28012,7 @@
         <v>32</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L363" s="4" t="s">
         <v>57</v>
@@ -28134,10 +28134,10 @@
         <v>32</v>
       </c>
       <c r="K365" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L365" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L365" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M365" s="8" t="n">
         <f aca="false">IF(OR(H365="",I365=""),"",IF(I365&gt;0,H365/I365,""))</f>
@@ -28201,10 +28201,10 @@
         <v>32</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L366" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M366" s="8" t="n">
         <f aca="false">IF(OR(H366="",I366=""),"",IF(I366&gt;0,H366/I366,""))</f>
@@ -28268,10 +28268,10 @@
         <v>32</v>
       </c>
       <c r="K367" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L367" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L367" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M367" s="8" t="n">
         <f aca="false">IF(OR(H367="",I367=""),"",IF(I367&gt;0,H367/I367,""))</f>
@@ -28335,10 +28335,10 @@
         <v>32</v>
       </c>
       <c r="K368" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L368" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L368" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M368" s="8" t="n">
         <f aca="false">IF(OR(H368="",I368=""),"",IF(I368&gt;0,H368/I368,""))</f>
@@ -28404,10 +28404,10 @@
         <v>32</v>
       </c>
       <c r="K369" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L369" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L369" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M369" s="8" t="n">
         <f aca="false">IF(OR(H369="",I369=""),"",IF(I369&gt;0,H369/I369,""))</f>
@@ -28471,7 +28471,7 @@
         <v>32</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L370" s="4" t="s">
         <v>57</v>
@@ -28595,10 +28595,10 @@
         <v>32</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L372" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M372" s="8" t="str">
         <f aca="false">IF(OR(H372="",I372=""),"",IF(I372&gt;0,H372/I372,""))</f>
@@ -28662,10 +28662,10 @@
         <v>32</v>
       </c>
       <c r="K373" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L373" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L373" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M373" s="8" t="n">
         <f aca="false">IF(OR(H373="",I373=""),"",IF(I373&gt;0,H373/I373,""))</f>
@@ -28729,7 +28729,7 @@
         <v>32</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L374" s="4" t="s">
         <v>57</v>
@@ -28780,7 +28780,7 @@
         <v>17.62</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H375" s="6" t="n">
         <v>7048</v>
@@ -28961,10 +28961,10 @@
         <v>32</v>
       </c>
       <c r="K378" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L378" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L378" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M378" s="8" t="str">
         <f aca="false">IF(OR(H378="",I378=""),"",IF(I378&gt;0,H378/I378,""))</f>
@@ -29085,7 +29085,7 @@
         <v>32</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L380" s="4" t="s">
         <v>57</v>
@@ -29152,10 +29152,10 @@
         <v>32</v>
       </c>
       <c r="K381" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L381" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L381" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M381" s="8" t="n">
         <f aca="false">IF(OR(H381="",I381=""),"",IF(I381&gt;0,H381/I381,""))</f>
@@ -29219,10 +29219,10 @@
         <v>32</v>
       </c>
       <c r="K382" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L382" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L382" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M382" s="8" t="str">
         <f aca="false">IF(OR(H382="",I382=""),"",IF(I382&gt;0,H382/I382,""))</f>
@@ -29286,7 +29286,7 @@
         <v>32</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L383" s="4" t="s">
         <v>57</v>
@@ -29353,10 +29353,10 @@
         <v>32</v>
       </c>
       <c r="K384" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L384" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L384" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M384" s="8" t="n">
         <f aca="false">IF(OR(H384="",I384=""),"",IF(I384&gt;0,H384/I384,""))</f>
@@ -29417,13 +29417,13 @@
         <v>-617.4316608</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L385" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M385" s="8" t="str">
         <f aca="false">IF(OR(H385="",I385=""),"",IF(I385&gt;0,H385/I385,""))</f>
@@ -29487,7 +29487,7 @@
         <v>32</v>
       </c>
       <c r="K386" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L386" s="4" t="s">
         <v>57</v>
@@ -29607,7 +29607,7 @@
         <v>32</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L388" s="4" t="s">
         <v>57</v>
@@ -29662,7 +29662,7 @@
         <v>5182.5</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H389" s="6" t="n">
         <v>9800.4650925</v>
@@ -29674,7 +29674,7 @@
         <v>32</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L389" s="4" t="s">
         <v>57</v>
@@ -29741,10 +29741,10 @@
         <v>32</v>
       </c>
       <c r="K390" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L390" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L390" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M390" s="8" t="str">
         <f aca="false">IF(OR(H390="",I390=""),"",IF(I390&gt;0,H390/I390,""))</f>
@@ -29790,7 +29790,7 @@
         <v>30</v>
       </c>
       <c r="E391" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F391" s="5" t="n">
         <v>23.56</v>
@@ -29808,7 +29808,7 @@
         <v>32</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L391" s="4" t="s">
         <v>57</v>
@@ -29875,10 +29875,10 @@
         <v>32</v>
       </c>
       <c r="K392" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L392" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L392" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M392" s="8" t="n">
         <f aca="false">IF(OR(H392="",I392=""),"",IF(I392&gt;0,H392/I392,""))</f>
@@ -29942,10 +29942,10 @@
         <v>32</v>
       </c>
       <c r="K393" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L393" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L393" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M393" s="8" t="str">
         <f aca="false">IF(OR(H393="",I393=""),"",IF(I393&gt;0,H393/I393,""))</f>
@@ -30009,10 +30009,10 @@
         <v>32</v>
       </c>
       <c r="K394" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L394" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L394" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M394" s="8" t="str">
         <f aca="false">IF(OR(H394="",I394=""),"",IF(I394&gt;0,H394/I394,""))</f>
@@ -30076,7 +30076,7 @@
         <v>32</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L395" s="4" t="s">
         <v>57</v>
@@ -30143,10 +30143,10 @@
         <v>32</v>
       </c>
       <c r="K396" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L396" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L396" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M396" s="8" t="n">
         <f aca="false">IF(OR(H396="",I396=""),"",IF(I396&gt;0,H396/I396,""))</f>
@@ -30207,10 +30207,10 @@
         <v>0.9059904</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L397" s="4" t="s">
         <v>57</v>
@@ -30277,10 +30277,10 @@
         <v>32</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L398" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M398" s="8" t="n">
         <f aca="false">IF(OR(H398="",I398=""),"",IF(I398&gt;0,H398/I398,""))</f>
@@ -30397,10 +30397,10 @@
         <v>32</v>
       </c>
       <c r="K400" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L400" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L400" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M400" s="8" t="n">
         <f aca="false">IF(OR(H400="",I400=""),"",IF(I400&gt;0,H400/I400,""))</f>
@@ -30446,7 +30446,7 @@
         <v>30</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F401" s="5" t="n">
         <v>96.85</v>
@@ -30462,10 +30462,10 @@
         <v>32</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L401" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M401" s="8" t="str">
         <f aca="false">IF(OR(H401="",I401=""),"",IF(I401&gt;0,H401/I401,""))</f>
@@ -30527,7 +30527,7 @@
         <v>32</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L402" s="4" t="s">
         <v>57</v>
@@ -30592,10 +30592,10 @@
         <v>32</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L403" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M403" s="8" t="str">
         <f aca="false">IF(OR(H403="",I403=""),"",IF(I403&gt;0,H403/I403,""))</f>
@@ -30659,10 +30659,10 @@
         <v>32</v>
       </c>
       <c r="K404" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L404" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L404" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M404" s="8" t="str">
         <f aca="false">IF(OR(H404="",I404=""),"",IF(I404&gt;0,H404/I404,""))</f>
@@ -30728,10 +30728,10 @@
         <v>32</v>
       </c>
       <c r="K405" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L405" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L405" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M405" s="8" t="n">
         <f aca="false">IF(OR(H405="",I405=""),"",IF(I405&gt;0,H405/I405,""))</f>
@@ -30783,7 +30783,7 @@
         <v>22</v>
       </c>
       <c r="G406" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H406" s="6" t="n">
         <v>1657.7</v>
@@ -30795,10 +30795,10 @@
         <v>32</v>
       </c>
       <c r="K406" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L406" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L406" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M406" s="8" t="str">
         <f aca="false">IF(OR(H406="",I406=""),"",IF(I406&gt;0,H406/I406,""))</f>
@@ -30862,7 +30862,7 @@
         <v>32</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L407" s="4" t="s">
         <v>57</v>
@@ -30929,10 +30929,10 @@
         <v>32</v>
       </c>
       <c r="K408" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L408" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M408" s="8" t="n">
         <f aca="false">IF(OR(H408="",I408=""),"",IF(I408&gt;0,H408/I408,""))</f>
@@ -30996,10 +30996,10 @@
         <v>32</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L409" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M409" s="8" t="str">
         <f aca="false">IF(OR(H409="",I409=""),"",IF(I409&gt;0,H409/I409,""))</f>
@@ -31065,7 +31065,7 @@
         <v>32</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L410" s="4" t="s">
         <v>57</v>
@@ -31130,10 +31130,10 @@
         <v>32</v>
       </c>
       <c r="K411" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L411" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L411" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M411" s="8" t="n">
         <f aca="false">IF(OR(H411="",I411=""),"",IF(I411&gt;0,H411/I411,""))</f>
@@ -31197,10 +31197,10 @@
         <v>32</v>
       </c>
       <c r="K412" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L412" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L412" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M412" s="8" t="str">
         <f aca="false">IF(OR(H412="",I412=""),"",IF(I412&gt;0,H412/I412,""))</f>
@@ -31262,10 +31262,10 @@
         <v>32</v>
       </c>
       <c r="K413" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L413" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L413" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M413" s="8" t="n">
         <f aca="false">IF(OR(H413="",I413=""),"",IF(I413&gt;0,H413/I413,""))</f>
@@ -31386,10 +31386,10 @@
         <v>32</v>
       </c>
       <c r="K415" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L415" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L415" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M415" s="8" t="str">
         <f aca="false">IF(OR(H415="",I415=""),"",IF(I415&gt;0,H415/I415,""))</f>
@@ -31453,10 +31453,10 @@
         <v>32</v>
       </c>
       <c r="K416" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L416" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L416" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M416" s="8" t="str">
         <f aca="false">IF(OR(H416="",I416=""),"",IF(I416&gt;0,H416/I416,""))</f>
@@ -31520,10 +31520,10 @@
         <v>32</v>
       </c>
       <c r="K417" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L417" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L417" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M417" s="8" t="n">
         <f aca="false">IF(OR(H417="",I417=""),"",IF(I417&gt;0,H417/I417,""))</f>
@@ -31587,7 +31587,7 @@
         <v>32</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L418" s="4" t="s">
         <v>57</v>
@@ -31654,10 +31654,10 @@
         <v>32</v>
       </c>
       <c r="K419" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L419" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L419" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M419" s="8" t="str">
         <f aca="false">IF(OR(H419="",I419=""),"",IF(I419&gt;0,H419/I419,""))</f>
@@ -31721,10 +31721,10 @@
         <v>32</v>
       </c>
       <c r="K420" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L420" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L420" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M420" s="8" t="n">
         <f aca="false">IF(OR(H420="",I420=""),"",IF(I420&gt;0,H420/I420,""))</f>
@@ -31788,10 +31788,10 @@
         <v>32</v>
       </c>
       <c r="K421" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L421" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L421" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M421" s="8" t="n">
         <f aca="false">IF(OR(H421="",I421=""),"",IF(I421&gt;0,H421/I421,""))</f>
@@ -31855,10 +31855,10 @@
         <v>32</v>
       </c>
       <c r="K422" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L422" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L422" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M422" s="8" t="n">
         <f aca="false">IF(OR(H422="",I422=""),"",IF(I422&gt;0,H422/I422,""))</f>
@@ -31977,10 +31977,10 @@
         <v>32</v>
       </c>
       <c r="K424" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L424" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L424" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M424" s="8" t="n">
         <f aca="false">IF(OR(H424="",I424=""),"",IF(I424&gt;0,H424/I424,""))</f>
@@ -32099,10 +32099,10 @@
         <v>32</v>
       </c>
       <c r="K426" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L426" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L426" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M426" s="8" t="str">
         <f aca="false">IF(OR(H426="",I426=""),"",IF(I426&gt;0,H426/I426,""))</f>
@@ -32150,7 +32150,7 @@
         <v>7.98</v>
       </c>
       <c r="G427" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H427" s="6" t="n">
         <v>335.16</v>
@@ -32218,10 +32218,10 @@
         <v>-335.8992272</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L428" s="4" t="s">
         <v>57</v>
@@ -32288,10 +32288,10 @@
         <v>32</v>
       </c>
       <c r="K429" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L429" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L429" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M429" s="8" t="str">
         <f aca="false">IF(OR(H429="",I429=""),"",IF(I429&gt;0,H429/I429,""))</f>
@@ -32355,7 +32355,7 @@
         <v>32</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L430" s="4" t="s">
         <v>57</v>
@@ -32422,7 +32422,7 @@
         <v>32</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L431" s="4" t="s">
         <v>57</v>
@@ -32483,10 +32483,10 @@
         <v>32</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L432" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M432" s="8" t="str">
         <f aca="false">IF(OR(H432="",I432=""),"",IF(I432&gt;0,H432/I432,""))</f>
@@ -32548,10 +32548,10 @@
         <v>32</v>
       </c>
       <c r="K433" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L433" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L433" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M433" s="8" t="str">
         <f aca="false">IF(OR(H433="",I433=""),"",IF(I433&gt;0,H433/I433,""))</f>
@@ -32615,10 +32615,10 @@
         <v>32</v>
       </c>
       <c r="K434" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L434" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L434" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M434" s="8" t="n">
         <f aca="false">IF(OR(H434="",I434=""),"",IF(I434&gt;0,H434/I434,""))</f>
@@ -32682,10 +32682,10 @@
         <v>32</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L435" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M435" s="8" t="str">
         <f aca="false">IF(OR(H435="",I435=""),"",IF(I435&gt;0,H435/I435,""))</f>
@@ -32804,7 +32804,7 @@
         <v>32</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L437" s="4" t="s">
         <v>57</v>
@@ -32873,10 +32873,10 @@
         <v>32</v>
       </c>
       <c r="K438" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L438" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L438" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M438" s="8" t="str">
         <f aca="false">IF(OR(H438="",I438=""),"",IF(I438&gt;0,H438/I438,""))</f>
@@ -32940,10 +32940,10 @@
         <v>32</v>
       </c>
       <c r="K439" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L439" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L439" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M439" s="8" t="str">
         <f aca="false">IF(OR(H439="",I439=""),"",IF(I439&gt;0,H439/I439,""))</f>
@@ -33007,10 +33007,10 @@
         <v>32</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L440" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M440" s="8" t="str">
         <f aca="false">IF(OR(H440="",I440=""),"",IF(I440&gt;0,H440/I440,""))</f>
@@ -33074,7 +33074,7 @@
         <v>32</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L441" s="4" t="s">
         <v>57</v>
@@ -33141,10 +33141,10 @@
         <v>32</v>
       </c>
       <c r="K442" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L442" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L442" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M442" s="8" t="str">
         <f aca="false">IF(OR(H442="",I442=""),"",IF(I442&gt;0,H442/I442,""))</f>
@@ -33208,7 +33208,7 @@
         <v>32</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L443" s="4" t="s">
         <v>57</v>
@@ -33275,10 +33275,10 @@
         <v>32</v>
       </c>
       <c r="K444" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L444" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L444" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M444" s="8" t="str">
         <f aca="false">IF(OR(H444="",I444=""),"",IF(I444&gt;0,H444/I444,""))</f>
@@ -33344,10 +33344,10 @@
         <v>32</v>
       </c>
       <c r="K445" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L445" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L445" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M445" s="8" t="str">
         <f aca="false">IF(OR(H445="",I445=""),"",IF(I445&gt;0,H445/I445,""))</f>
@@ -33405,7 +33405,7 @@
         <v>9120</v>
       </c>
       <c r="I446" s="7" t="n">
-        <v>380.847</v>
+        <v>380.8466448</v>
       </c>
       <c r="J446" s="4" t="s">
         <v>32</v>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="M446" s="8" t="n">
         <f aca="false">IF(OR(H446="",I446=""),"",IF(I446&gt;0,H446/I446,""))</f>
-        <v>23.946624234929</v>
+        <v>23.9466465689604</v>
       </c>
       <c r="N446" s="4" t="str">
         <f aca="false">IF(I446="",IF(K446="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I446&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K446="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -33480,7 +33480,7 @@
         <v>32</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L447" s="4" t="s">
         <v>57</v>
@@ -33545,10 +33545,10 @@
         <v>32</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L448" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M448" s="8" t="str">
         <f aca="false">IF(OR(H448="",I448=""),"",IF(I448&gt;0,H448/I448,""))</f>
@@ -33665,10 +33665,10 @@
         <v>32</v>
       </c>
       <c r="K450" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L450" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L450" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M450" s="8" t="str">
         <f aca="false">IF(OR(H450="",I450=""),"",IF(I450&gt;0,H450/I450,""))</f>
@@ -33734,10 +33734,10 @@
         <v>32</v>
       </c>
       <c r="K451" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L451" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L451" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M451" s="8" t="str">
         <f aca="false">IF(OR(H451="",I451=""),"",IF(I451&gt;0,H451/I451,""))</f>
@@ -33801,10 +33801,10 @@
         <v>32</v>
       </c>
       <c r="K452" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L452" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L452" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M452" s="8" t="str">
         <f aca="false">IF(OR(H452="",I452=""),"",IF(I452&gt;0,H452/I452,""))</f>
@@ -33871,7 +33871,7 @@
         <v>154</v>
       </c>
       <c r="L453" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M453" s="8" t="n">
         <f aca="false">IF(OR(H453="",I453=""),"",IF(I453&gt;0,H453/I453,""))</f>
@@ -33990,10 +33990,10 @@
         <v>32</v>
       </c>
       <c r="K455" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L455" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L455" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M455" s="8" t="str">
         <f aca="false">IF(OR(H455="",I455=""),"",IF(I455&gt;0,H455/I455,""))</f>
@@ -34112,10 +34112,10 @@
         <v>32</v>
       </c>
       <c r="K457" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L457" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L457" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M457" s="8" t="str">
         <f aca="false">IF(OR(H457="",I457=""),"",IF(I457&gt;0,H457/I457,""))</f>
@@ -34163,7 +34163,7 @@
         <v>1.7</v>
       </c>
       <c r="G458" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H458" s="6" t="n">
         <v>1700</v>
@@ -34277,7 +34277,7 @@
         <v>12.29</v>
       </c>
       <c r="G460" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H460" s="6" t="n">
         <v>903.315</v>
@@ -34289,7 +34289,7 @@
         <v>32</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L460" s="4" t="s">
         <v>57</v>
@@ -34356,7 +34356,7 @@
         <v>32</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L461" s="4" t="s">
         <v>57</v>
@@ -34411,7 +34411,7 @@
         <v>11.71</v>
       </c>
       <c r="G462" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H462" s="6" t="n">
         <v>4954.7352</v>
@@ -34423,10 +34423,10 @@
         <v>32</v>
       </c>
       <c r="K462" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L462" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L462" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M462" s="8" t="n">
         <f aca="false">IF(OR(H462="",I462=""),"",IF(I462&gt;0,H462/I462,""))</f>
@@ -34544,10 +34544,10 @@
         <v>-1619.5257312</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L464" s="4" t="s">
         <v>57</v>
@@ -34612,10 +34612,10 @@
         <v>32</v>
       </c>
       <c r="K465" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L465" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L465" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M465" s="8" t="str">
         <f aca="false">IF(OR(H465="",I465=""),"",IF(I465&gt;0,H465/I465,""))</f>
@@ -34679,10 +34679,10 @@
         <v>32</v>
       </c>
       <c r="K466" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L466" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L466" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M466" s="8" t="n">
         <f aca="false">IF(OR(H466="",I466=""),"",IF(I466&gt;0,H466/I466,""))</f>
@@ -34734,7 +34734,7 @@
         <v>60.55</v>
       </c>
       <c r="G467" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H467" s="6" t="n">
         <v>5255.0571171</v>
@@ -34746,10 +34746,10 @@
         <v>32</v>
       </c>
       <c r="K467" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L467" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L467" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M467" s="8" t="str">
         <f aca="false">IF(OR(H467="",I467=""),"",IF(I467&gt;0,H467/I467,""))</f>
@@ -34801,7 +34801,7 @@
         <v>41.4</v>
       </c>
       <c r="G468" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H468" s="6" t="n">
         <v>27820.8</v>
@@ -34813,10 +34813,10 @@
         <v>32</v>
       </c>
       <c r="K468" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L468" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L468" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M468" s="8" t="str">
         <f aca="false">IF(OR(H468="",I468=""),"",IF(I468&gt;0,H468/I468,""))</f>
@@ -34880,10 +34880,10 @@
         <v>32</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L469" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M469" s="8" t="str">
         <f aca="false">IF(OR(H469="",I469=""),"",IF(I469&gt;0,H469/I469,""))</f>
@@ -34929,7 +34929,7 @@
         <v>30</v>
       </c>
       <c r="E470" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F470" s="5" t="n">
         <v>30.94</v>
@@ -34947,7 +34947,7 @@
         <v>32</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L470" s="4" t="s">
         <v>57</v>
@@ -35069,10 +35069,10 @@
         <v>32</v>
       </c>
       <c r="K472" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L472" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L472" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M472" s="8" t="n">
         <f aca="false">IF(OR(H472="",I472=""),"",IF(I472&gt;0,H472/I472,""))</f>
@@ -35136,10 +35136,10 @@
         <v>32</v>
       </c>
       <c r="K473" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L473" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L473" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M473" s="8" t="n">
         <f aca="false">IF(OR(H473="",I473=""),"",IF(I473&gt;0,H473/I473,""))</f>
@@ -35203,7 +35203,7 @@
         <v>32</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L474" s="4" t="s">
         <v>57</v>
@@ -35270,10 +35270,10 @@
         <v>32</v>
       </c>
       <c r="K475" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L475" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L475" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M475" s="8" t="n">
         <f aca="false">IF(OR(H475="",I475=""),"",IF(I475&gt;0,H475/I475,""))</f>
@@ -35337,10 +35337,10 @@
         <v>32</v>
       </c>
       <c r="K476" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L476" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M476" s="8" t="n">
         <f aca="false">IF(OR(H476="",I476=""),"",IF(I476&gt;0,H476/I476,""))</f>
@@ -35404,10 +35404,10 @@
         <v>32</v>
       </c>
       <c r="K477" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L477" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L477" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M477" s="8" t="n">
         <f aca="false">IF(OR(H477="",I477=""),"",IF(I477&gt;0,H477/I477,""))</f>
@@ -35471,10 +35471,10 @@
         <v>32</v>
       </c>
       <c r="K478" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L478" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L478" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M478" s="8" t="n">
         <f aca="false">IF(OR(H478="",I478=""),"",IF(I478&gt;0,H478/I478,""))</f>
@@ -35538,10 +35538,10 @@
         <v>32</v>
       </c>
       <c r="K479" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L479" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L479" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M479" s="8" t="n">
         <f aca="false">IF(OR(H479="",I479=""),"",IF(I479&gt;0,H479/I479,""))</f>
@@ -35608,7 +35608,7 @@
         <v>154</v>
       </c>
       <c r="L480" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M480" s="8" t="n">
         <f aca="false">IF(OR(H480="",I480=""),"",IF(I480&gt;0,H480/I480,""))</f>
@@ -35660,7 +35660,7 @@
         <v>33.96</v>
       </c>
       <c r="G481" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H481" s="6" t="n">
         <v>2547</v>
@@ -35675,7 +35675,7 @@
         <v>154</v>
       </c>
       <c r="L481" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M481" s="8" t="str">
         <f aca="false">IF(OR(H481="",I481=""),"",IF(I481&gt;0,H481/I481,""))</f>
@@ -35739,10 +35739,10 @@
         <v>32</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L482" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M482" s="8" t="n">
         <f aca="false">IF(OR(H482="",I482=""),"",IF(I482&gt;0,H482/I482,""))</f>
@@ -35806,10 +35806,10 @@
         <v>32</v>
       </c>
       <c r="K483" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L483" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L483" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M483" s="8" t="n">
         <f aca="false">IF(OR(H483="",I483=""),"",IF(I483&gt;0,H483/I483,""))</f>
@@ -35873,10 +35873,10 @@
         <v>32</v>
       </c>
       <c r="K484" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L484" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L484" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M484" s="8" t="n">
         <f aca="false">IF(OR(H484="",I484=""),"",IF(I484&gt;0,H484/I484,""))</f>
@@ -35995,10 +35995,10 @@
         <v>32</v>
       </c>
       <c r="K486" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L486" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L486" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M486" s="8" t="str">
         <f aca="false">IF(OR(H486="",I486=""),"",IF(I486&gt;0,H486/I486,""))</f>
@@ -36062,10 +36062,10 @@
         <v>32</v>
       </c>
       <c r="K487" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L487" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L487" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M487" s="8" t="str">
         <f aca="false">IF(OR(H487="",I487=""),"",IF(I487&gt;0,H487/I487,""))</f>
@@ -36129,7 +36129,7 @@
         <v>32</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L488" s="4" t="s">
         <v>57</v>
@@ -36196,10 +36196,10 @@
         <v>32</v>
       </c>
       <c r="K489" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L489" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L489" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M489" s="8" t="str">
         <f aca="false">IF(OR(H489="",I489=""),"",IF(I489&gt;0,H489/I489,""))</f>
@@ -36431,7 +36431,7 @@
         <v>154</v>
       </c>
       <c r="L493" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M493" s="8" t="n">
         <f aca="false">IF(OR(H493="",I493=""),"",IF(I493&gt;0,H493/I493,""))</f>
@@ -36658,10 +36658,10 @@
         <v>32</v>
       </c>
       <c r="K497" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L497" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L497" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M497" s="8" t="n">
         <f aca="false">IF(OR(H497="",I497=""),"",IF(I497&gt;0,H497/I497,""))</f>
@@ -36768,7 +36768,7 @@
         <v>1.8</v>
       </c>
       <c r="G499" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H499" s="6" t="n">
         <v>1080</v>
@@ -36780,10 +36780,10 @@
         <v>32</v>
       </c>
       <c r="K499" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L499" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L499" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M499" s="8" t="str">
         <f aca="false">IF(OR(H499="",I499=""),"",IF(I499&gt;0,H499/I499,""))</f>
@@ -36847,7 +36847,7 @@
         <v>32</v>
       </c>
       <c r="K500" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L500" s="4" t="s">
         <v>57</v>
@@ -36914,10 +36914,10 @@
         <v>32</v>
       </c>
       <c r="K501" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L501" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M501" s="8" t="str">
         <f aca="false">IF(OR(H501="",I501=""),"",IF(I501&gt;0,H501/I501,""))</f>
@@ -36981,10 +36981,10 @@
         <v>32</v>
       </c>
       <c r="K502" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L502" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M502" s="8" t="str">
         <f aca="false">IF(OR(H502="",I502=""),"",IF(I502&gt;0,H502/I502,""))</f>
@@ -37048,7 +37048,7 @@
         <v>32</v>
       </c>
       <c r="K503" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L503" s="4" t="s">
         <v>57</v>
@@ -37170,10 +37170,10 @@
         <v>32</v>
       </c>
       <c r="K505" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L505" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L505" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M505" s="8" t="str">
         <f aca="false">IF(OR(H505="",I505=""),"",IF(I505&gt;0,H505/I505,""))</f>
@@ -37237,10 +37237,10 @@
         <v>32</v>
       </c>
       <c r="K506" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L506" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L506" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M506" s="8" t="n">
         <f aca="false">IF(OR(H506="",I506=""),"",IF(I506&gt;0,H506/I506,""))</f>
@@ -37301,13 +37301,13 @@
         <v>-49369.3456896</v>
       </c>
       <c r="J507" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K507" s="4" t="s">
         <v>154</v>
       </c>
       <c r="L507" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M507" s="8" t="str">
         <f aca="false">IF(OR(H507="",I507=""),"",IF(I507&gt;0,H507/I507,""))</f>
@@ -37371,7 +37371,7 @@
         <v>32</v>
       </c>
       <c r="K508" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L508" s="4" t="s">
         <v>57</v>
@@ -37438,10 +37438,10 @@
         <v>32</v>
       </c>
       <c r="K509" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L509" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L509" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M509" s="8" t="n">
         <f aca="false">IF(OR(H509="",I509=""),"",IF(I509&gt;0,H509/I509,""))</f>
@@ -37505,10 +37505,10 @@
         <v>32</v>
       </c>
       <c r="K510" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L510" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L510" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M510" s="8" t="str">
         <f aca="false">IF(OR(H510="",I510=""),"",IF(I510&gt;0,H510/I510,""))</f>
@@ -37572,10 +37572,10 @@
         <v>32</v>
       </c>
       <c r="K511" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L511" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L511" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M511" s="8" t="n">
         <f aca="false">IF(OR(H511="",I511=""),"",IF(I511&gt;0,H511/I511,""))</f>
@@ -37637,10 +37637,10 @@
         <v>32</v>
       </c>
       <c r="K512" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L512" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M512" s="8" t="str">
         <f aca="false">IF(OR(H512="",I512=""),"",IF(I512&gt;0,H512/I512,""))</f>
@@ -37702,10 +37702,10 @@
         <v>32</v>
       </c>
       <c r="K513" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L513" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L513" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M513" s="8" t="str">
         <f aca="false">IF(OR(H513="",I513=""),"",IF(I513&gt;0,H513/I513,""))</f>
@@ -37769,7 +37769,7 @@
         <v>32</v>
       </c>
       <c r="K514" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L514" s="4" t="s">
         <v>57</v>
@@ -37839,7 +37839,7 @@
         <v>154</v>
       </c>
       <c r="L515" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M515" s="8" t="n">
         <f aca="false">IF(OR(H515="",I515=""),"",IF(I515&gt;0,H515/I515,""))</f>
@@ -37903,10 +37903,10 @@
         <v>32</v>
       </c>
       <c r="K516" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L516" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L516" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M516" s="8" t="str">
         <f aca="false">IF(OR(H516="",I516=""),"",IF(I516&gt;0,H516/I516,""))</f>
@@ -37972,7 +37972,7 @@
         <v>32</v>
       </c>
       <c r="K517" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L517" s="4" t="s">
         <v>57</v>
@@ -38151,10 +38151,10 @@
         <v>32</v>
       </c>
       <c r="K520" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L520" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M520" s="8" t="str">
         <f aca="false">IF(OR(H520="",I520=""),"",IF(I520&gt;0,H520/I520,""))</f>
@@ -38218,10 +38218,10 @@
         <v>32</v>
       </c>
       <c r="K521" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L521" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L521" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M521" s="8" t="str">
         <f aca="false">IF(OR(H521="",I521=""),"",IF(I521&gt;0,H521/I521,""))</f>
@@ -38285,10 +38285,10 @@
         <v>32</v>
       </c>
       <c r="K522" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L522" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M522" s="8" t="str">
         <f aca="false">IF(OR(H522="",I522=""),"",IF(I522&gt;0,H522/I522,""))</f>
@@ -38352,10 +38352,10 @@
         <v>32</v>
       </c>
       <c r="K523" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L523" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M523" s="8" t="n">
         <f aca="false">IF(OR(H523="",I523=""),"",IF(I523&gt;0,H523/I523,""))</f>
@@ -38419,10 +38419,10 @@
         <v>32</v>
       </c>
       <c r="K524" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L524" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L524" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M524" s="8" t="n">
         <f aca="false">IF(OR(H524="",I524=""),"",IF(I524&gt;0,H524/I524,""))</f>
@@ -38468,7 +38468,7 @@
         <v>30</v>
       </c>
       <c r="E525" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F525" s="5" t="n">
         <v>1.68</v>
@@ -38486,10 +38486,10 @@
         <v>32</v>
       </c>
       <c r="K525" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L525" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M525" s="8" t="n">
         <f aca="false">IF(OR(H525="",I525=""),"",IF(I525&gt;0,H525/I525,""))</f>
@@ -38553,10 +38553,10 @@
         <v>32</v>
       </c>
       <c r="K526" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L526" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L526" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M526" s="8" t="str">
         <f aca="false">IF(OR(H526="",I526=""),"",IF(I526&gt;0,H526/I526,""))</f>
@@ -38675,10 +38675,10 @@
         <v>32</v>
       </c>
       <c r="K528" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L528" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L528" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M528" s="8" t="str">
         <f aca="false">IF(OR(H528="",I528=""),"",IF(I528&gt;0,H528/I528,""))</f>
@@ -38742,10 +38742,10 @@
         <v>32</v>
       </c>
       <c r="K529" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L529" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L529" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M529" s="8" t="n">
         <f aca="false">IF(OR(H529="",I529=""),"",IF(I529&gt;0,H529/I529,""))</f>
@@ -38864,10 +38864,10 @@
         <v>32</v>
       </c>
       <c r="K531" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L531" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L531" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M531" s="8" t="n">
         <f aca="false">IF(OR(H531="",I531=""),"",IF(I531&gt;0,H531/I531,""))</f>
@@ -38931,10 +38931,10 @@
         <v>32</v>
       </c>
       <c r="K532" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L532" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L532" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M532" s="8" t="str">
         <f aca="false">IF(OR(H532="",I532=""),"",IF(I532&gt;0,H532/I532,""))</f>
@@ -39110,10 +39110,10 @@
         <v>32</v>
       </c>
       <c r="K535" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L535" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L535" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M535" s="8" t="n">
         <f aca="false">IF(OR(H535="",I535=""),"",IF(I535&gt;0,H535/I535,""))</f>
@@ -39177,10 +39177,10 @@
         <v>32</v>
       </c>
       <c r="K536" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L536" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L536" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M536" s="8" t="n">
         <f aca="false">IF(OR(H536="",I536=""),"",IF(I536&gt;0,H536/I536,""))</f>
@@ -39244,7 +39244,7 @@
         <v>32</v>
       </c>
       <c r="K537" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L537" s="4" t="s">
         <v>57</v>
@@ -39309,10 +39309,10 @@
         <v>32</v>
       </c>
       <c r="K538" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L538" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M538" s="8" t="str">
         <f aca="false">IF(OR(H538="",I538=""),"",IF(I538&gt;0,H538/I538,""))</f>
@@ -39374,10 +39374,10 @@
         <v>32</v>
       </c>
       <c r="K539" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L539" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L539" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M539" s="8" t="n">
         <f aca="false">IF(OR(H539="",I539=""),"",IF(I539&gt;0,H539/I539,""))</f>
@@ -39441,10 +39441,10 @@
         <v>32</v>
       </c>
       <c r="K540" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L540" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L540" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M540" s="8" t="n">
         <f aca="false">IF(OR(H540="",I540=""),"",IF(I540&gt;0,H540/I540,""))</f>
@@ -39511,7 +39511,7 @@
         <v>154</v>
       </c>
       <c r="L541" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M541" s="8" t="n">
         <f aca="false">IF(OR(H541="",I541=""),"",IF(I541&gt;0,H541/I541,""))</f>
@@ -39628,10 +39628,10 @@
         <v>32</v>
       </c>
       <c r="K543" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L543" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M543" s="8" t="str">
         <f aca="false">IF(OR(H543="",I543=""),"",IF(I543&gt;0,H543/I543,""))</f>
@@ -39693,7 +39693,7 @@
         <v>32</v>
       </c>
       <c r="K544" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L544" s="4" t="s">
         <v>57</v>
@@ -39763,7 +39763,7 @@
         <v>154</v>
       </c>
       <c r="L545" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M545" s="8" t="n">
         <f aca="false">IF(OR(H545="",I545=""),"",IF(I545&gt;0,H545/I545,""))</f>
@@ -39882,10 +39882,10 @@
         <v>32</v>
       </c>
       <c r="K547" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L547" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L547" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M547" s="8" t="n">
         <f aca="false">IF(OR(H547="",I547=""),"",IF(I547&gt;0,H547/I547,""))</f>
@@ -40002,10 +40002,10 @@
         <v>32</v>
       </c>
       <c r="K549" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L549" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L549" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M549" s="8" t="str">
         <f aca="false">IF(OR(H549="",I549=""),"",IF(I549&gt;0,H549/I549,""))</f>
@@ -40069,10 +40069,10 @@
         <v>32</v>
       </c>
       <c r="K550" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L550" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L550" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M550" s="8" t="str">
         <f aca="false">IF(OR(H550="",I550=""),"",IF(I550&gt;0,H550/I550,""))</f>
@@ -40136,10 +40136,10 @@
         <v>32</v>
       </c>
       <c r="K551" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L551" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L551" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M551" s="8" t="str">
         <f aca="false">IF(OR(H551="",I551=""),"",IF(I551&gt;0,H551/I551,""))</f>
@@ -40203,10 +40203,10 @@
         <v>32</v>
       </c>
       <c r="K552" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L552" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L552" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M552" s="8" t="n">
         <f aca="false">IF(OR(H552="",I552=""),"",IF(I552&gt;0,H552/I552,""))</f>
@@ -40270,10 +40270,10 @@
         <v>32</v>
       </c>
       <c r="K553" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L553" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L553" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M553" s="8" t="n">
         <f aca="false">IF(OR(H553="",I553=""),"",IF(I553&gt;0,H553/I553,""))</f>
@@ -40337,10 +40337,10 @@
         <v>32</v>
       </c>
       <c r="K554" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L554" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L554" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M554" s="8" t="str">
         <f aca="false">IF(OR(H554="",I554=""),"",IF(I554&gt;0,H554/I554,""))</f>
@@ -40404,10 +40404,10 @@
         <v>32</v>
       </c>
       <c r="K555" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L555" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L555" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M555" s="8" t="str">
         <f aca="false">IF(OR(H555="",I555=""),"",IF(I555&gt;0,H555/I555,""))</f>
@@ -40471,10 +40471,10 @@
         <v>32</v>
       </c>
       <c r="K556" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L556" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M556" s="8" t="str">
         <f aca="false">IF(OR(H556="",I556=""),"",IF(I556&gt;0,H556/I556,""))</f>
@@ -40590,10 +40590,10 @@
         <v>-2186.2780384</v>
       </c>
       <c r="J558" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K558" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L558" s="4" t="s">
         <v>57</v>
@@ -40660,10 +40660,10 @@
         <v>32</v>
       </c>
       <c r="K559" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L559" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L559" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M559" s="8" t="str">
         <f aca="false">IF(OR(H559="",I559=""),"",IF(I559&gt;0,H559/I559,""))</f>
@@ -40785,7 +40785,7 @@
         <v>154</v>
       </c>
       <c r="L561" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M561" s="8" t="n">
         <f aca="false">IF(OR(H561="",I561=""),"",IF(I561&gt;0,H561/I561,""))</f>
@@ -40849,7 +40849,7 @@
         <v>32</v>
       </c>
       <c r="K562" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L562" s="4" t="s">
         <v>57</v>
@@ -40916,10 +40916,10 @@
         <v>32</v>
       </c>
       <c r="K563" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L563" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L563" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M563" s="8" t="str">
         <f aca="false">IF(OR(H563="",I563=""),"",IF(I563&gt;0,H563/I563,""))</f>
@@ -40980,13 +40980,13 @@
         <v>2096.173</v>
       </c>
       <c r="J564" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K564" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L564" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L564" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M564" s="8" t="n">
         <f aca="false">IF(OR(H564="",I564=""),"",IF(I564&gt;0,H564/I564,""))</f>
@@ -41048,10 +41048,10 @@
         <v>32</v>
       </c>
       <c r="K565" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L565" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M565" s="8" t="str">
         <f aca="false">IF(OR(H565="",I565=""),"",IF(I565&gt;0,H565/I565,""))</f>
@@ -41113,10 +41113,10 @@
         <v>32</v>
       </c>
       <c r="K566" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L566" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M566" s="8" t="n">
         <f aca="false">IF(OR(H566="",I566=""),"",IF(I566&gt;0,H566/I566,""))</f>
@@ -41180,7 +41180,7 @@
         <v>32</v>
       </c>
       <c r="K567" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L567" s="4" t="s">
         <v>57</v>
@@ -41247,10 +41247,10 @@
         <v>32</v>
       </c>
       <c r="K568" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="L568" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M568" s="8" t="str">
         <f aca="false">IF(OR(H568="",I568=""),"",IF(I568&gt;0,H568/I568,""))</f>
@@ -41314,7 +41314,7 @@
         <v>32</v>
       </c>
       <c r="K569" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L569" s="4" t="s">
         <v>57</v>
@@ -41381,7 +41381,7 @@
         <v>32</v>
       </c>
       <c r="K570" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L570" s="4" t="s">
         <v>57</v>
@@ -41442,13 +41442,13 @@
         <v>134875</v>
       </c>
       <c r="I571" s="7" t="n">
-        <v>-30816.057</v>
+        <v>-30816.062984</v>
       </c>
       <c r="J571" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K571" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L571" s="4" t="s">
         <v>34</v>
@@ -41515,10 +41515,10 @@
         <v>32</v>
       </c>
       <c r="K572" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L572" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L572" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M572" s="8" t="str">
         <f aca="false">IF(OR(H572="",I572=""),"",IF(I572&gt;0,H572/I572,""))</f>
@@ -41582,10 +41582,10 @@
         <v>32</v>
       </c>
       <c r="K573" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L573" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L573" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M573" s="8" t="str">
         <f aca="false">IF(OR(H573="",I573=""),"",IF(I573&gt;0,H573/I573,""))</f>
@@ -41649,10 +41649,10 @@
         <v>32</v>
       </c>
       <c r="K574" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L574" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L574" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M574" s="8" t="str">
         <f aca="false">IF(OR(H574="",I574=""),"",IF(I574&gt;0,H574/I574,""))</f>
@@ -41768,10 +41768,10 @@
         <v>294.1801712</v>
       </c>
       <c r="J576" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K576" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L576" s="4" t="s">
         <v>57</v>
@@ -41836,10 +41836,10 @@
         <v>32</v>
       </c>
       <c r="K577" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L577" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M577" s="8" t="str">
         <f aca="false">IF(OR(H577="",I577=""),"",IF(I577&gt;0,H577/I577,""))</f>
@@ -41905,7 +41905,7 @@
         <v>32</v>
       </c>
       <c r="K578" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L578" s="4" t="s">
         <v>57</v>
@@ -42080,10 +42080,10 @@
         <v>32</v>
       </c>
       <c r="K581" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L581" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M581" s="8" t="str">
         <f aca="false">IF(OR(H581="",I581=""),"",IF(I581&gt;0,H581/I581,""))</f>
@@ -42147,10 +42147,10 @@
         <v>32</v>
       </c>
       <c r="K582" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L582" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L582" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M582" s="8" t="str">
         <f aca="false">IF(OR(H582="",I582=""),"",IF(I582&gt;0,H582/I582,""))</f>
@@ -42214,10 +42214,10 @@
         <v>32</v>
       </c>
       <c r="K583" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L583" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L583" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M583" s="8" t="n">
         <f aca="false">IF(OR(H583="",I583=""),"",IF(I583&gt;0,H583/I583,""))</f>
@@ -42281,10 +42281,10 @@
         <v>32</v>
       </c>
       <c r="K584" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L584" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L584" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M584" s="8" t="str">
         <f aca="false">IF(OR(H584="",I584=""),"",IF(I584&gt;0,H584/I584,""))</f>
@@ -42348,10 +42348,10 @@
         <v>32</v>
       </c>
       <c r="K585" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L585" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L585" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M585" s="8" t="n">
         <f aca="false">IF(OR(H585="",I585=""),"",IF(I585&gt;0,H585/I585,""))</f>
@@ -42415,10 +42415,10 @@
         <v>32</v>
       </c>
       <c r="K586" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L586" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L586" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M586" s="8" t="n">
         <f aca="false">IF(OR(H586="",I586=""),"",IF(I586&gt;0,H586/I586,""))</f>
@@ -42482,10 +42482,10 @@
         <v>32</v>
       </c>
       <c r="K587" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L587" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M587" s="8" t="n">
         <f aca="false">IF(OR(H587="",I587=""),"",IF(I587&gt;0,H587/I587,""))</f>
@@ -42549,7 +42549,7 @@
         <v>32</v>
       </c>
       <c r="K588" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L588" s="4" t="s">
         <v>57</v>
@@ -42673,7 +42673,7 @@
         <v>32</v>
       </c>
       <c r="K590" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L590" s="4" t="s">
         <v>57</v>
@@ -42738,10 +42738,10 @@
         <v>32</v>
       </c>
       <c r="K591" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L591" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L591" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M591" s="8" t="str">
         <f aca="false">IF(OR(H591="",I591=""),"",IF(I591&gt;0,H591/I591,""))</f>
@@ -42805,7 +42805,7 @@
         <v>32</v>
       </c>
       <c r="K592" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L592" s="4" t="s">
         <v>57</v>
@@ -42872,10 +42872,10 @@
         <v>32</v>
       </c>
       <c r="K593" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L593" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L593" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M593" s="8" t="n">
         <f aca="false">IF(OR(H593="",I593=""),"",IF(I593&gt;0,H593/I593,""))</f>
@@ -42923,7 +42923,7 @@
         <v>1.46</v>
       </c>
       <c r="G594" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H594" s="6" t="n">
         <v>1576.8</v>
@@ -42996,10 +42996,10 @@
         <v>32</v>
       </c>
       <c r="K595" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L595" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L595" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M595" s="8" t="n">
         <f aca="false">IF(OR(H595="",I595=""),"",IF(I595&gt;0,H595/I595,""))</f>
@@ -43063,10 +43063,10 @@
         <v>32</v>
       </c>
       <c r="K596" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L596" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L596" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M596" s="8" t="str">
         <f aca="false">IF(OR(H596="",I596=""),"",IF(I596&gt;0,H596/I596,""))</f>
@@ -43165,7 +43165,7 @@
         <v>11.09</v>
       </c>
       <c r="G598" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H598" s="6" t="n">
         <v>1948.9566</v>
@@ -43174,13 +43174,13 @@
         <v>-1091.96</v>
       </c>
       <c r="J598" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K598" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L598" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L598" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M598" s="8" t="str">
         <f aca="false">IF(OR(H598="",I598=""),"",IF(I598&gt;0,H598/I598,""))</f>
@@ -43244,10 +43244,10 @@
         <v>32</v>
       </c>
       <c r="K599" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L599" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L599" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M599" s="8" t="str">
         <f aca="false">IF(OR(H599="",I599=""),"",IF(I599&gt;0,H599/I599,""))</f>
@@ -43311,10 +43311,10 @@
         <v>32</v>
       </c>
       <c r="K600" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L600" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L600" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M600" s="8" t="str">
         <f aca="false">IF(OR(H600="",I600=""),"",IF(I600&gt;0,H600/I600,""))</f>
@@ -43544,7 +43544,7 @@
         <v>154</v>
       </c>
       <c r="L604" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M604" s="8" t="n">
         <f aca="false">IF(OR(H604="",I604=""),"",IF(I604&gt;0,H604/I604,""))</f>
@@ -43596,7 +43596,7 @@
         <v>69.4</v>
       </c>
       <c r="G605" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H605" s="6" t="n">
         <v>1735</v>
@@ -43675,10 +43675,10 @@
         <v>32</v>
       </c>
       <c r="K606" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L606" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L606" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M606" s="8" t="n">
         <f aca="false">IF(OR(H606="",I606=""),"",IF(I606&gt;0,H606/I606,""))</f>
@@ -43797,10 +43797,10 @@
         <v>32</v>
       </c>
       <c r="K608" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L608" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L608" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M608" s="8" t="str">
         <f aca="false">IF(OR(H608="",I608=""),"",IF(I608&gt;0,H608/I608,""))</f>
@@ -43846,7 +43846,7 @@
         <v>30</v>
       </c>
       <c r="E609" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F609" s="5" t="n">
         <v>4.09</v>
@@ -43864,10 +43864,10 @@
         <v>32</v>
       </c>
       <c r="K609" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L609" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L609" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M609" s="8" t="n">
         <f aca="false">IF(OR(H609="",I609=""),"",IF(I609&gt;0,H609/I609,""))</f>
@@ -43913,7 +43913,7 @@
         <v>30</v>
       </c>
       <c r="E610" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F610" s="5" t="n">
         <v>18.06</v>
@@ -43931,10 +43931,10 @@
         <v>32</v>
       </c>
       <c r="K610" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L610" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L610" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M610" s="8" t="str">
         <f aca="false">IF(OR(H610="",I610=""),"",IF(I610&gt;0,H610/I610,""))</f>
@@ -43996,10 +43996,10 @@
         <v>32</v>
       </c>
       <c r="K611" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L611" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M611" s="8" t="str">
         <f aca="false">IF(OR(H611="",I611=""),"",IF(I611&gt;0,H611/I611,""))</f>
@@ -44100,7 +44100,7 @@
         <v>1.67</v>
       </c>
       <c r="G613" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H613" s="6" t="n">
         <v>7348</v>
@@ -44173,10 +44173,10 @@
         <v>32</v>
       </c>
       <c r="K614" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L614" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L614" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M614" s="8" t="str">
         <f aca="false">IF(OR(H614="",I614=""),"",IF(I614&gt;0,H614/I614,""))</f>
@@ -44295,10 +44295,10 @@
         <v>32</v>
       </c>
       <c r="K616" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L616" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L616" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M616" s="8" t="str">
         <f aca="false">IF(OR(H616="",I616=""),"",IF(I616&gt;0,H616/I616,""))</f>
@@ -44364,10 +44364,10 @@
         <v>32</v>
       </c>
       <c r="K617" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L617" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L617" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M617" s="8" t="str">
         <f aca="false">IF(OR(H617="",I617=""),"",IF(I617&gt;0,H617/I617,""))</f>
@@ -44431,10 +44431,10 @@
         <v>32</v>
       </c>
       <c r="K618" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L618" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L618" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M618" s="8" t="n">
         <f aca="false">IF(OR(H618="",I618=""),"",IF(I618&gt;0,H618/I618,""))</f>
@@ -44486,7 +44486,7 @@
         <v>13.99</v>
       </c>
       <c r="G619" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H619" s="6" t="n">
         <v>697.75125</v>
@@ -44501,7 +44501,7 @@
         <v>154</v>
       </c>
       <c r="L619" s="4" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="M619" s="8" t="str">
         <f aca="false">IF(OR(H619="",I619=""),"",IF(I619&gt;0,H619/I619,""))</f>
@@ -44565,7 +44565,7 @@
         <v>32</v>
       </c>
       <c r="K620" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L620" s="4" t="s">
         <v>57</v>
@@ -44632,7 +44632,7 @@
         <v>32</v>
       </c>
       <c r="K621" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L621" s="4" t="s">
         <v>57</v>
@@ -44701,10 +44701,10 @@
         <v>32</v>
       </c>
       <c r="K622" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L622" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L622" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M622" s="8" t="n">
         <f aca="false">IF(OR(H622="",I622=""),"",IF(I622&gt;0,H622/I622,""))</f>
@@ -44823,10 +44823,10 @@
         <v>32</v>
       </c>
       <c r="K624" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L624" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L624" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M624" s="8" t="str">
         <f aca="false">IF(OR(H624="",I624=""),"",IF(I624&gt;0,H624/I624,""))</f>
@@ -44945,10 +44945,10 @@
         <v>32</v>
       </c>
       <c r="K626" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L626" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L626" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M626" s="8" t="n">
         <f aca="false">IF(OR(H626="",I626=""),"",IF(I626&gt;0,H626/I626,""))</f>
@@ -45012,7 +45012,7 @@
         <v>32</v>
       </c>
       <c r="K627" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L627" s="4" t="s">
         <v>57</v>
@@ -45079,10 +45079,10 @@
         <v>32</v>
       </c>
       <c r="K628" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L628" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L628" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M628" s="8" t="n">
         <f aca="false">IF(OR(H628="",I628=""),"",IF(I628&gt;0,H628/I628,""))</f>
@@ -45146,10 +45146,10 @@
         <v>32</v>
       </c>
       <c r="K629" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L629" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L629" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M629" s="8" t="str">
         <f aca="false">IF(OR(H629="",I629=""),"",IF(I629&gt;0,H629/I629,""))</f>
@@ -45213,10 +45213,10 @@
         <v>32</v>
       </c>
       <c r="K630" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L630" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L630" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M630" s="8" t="str">
         <f aca="false">IF(OR(H630="",I630=""),"",IF(I630&gt;0,H630/I630,""))</f>
@@ -45280,10 +45280,10 @@
         <v>32</v>
       </c>
       <c r="K631" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L631" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L631" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M631" s="8" t="str">
         <f aca="false">IF(OR(H631="",I631=""),"",IF(I631&gt;0,H631/I631,""))</f>
@@ -45453,10 +45453,10 @@
         <v>32</v>
       </c>
       <c r="K634" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L634" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="L634" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M634" s="8" t="str">
         <f aca="false">IF(OR(H634="",I634=""),"",IF(I634&gt;0,H634/I634,""))</f>

--- a/FCF_K13/PFCF_GETIRI.xlsx
+++ b/FCF_K13/PFCF_GETIRI.xlsx
@@ -35599,24 +35599,24 @@
         <v>3788.73</v>
       </c>
       <c r="I480" s="7" t="n">
-        <v>2147.827</v>
+        <v>1317.5914384</v>
       </c>
       <c r="J480" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L480" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M480" s="8" t="n">
         <f aca="false">IF(OR(H480="",I480=""),"",IF(I480&gt;0,H480/I480,""))</f>
-        <v>1.76398285336761</v>
+        <v>2.87549682669523</v>
       </c>
       <c r="N480" s="4" t="str">
         <f aca="false">IF(I480="",IF(K480="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I480&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K480="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O480" s="9" t="n">
         <f aca="false">IF(Q480="","",F480*R480/Q480-1)</f>

--- a/FCF_K13/PFCF_GETIRI.xlsx
+++ b/FCF_K13/PFCF_GETIRI.xlsx
@@ -5142,7 +5142,7 @@
         <v>6403.32</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-406.025</v>
+        <v>-406.0259744</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>32</v>
@@ -5151,7 +5151,7 @@
         <v>33</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M9" s="8" t="str">
         <f aca="false">IF(OR(H9="",I9=""),"",IF(I9&gt;0,H9/I9,""))</f>
@@ -9330,7 +9330,7 @@
         <v>9150</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>-0.0900000000000105</v>
+        <v>-0.0903120000000044</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>32</v>
@@ -9339,7 +9339,7 @@
         <v>33</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M75" s="8" t="str">
         <f aca="false">IF(OR(H75="",I75=""),"",IF(I75&gt;0,H75/I75,""))</f>
@@ -9464,20 +9464,20 @@
         <v>7187.25</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>1752.834604</v>
+        <v>1752.8383072</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M77" s="8" t="n">
         <f aca="false">IF(OR(H77="",I77=""),"",IF(I77&gt;0,H77/I77,""))</f>
-        <v>4.10035834732984</v>
+        <v>4.10034968455304</v>
       </c>
       <c r="N77" s="4" t="str">
         <f aca="false">IF(I77="",IF(K77="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I77&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K77="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -13097,7 +13097,7 @@
         <v>2705.32</v>
       </c>
       <c r="I132" s="7" t="n">
-        <v>-351.893</v>
+        <v>-351.8936208</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>32</v>
@@ -13106,7 +13106,7 @@
         <v>33</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M132" s="8" t="str">
         <f aca="false">IF(OR(H132="",I132=""),"",IF(I132&gt;0,H132/I132,""))</f>
@@ -13499,16 +13499,16 @@
         <v>11356.81977738</v>
       </c>
       <c r="I138" s="7" t="n">
-        <v>-563.771</v>
+        <v>-563.7706496</v>
       </c>
       <c r="J138" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M138" s="8" t="str">
         <f aca="false">IF(OR(H138="",I138=""),"",IF(I138&gt;0,H138/I138,""))</f>
@@ -15609,20 +15609,20 @@
         <v>1553.8</v>
       </c>
       <c r="I170" s="7" t="n">
-        <v>1036.616</v>
+        <v>1036.6163248</v>
       </c>
       <c r="J170" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K170" s="4" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M170" s="8" t="n">
         <f aca="false">IF(OR(H170="",I170=""),"",IF(I170&gt;0,H170/I170,""))</f>
-        <v>1.49891570263241</v>
+        <v>1.49891523298148</v>
       </c>
       <c r="N170" s="4" t="str">
         <f aca="false">IF(I170="",IF(K170="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I170&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K170="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -16001,7 +16001,7 @@
         <v>1254.375</v>
       </c>
       <c r="I176" s="7" t="n">
-        <v>-132.539</v>
+        <v>-132.5397248</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>32</v>
@@ -16010,7 +16010,7 @@
         <v>33</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M176" s="8" t="str">
         <f aca="false">IF(OR(H176="",I176=""),"",IF(I176&gt;0,H176/I176,""))</f>
@@ -16592,7 +16592,7 @@
         <v>3108</v>
       </c>
       <c r="I185" s="7" t="n">
-        <v>645.578</v>
+        <v>645.5777056</v>
       </c>
       <c r="J185" s="4" t="s">
         <v>32</v>
@@ -16601,11 +16601,11 @@
         <v>33</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M185" s="8" t="n">
         <f aca="false">IF(OR(H185="",I185=""),"",IF(I185&gt;0,H185/I185,""))</f>
-        <v>4.81429044979848</v>
+        <v>4.81429264523846</v>
       </c>
       <c r="N185" s="4" t="str">
         <f aca="false">IF(I185="",IF(K185="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I185&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K185="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -17807,16 +17807,16 @@
         <v>3841.6</v>
       </c>
       <c r="I204" s="7" t="n">
-        <v>-840.062</v>
+        <v>-840.0628896</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K204" s="4" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="L204" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M204" s="8" t="str">
         <f aca="false">IF(OR(H204="",I204=""),"",IF(I204&gt;0,H204/I204,""))</f>
@@ -17941,7 +17941,7 @@
         <v>2604.96</v>
       </c>
       <c r="I206" s="7" t="n">
-        <v>-172.025</v>
+        <v>-172.025048</v>
       </c>
       <c r="J206" s="4" t="s">
         <v>32</v>
@@ -17950,7 +17950,7 @@
         <v>33</v>
       </c>
       <c r="L206" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M206" s="8" t="str">
         <f aca="false">IF(OR(H206="",I206=""),"",IF(I206&gt;0,H206/I206,""))</f>
@@ -19133,7 +19133,7 @@
         <v>4641</v>
       </c>
       <c r="I224" s="7" t="n">
-        <v>507.641</v>
+        <v>507.6426352</v>
       </c>
       <c r="J224" s="4" t="s">
         <v>32</v>
@@ -19142,11 +19142,11 @@
         <v>33</v>
       </c>
       <c r="L224" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M224" s="8" t="n">
         <f aca="false">IF(OR(H224="",I224=""),"",IF(I224&gt;0,H224/I224,""))</f>
-        <v>9.14228756148538</v>
+        <v>9.14225811268108</v>
       </c>
       <c r="N224" s="4" t="str">
         <f aca="false">IF(I224="",IF(K224="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I224&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K224="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -22191,7 +22191,7 @@
         <v>137775</v>
       </c>
       <c r="I272" s="7" t="n">
-        <v>11617.73</v>
+        <v>11617.7373744</v>
       </c>
       <c r="J272" s="4" t="s">
         <v>32</v>
@@ -22200,11 +22200,11 @@
         <v>33</v>
       </c>
       <c r="L272" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M272" s="8" t="n">
         <f aca="false">IF(OR(H272="",I272=""),"",IF(I272&gt;0,H272/I272,""))</f>
-        <v>11.8590292595886</v>
+        <v>11.8590217320277</v>
       </c>
       <c r="N272" s="4" t="str">
         <f aca="false">IF(I272="",IF(K272="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I272&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K272="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -22392,7 +22392,7 @@
         <v>1992.9</v>
       </c>
       <c r="I275" s="7" t="n">
-        <v>-582.559</v>
+        <v>-582.558512</v>
       </c>
       <c r="J275" s="4" t="s">
         <v>32</v>
@@ -22401,7 +22401,7 @@
         <v>33</v>
       </c>
       <c r="L275" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M275" s="8" t="str">
         <f aca="false">IF(OR(H275="",I275=""),"",IF(I275&gt;0,H275/I275,""))</f>
@@ -22949,7 +22949,7 @@
         <v>4003.19283616</v>
       </c>
       <c r="I284" s="7" t="n">
-        <v>-771.952</v>
+        <v>-771.953312</v>
       </c>
       <c r="J284" s="4" t="s">
         <v>32</v>
@@ -22958,7 +22958,7 @@
         <v>33</v>
       </c>
       <c r="L284" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M284" s="8" t="str">
         <f aca="false">IF(OR(H284="",I284=""),"",IF(I284&gt;0,H284/I284,""))</f>
@@ -25366,7 +25366,7 @@
         <v>9579.5</v>
       </c>
       <c r="I323" s="7" t="n">
-        <v>504.076</v>
+        <v>504.07848</v>
       </c>
       <c r="J323" s="4" t="s">
         <v>32</v>
@@ -25375,11 +25375,11 @@
         <v>33</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M323" s="8" t="n">
         <f aca="false">IF(OR(H323="",I323=""),"",IF(I323&gt;0,H323/I323,""))</f>
-        <v>19.0040787500298</v>
+        <v>19.0039852524551</v>
       </c>
       <c r="N323" s="4" t="str">
         <f aca="false">IF(I323="",IF(K323="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I323&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K323="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -25567,7 +25567,7 @@
         <v>10095</v>
       </c>
       <c r="I326" s="7" t="n">
-        <v>915.675</v>
+        <v>915.6774576</v>
       </c>
       <c r="J326" s="4" t="s">
         <v>32</v>
@@ -25576,11 +25576,11 @@
         <v>33</v>
       </c>
       <c r="L326" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M326" s="8" t="n">
         <f aca="false">IF(OR(H326="",I326=""),"",IF(I326&gt;0,H326/I326,""))</f>
-        <v>11.0246539438119</v>
+        <v>11.0246243545834</v>
       </c>
       <c r="N326" s="4" t="str">
         <f aca="false">IF(I326="",IF(K326="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I326&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K326="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -26034,16 +26034,16 @@
         <v>3294.4725</v>
       </c>
       <c r="I333" s="7" t="n">
-        <v>-767.427</v>
+        <v>-767.4290128</v>
       </c>
       <c r="J333" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="L333" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M333" s="8" t="str">
         <f aca="false">IF(OR(H333="",I333=""),"",IF(I333&gt;0,H333/I333,""))</f>
@@ -26434,7 +26434,7 @@
         <v>4708.04064</v>
       </c>
       <c r="I339" s="7" t="n">
-        <v>-177.866</v>
+        <v>-177.8681952</v>
       </c>
       <c r="J339" s="4" t="s">
         <v>32</v>
@@ -26443,7 +26443,7 @@
         <v>33</v>
       </c>
       <c r="L339" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M339" s="8" t="str">
         <f aca="false">IF(OR(H339="",I339=""),"",IF(I339&gt;0,H339/I339,""))</f>
@@ -29869,7 +29869,7 @@
         <v>24219.5</v>
       </c>
       <c r="I392" s="7" t="n">
-        <v>93.4279999999999</v>
+        <v>93.4278944</v>
       </c>
       <c r="J392" s="4" t="s">
         <v>32</v>
@@ -29878,11 +29878,11 @@
         <v>33</v>
       </c>
       <c r="L392" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M392" s="8" t="n">
         <f aca="false">IF(OR(H392="",I392=""),"",IF(I392&gt;0,H392/I392,""))</f>
-        <v>259.231707839192</v>
+        <v>259.232000844493</v>
       </c>
       <c r="N392" s="4" t="str">
         <f aca="false">IF(I392="",IF(K392="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I392&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K392="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -30662,7 +30662,7 @@
         <v>33</v>
       </c>
       <c r="L404" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M404" s="8" t="str">
         <f aca="false">IF(OR(H404="",I404=""),"",IF(I404&gt;0,H404/I404,""))</f>
@@ -32093,7 +32093,7 @@
         <v>2273.31</v>
       </c>
       <c r="I426" s="7" t="n">
-        <v>-153.87</v>
+        <v>-181.2489728</v>
       </c>
       <c r="J426" s="4" t="s">
         <v>32</v>
@@ -32102,7 +32102,7 @@
         <v>33</v>
       </c>
       <c r="L426" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M426" s="8" t="str">
         <f aca="false">IF(OR(H426="",I426=""),"",IF(I426&gt;0,H426/I426,""))</f>
@@ -32867,7 +32867,7 @@
         <v>12973.15279854</v>
       </c>
       <c r="I438" s="7" t="n">
-        <v>-1015.45</v>
+        <v>-1015.4494096</v>
       </c>
       <c r="J438" s="4" t="s">
         <v>32</v>
@@ -32876,7 +32876,7 @@
         <v>33</v>
       </c>
       <c r="L438" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M438" s="8" t="str">
         <f aca="false">IF(OR(H438="",I438=""),"",IF(I438&gt;0,H438/I438,""))</f>
@@ -33984,7 +33984,7 @@
         <v>573.75</v>
       </c>
       <c r="I455" s="7" t="n">
-        <v>-103.035</v>
+        <v>-103.0356896</v>
       </c>
       <c r="J455" s="4" t="s">
         <v>32</v>
@@ -33993,7 +33993,7 @@
         <v>33</v>
       </c>
       <c r="L455" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M455" s="8" t="str">
         <f aca="false">IF(OR(H455="",I455=""),"",IF(I455&gt;0,H455/I455,""))</f>
@@ -35398,7 +35398,7 @@
         <v>2518.7927875</v>
       </c>
       <c r="I477" s="7" t="n">
-        <v>200.312</v>
+        <v>200.3121024</v>
       </c>
       <c r="J477" s="4" t="s">
         <v>32</v>
@@ -35407,11 +35407,11 @@
         <v>33</v>
       </c>
       <c r="L477" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M477" s="8" t="n">
         <f aca="false">IF(OR(H477="",I477=""),"",IF(I477&gt;0,H477/I477,""))</f>
-        <v>12.5743479546907</v>
+        <v>12.5743415266556</v>
       </c>
       <c r="N477" s="4" t="str">
         <f aca="false">IF(I477="",IF(K477="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I477&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K477="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -35465,7 +35465,7 @@
         <v>2138.5</v>
       </c>
       <c r="I478" s="7" t="n">
-        <v>121.425</v>
+        <v>121.424712</v>
       </c>
       <c r="J478" s="4" t="s">
         <v>32</v>
@@ -35474,11 +35474,11 @@
         <v>33</v>
       </c>
       <c r="L478" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M478" s="8" t="n">
         <f aca="false">IF(OR(H478="",I478=""),"",IF(I478&gt;0,H478/I478,""))</f>
-        <v>17.6116944616018</v>
+        <v>17.6117362337248</v>
       </c>
       <c r="N478" s="4" t="str">
         <f aca="false">IF(I478="",IF(K478="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I478&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K478="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -35532,7 +35532,7 @@
         <v>2478.36672</v>
       </c>
       <c r="I479" s="7" t="n">
-        <v>9.60300000000001</v>
+        <v>9.60355520000002</v>
       </c>
       <c r="J479" s="4" t="s">
         <v>32</v>
@@ -35541,11 +35541,11 @@
         <v>33</v>
       </c>
       <c r="L479" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M479" s="8" t="n">
         <f aca="false">IF(OR(H479="",I479=""),"",IF(I479&gt;0,H479/I479,""))</f>
-        <v>258.082549203374</v>
+        <v>258.067628954743</v>
       </c>
       <c r="N479" s="4" t="str">
         <f aca="false">IF(I479="",IF(K479="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I479&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K479="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -35800,7 +35800,7 @@
         <v>14062.59</v>
       </c>
       <c r="I483" s="7" t="n">
-        <v>169.909</v>
+        <v>169.9078768</v>
       </c>
       <c r="J483" s="4" t="s">
         <v>32</v>
@@ -35809,11 +35809,11 @@
         <v>33</v>
       </c>
       <c r="L483" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M483" s="8" t="n">
         <f aca="false">IF(OR(H483="",I483=""),"",IF(I483&gt;0,H483/I483,""))</f>
-        <v>82.7654214903272</v>
+        <v>82.7659686228273</v>
       </c>
       <c r="N483" s="4" t="str">
         <f aca="false">IF(I483="",IF(K483="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I483&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K483="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -38413,7 +38413,7 @@
         <v>602</v>
       </c>
       <c r="I524" s="7" t="n">
-        <v>74.11</v>
+        <v>74.1103312</v>
       </c>
       <c r="J524" s="4" t="s">
         <v>32</v>
@@ -38422,11 +38422,11 @@
         <v>33</v>
       </c>
       <c r="L524" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M524" s="8" t="n">
         <f aca="false">IF(OR(H524="",I524=""),"",IF(I524&gt;0,H524/I524,""))</f>
-        <v>8.12306031574686</v>
+        <v>8.12302401368839</v>
       </c>
       <c r="N524" s="4" t="str">
         <f aca="false">IF(I524="",IF(K524="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I524&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K524="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -38858,7 +38858,7 @@
         <v>518.08425</v>
       </c>
       <c r="I531" s="7" t="n">
-        <v>1.54299999999993</v>
+        <v>1.54268639999994</v>
       </c>
       <c r="J531" s="4" t="s">
         <v>32</v>
@@ -38867,11 +38867,11 @@
         <v>33</v>
       </c>
       <c r="L531" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M531" s="8" t="n">
         <f aca="false">IF(OR(H531="",I531=""),"",IF(I531&gt;0,H531/I531,""))</f>
-        <v>335.764257939095</v>
+        <v>335.832512686973</v>
       </c>
       <c r="N531" s="4" t="str">
         <f aca="false">IF(I531="",IF(K531="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I531&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K531="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -39104,7 +39104,7 @@
         <v>1368</v>
       </c>
       <c r="I535" s="7" t="n">
-        <v>324.29</v>
+        <v>320.3424768</v>
       </c>
       <c r="J535" s="4" t="s">
         <v>32</v>
@@ -39113,11 +39113,11 @@
         <v>33</v>
       </c>
       <c r="L535" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M535" s="8" t="n">
         <f aca="false">IF(OR(H535="",I535=""),"",IF(I535&gt;0,H535/I535,""))</f>
-        <v>4.21844645224953</v>
+        <v>4.27042961540841</v>
       </c>
       <c r="N535" s="4" t="str">
         <f aca="false">IF(I535="",IF(K535="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I535&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K535="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -39171,7 +39171,7 @@
         <v>7191.6</v>
       </c>
       <c r="I536" s="7" t="n">
-        <v>554.258</v>
+        <v>554.2561824</v>
       </c>
       <c r="J536" s="4" t="s">
         <v>32</v>
@@ -39180,11 +39180,11 @@
         <v>33</v>
       </c>
       <c r="L536" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M536" s="8" t="n">
         <f aca="false">IF(OR(H536="",I536=""),"",IF(I536&gt;0,H536/I536,""))</f>
-        <v>12.9751848417163</v>
+        <v>12.9752273918885</v>
       </c>
       <c r="N536" s="4" t="str">
         <f aca="false">IF(I536="",IF(K536="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I536&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K536="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -40654,7 +40654,7 @@
         <v>1326</v>
       </c>
       <c r="I559" s="7" t="n">
-        <v>-94.143</v>
+        <v>-94.1420704</v>
       </c>
       <c r="J559" s="4" t="s">
         <v>32</v>
@@ -40663,7 +40663,7 @@
         <v>33</v>
       </c>
       <c r="L559" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M559" s="8" t="str">
         <f aca="false">IF(OR(H559="",I559=""),"",IF(I559&gt;0,H559/I559,""))</f>
@@ -41509,7 +41509,7 @@
         <v>138860.4</v>
       </c>
       <c r="I572" s="7" t="n">
-        <v>-880.248999999999</v>
+        <v>-880.2476432</v>
       </c>
       <c r="J572" s="4" t="s">
         <v>32</v>
@@ -41518,7 +41518,7 @@
         <v>33</v>
       </c>
       <c r="L572" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M572" s="8" t="str">
         <f aca="false">IF(OR(H572="",I572=""),"",IF(I572&gt;0,H572/I572,""))</f>
@@ -42208,7 +42208,7 @@
         <v>40301.93390625</v>
       </c>
       <c r="I583" s="7" t="n">
-        <v>2948.957</v>
+        <v>2948.9602752</v>
       </c>
       <c r="J583" s="4" t="s">
         <v>32</v>
@@ -42217,11 +42217,11 @@
         <v>33</v>
       </c>
       <c r="L583" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M583" s="8" t="n">
         <f aca="false">IF(OR(H583="",I583=""),"",IF(I583&gt;0,H583/I583,""))</f>
-        <v>13.6665044306343</v>
+        <v>13.6664892522219</v>
       </c>
       <c r="N583" s="4" t="str">
         <f aca="false">IF(I583="",IF(K583="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I583&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K583="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
@@ -43238,7 +43238,7 @@
         <v>1053.5</v>
       </c>
       <c r="I599" s="7" t="n">
-        <v>-2456.821</v>
+        <v>-2456.8216096</v>
       </c>
       <c r="J599" s="4" t="s">
         <v>32</v>
@@ -43247,7 +43247,7 @@
         <v>33</v>
       </c>
       <c r="L599" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M599" s="8" t="str">
         <f aca="false">IF(OR(H599="",I599=""),"",IF(I599&gt;0,H599/I599,""))</f>
@@ -43305,7 +43305,7 @@
         <v>1157.5985</v>
       </c>
       <c r="I600" s="7" t="n">
-        <v>-2.419</v>
+        <v>-2.4193344</v>
       </c>
       <c r="J600" s="4" t="s">
         <v>32</v>
@@ -43314,7 +43314,7 @@
         <v>33</v>
       </c>
       <c r="L600" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M600" s="8" t="str">
         <f aca="false">IF(OR(H600="",I600=""),"",IF(I600&gt;0,H600/I600,""))</f>
@@ -44167,7 +44167,7 @@
         <v>669.9</v>
       </c>
       <c r="I614" s="7" t="n">
-        <v>-536.127</v>
+        <v>-536.1262688</v>
       </c>
       <c r="J614" s="4" t="s">
         <v>32</v>
@@ -44176,7 +44176,7 @@
         <v>33</v>
       </c>
       <c r="L614" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M614" s="8" t="str">
         <f aca="false">IF(OR(H614="",I614=""),"",IF(I614&gt;0,H614/I614,""))</f>

--- a/FCF_K13/PFCF_GETIRI.xlsx
+++ b/FCF_K13/PFCF_GETIRI.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5113" uniqueCount="1406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5113" uniqueCount="1407">
   <si>
     <t xml:space="preserve">P/FCF ve getiriler — BIST (FCF: FCF_MASTER, GEM v6.2)</t>
   </si>
@@ -522,112 +522,115 @@
     <t xml:space="preserve">Doğu Aras Enerji Yatırımları A.Ş.</t>
   </si>
   <si>
+    <t xml:space="preserve">KARMA (Diğer içindeki capex: BELGE dipnot; diğer bileşenler: EVO (belgeyle teyitli))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCLK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arçelik A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARDYZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ard Grup Bilişim Teknolojileri A.Ş</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilişim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arena Bilgisayar Sanayi ve Ticaret A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknoloji Ticaret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARFYE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arf Bio Yenilenebilir Enerji Üretim A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armada Gıda Ticaret Sanayi A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARSAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arsan Holding A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artemis Halı A.Ş</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekstil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARZUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arzum Elektrikli Ev Aletleri Sanayi ve Ticaret A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASELS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aselsan Elektronik Sanayi ve Ticaret A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASGYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asce Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astor Enerji A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASUZU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anadolu Isuzu Otomotiv Sanayi ve Ticaret A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otomotiv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATAGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.10.2026 16:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATAKP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atakey Patates Gıda Sanayi ve Ticaret AŞ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATATP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP Yazılım ve Teknoloji A.Ş.</t>
+  </si>
+  <si>
     <t xml:space="preserve">KOŞULLU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARCLK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arçelik A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARDYZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ard Grup Bilişim Teknolojileri A.Ş</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilişim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arena Bilgisayar Sanayi ve Ticaret A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teknoloji Ticaret</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARFYE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arf Bio Yenilenebilir Enerji Üretim A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMGD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armada Gıda Ticaret Sanayi A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARSAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arsan Holding A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARTMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artemis Halı A.Ş</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekstil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARZUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arzum Elektrikli Ev Aletleri Sanayi ve Ticaret A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASELS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aselsan Elektronik Sanayi ve Ticaret A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASGYO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asce Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astor Enerji A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASUZU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anadolu Isuzu Otomotiv Sanayi ve Ticaret A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Otomotiv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATAGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ata Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.10.2026 16:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATAKP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atakey Patates Gıda Sanayi ve Ticaret AŞ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATATP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP Yazılım ve Teknoloji A.Ş.</t>
   </si>
   <si>
     <t xml:space="preserve">ATATR</t>
@@ -7719,24 +7722,24 @@
         <v>24187.5</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>6966.1320704</v>
+        <v>2708.4126576</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K50" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L50" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="M50" s="8" t="n">
         <f aca="false">IF(OR(H50="",I50=""),"",IF(I50&gt;0,H50/I50,""))</f>
-        <v>3.4721563926093</v>
+        <v>8.93050766548744</v>
       </c>
       <c r="N50" s="4" t="str">
         <f aca="false">IF(I50="",IF(K50="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I50&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K50="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O50" s="9" t="n">
         <f aca="false">IF(Q50="","",F50*R50/Q50-1)</f>
@@ -8448,7 +8451,7 @@
         <v>32</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L61" s="4" t="s">
         <v>34</v>
@@ -8704,7 +8707,7 @@
         <v>32</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>34</v>
@@ -8741,10 +8744,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>29</v>
@@ -8753,7 +8756,7 @@
         <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>5.73</v>
@@ -8806,10 +8809,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>29</v>
@@ -8873,10 +8876,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>29</v>
@@ -8928,10 +8931,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>29</v>
@@ -8995,10 +8998,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>38</v>
@@ -9050,10 +9053,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>29</v>
@@ -9117,10 +9120,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>29</v>
@@ -9184,10 +9187,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>38</v>
@@ -9198,7 +9201,7 @@
         <v>52.1</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H73" s="6" t="n">
         <v>20840</v>
@@ -9239,10 +9242,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>29</v>
@@ -9251,7 +9254,7 @@
         <v>30</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>9.4</v>
@@ -9306,10 +9309,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>29</v>
@@ -9318,13 +9321,13 @@
         <v>30</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>366</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H75" s="6" t="n">
         <v>9150</v>
@@ -9373,10 +9376,10 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>29</v>
@@ -9440,10 +9443,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>29</v>
@@ -9507,10 +9510,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>29</v>
@@ -9571,15 +9574,15 @@
         <v>3.55555552</v>
       </c>
       <c r="U78" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>29</v>
@@ -9643,10 +9646,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>29</v>
@@ -9710,10 +9713,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>29</v>
@@ -9777,10 +9780,10 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>29</v>
@@ -9844,10 +9847,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>29</v>
@@ -9856,7 +9859,7 @@
         <v>30</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F83" s="5" t="n">
         <v>31.26</v>
@@ -9911,10 +9914,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>29</v>
@@ -9923,7 +9926,7 @@
         <v>30</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>59.6</v>
@@ -9978,10 +9981,10 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>29</v>
@@ -10043,10 +10046,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>29</v>
@@ -10110,10 +10113,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>29</v>
@@ -10122,7 +10125,7 @@
         <v>30</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F87" s="5" t="n">
         <v>5.7</v>
@@ -10177,10 +10180,10 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>29</v>
@@ -10244,10 +10247,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>29</v>
@@ -10311,10 +10314,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>29</v>
@@ -10378,10 +10381,10 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>38</v>
@@ -10433,10 +10436,10 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>29</v>
@@ -10500,10 +10503,10 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>29</v>
@@ -10530,7 +10533,7 @@
         <v>32</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L93" s="4" t="s">
         <v>34</v>
@@ -10567,10 +10570,10 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>29</v>
@@ -10632,10 +10635,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>29</v>
@@ -10695,10 +10698,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>29</v>
@@ -10762,10 +10765,10 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>29</v>
@@ -10774,7 +10777,7 @@
         <v>30</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F97" s="5" t="n">
         <v>108.8</v>
@@ -10829,10 +10832,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>29</v>
@@ -10841,7 +10844,7 @@
         <v>30</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>14.64</v>
@@ -10896,10 +10899,10 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>29</v>
@@ -10963,10 +10966,10 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>29</v>
@@ -10981,7 +10984,7 @@
         <v>32.44</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H100" s="6" t="n">
         <v>18717.88</v>
@@ -11030,10 +11033,10 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>29</v>
@@ -11097,10 +11100,10 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>29</v>
@@ -11109,7 +11112,7 @@
         <v>30</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F102" s="5" t="n">
         <v>408.5</v>
@@ -11161,15 +11164,15 @@
         <v>1</v>
       </c>
       <c r="U102" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>29</v>
@@ -11178,7 +11181,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F103" s="5" t="n">
         <v>47.04</v>
@@ -11233,10 +11236,10 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>29</v>
@@ -11300,10 +11303,10 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>29</v>
@@ -11367,10 +11370,10 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>29</v>
@@ -11379,7 +11382,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>19.41</v>
@@ -11434,10 +11437,10 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>29</v>
@@ -11446,7 +11449,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>1.58</v>
@@ -11499,10 +11502,10 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>38</v>
@@ -11552,10 +11555,10 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>29</v>
@@ -11616,15 +11619,15 @@
         <v>1</v>
       </c>
       <c r="U109" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>29</v>
@@ -11633,7 +11636,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>34.02</v>
@@ -11688,10 +11691,10 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>29</v>
@@ -11700,7 +11703,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>9.09</v>
@@ -11755,19 +11758,19 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E112" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="F112" s="5" t="n">
         <v>37.8</v>
@@ -11819,15 +11822,15 @@
         <v>1</v>
       </c>
       <c r="U112" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>29</v>
@@ -11836,13 +11839,13 @@
         <v>30</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F113" s="5" t="n">
         <v>5.54</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H113" s="6" t="n">
         <v>1339.9875</v>
@@ -11891,10 +11894,10 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>29</v>
@@ -11921,7 +11924,7 @@
         <v>32</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L114" s="4" t="s">
         <v>34</v>
@@ -11958,10 +11961,10 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>29</v>
@@ -11970,7 +11973,7 @@
         <v>30</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>1.63</v>
@@ -12025,10 +12028,10 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>29</v>
@@ -12092,10 +12095,10 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>29</v>
@@ -12159,10 +12162,10 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>29</v>
@@ -12171,7 +12174,7 @@
         <v>30</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F118" s="5" t="n">
         <v>72.2</v>
@@ -12226,10 +12229,10 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>29</v>
@@ -12293,10 +12296,10 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>29</v>
@@ -12360,10 +12363,10 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>60</v>
@@ -12415,10 +12418,10 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>29</v>
@@ -12482,10 +12485,10 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>29</v>
@@ -12549,10 +12552,10 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>29</v>
@@ -12561,7 +12564,7 @@
         <v>30</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F124" s="5" t="n">
         <v>681.5</v>
@@ -12616,10 +12619,10 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>29</v>
@@ -12683,10 +12686,10 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>29</v>
@@ -12750,10 +12753,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>29</v>
@@ -12817,10 +12820,10 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>29</v>
@@ -12884,10 +12887,10 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>38</v>
@@ -12939,10 +12942,10 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>29</v>
@@ -12951,7 +12954,7 @@
         <v>30</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F130" s="5" t="n">
         <v>26.88</v>
@@ -13006,10 +13009,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>29</v>
@@ -13018,13 +13021,13 @@
         <v>30</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F131" s="5" t="n">
         <v>488.25</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H131" s="6" t="n">
         <v>3587.500854</v>
@@ -13073,10 +13076,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>29</v>
@@ -13140,10 +13143,10 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>29</v>
@@ -13207,10 +13210,10 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>29</v>
@@ -13237,7 +13240,7 @@
         <v>32</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="L134" s="4" t="s">
         <v>42</v>
@@ -13274,10 +13277,10 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>29</v>
@@ -13341,10 +13344,10 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>29</v>
@@ -13408,10 +13411,10 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>29</v>
@@ -13475,10 +13478,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>29</v>
@@ -13487,7 +13490,7 @@
         <v>30</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F138" s="5" t="n">
         <v>29.46</v>
@@ -13542,10 +13545,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>29</v>
@@ -13554,7 +13557,7 @@
         <v>30</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F139" s="5" t="n">
         <v>3.14</v>
@@ -13609,10 +13612,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>29</v>
@@ -13621,7 +13624,7 @@
         <v>30</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F140" s="5" t="n">
         <v>7.84</v>
@@ -13676,10 +13679,10 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>29</v>
@@ -13688,7 +13691,7 @@
         <v>30</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F141" s="5" t="n">
         <v>5.46</v>
@@ -13740,15 +13743,15 @@
         <v>1</v>
       </c>
       <c r="U141" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>29</v>
@@ -13812,10 +13815,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>29</v>
@@ -13824,7 +13827,7 @@
         <v>30</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F143" s="5" t="n">
         <v>20.54</v>
@@ -13879,10 +13882,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>29</v>
@@ -13946,10 +13949,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>29</v>
@@ -14009,10 +14012,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>29</v>
@@ -14021,7 +14024,7 @@
         <v>30</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F146" s="5" t="n">
         <v>1354</v>
@@ -14076,10 +14079,10 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>29</v>
@@ -14143,10 +14146,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>29</v>
@@ -14210,10 +14213,10 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>29</v>
@@ -14277,10 +14280,10 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>29</v>
@@ -14344,10 +14347,10 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>60</v>
@@ -14399,10 +14402,10 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>29</v>
@@ -14411,7 +14414,7 @@
         <v>30</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F152" s="5" t="n">
         <v>222.4</v>
@@ -14466,10 +14469,10 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>29</v>
@@ -14478,7 +14481,7 @@
         <v>30</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F153" s="5" t="n">
         <v>19.44</v>
@@ -14533,10 +14536,10 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>29</v>
@@ -14545,7 +14548,7 @@
         <v>30</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F154" s="5" t="n">
         <v>12.45</v>
@@ -14597,15 +14600,15 @@
         <v>1</v>
       </c>
       <c r="U154" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>29</v>
@@ -14669,10 +14672,10 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>29</v>
@@ -14736,10 +14739,10 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>29</v>
@@ -14791,10 +14794,10 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>29</v>
@@ -14858,10 +14861,10 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>29</v>
@@ -14870,7 +14873,7 @@
         <v>30</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F159" s="5" t="n">
         <v>3.5</v>
@@ -14925,10 +14928,10 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>29</v>
@@ -14992,10 +14995,10 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>29</v>
@@ -15056,15 +15059,15 @@
         <v>1</v>
       </c>
       <c r="U161" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>29</v>
@@ -15128,10 +15131,10 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>29</v>
@@ -15195,10 +15198,10 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>29</v>
@@ -15262,10 +15265,10 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>29</v>
@@ -15329,10 +15332,10 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>29</v>
@@ -15396,10 +15399,10 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>38</v>
@@ -15451,10 +15454,10 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>29</v>
@@ -15463,7 +15466,7 @@
         <v>30</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F168" s="5" t="n">
         <v>3.81</v>
@@ -15518,10 +15521,10 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>29</v>
@@ -15585,10 +15588,10 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>29</v>
@@ -15597,7 +15600,7 @@
         <v>30</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F170" s="5" t="n">
         <v>9.14</v>
@@ -15652,10 +15655,10 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>29</v>
@@ -15719,10 +15722,10 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>29</v>
@@ -15731,7 +15734,7 @@
         <v>30</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F172" s="5" t="n">
         <v>6.81</v>
@@ -15786,10 +15789,10 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>29</v>
@@ -15850,15 +15853,15 @@
         <v>1</v>
       </c>
       <c r="U173" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>29</v>
@@ -15922,10 +15925,10 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>60</v>
@@ -15977,10 +15980,10 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>29</v>
@@ -15995,7 +15998,7 @@
         <v>22.5</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H176" s="6" t="n">
         <v>1254.375</v>
@@ -16044,10 +16047,10 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>29</v>
@@ -16111,10 +16114,10 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>29</v>
@@ -16178,10 +16181,10 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>29</v>
@@ -16245,10 +16248,10 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>29</v>
@@ -16257,7 +16260,7 @@
         <v>30</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F180" s="5" t="n">
         <v>15.94</v>
@@ -16312,10 +16315,10 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>60</v>
@@ -16326,7 +16329,7 @@
         <v>562.5</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H181" s="6" t="n">
         <v>187499.9998125</v>
@@ -16367,10 +16370,10 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>29</v>
@@ -16434,10 +16437,10 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>29</v>
@@ -16446,7 +16449,7 @@
         <v>30</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F183" s="5" t="n">
         <v>6.11</v>
@@ -16501,10 +16504,10 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>29</v>
@@ -16568,10 +16571,10 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>29</v>
@@ -16635,10 +16638,10 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>38</v>
@@ -16690,10 +16693,10 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>29</v>
@@ -16702,7 +16705,7 @@
         <v>30</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F187" s="5" t="n">
         <v>80.1</v>
@@ -16757,10 +16760,10 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>29</v>
@@ -16824,10 +16827,10 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>29</v>
@@ -16889,10 +16892,10 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>29</v>
@@ -16956,10 +16959,10 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>29</v>
@@ -17023,10 +17026,10 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>29</v>
@@ -17078,10 +17081,10 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>29</v>
@@ -17145,10 +17148,10 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>29</v>
@@ -17157,7 +17160,7 @@
         <v>30</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F194" s="5" t="n">
         <v>5015</v>
@@ -17175,7 +17178,7 @@
         <v>32</v>
       </c>
       <c r="K194" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L194" s="4" t="s">
         <v>34</v>
@@ -17186,7 +17189,7 @@
       </c>
       <c r="N194" s="4" t="str">
         <f aca="false">IF(I194="",IF(K194="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I194&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K194="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O194" s="9" t="n">
         <f aca="false">IF(Q194="","",F194*R194/Q194-1)</f>
@@ -17212,10 +17215,10 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>38</v>
@@ -17267,10 +17270,10 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>29</v>
@@ -17334,10 +17337,10 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>29</v>
@@ -17401,10 +17404,10 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>29</v>
@@ -17468,10 +17471,10 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>29</v>
@@ -17480,7 +17483,7 @@
         <v>30</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F199" s="5" t="n">
         <v>2.65</v>
@@ -17535,10 +17538,10 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>29</v>
@@ -17547,7 +17550,7 @@
         <v>30</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F200" s="5" t="n">
         <v>29.14</v>
@@ -17598,10 +17601,10 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>38</v>
@@ -17653,10 +17656,10 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>29</v>
@@ -17665,7 +17668,7 @@
         <v>30</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F202" s="5" t="n">
         <v>15.51</v>
@@ -17716,10 +17719,10 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>29</v>
@@ -17783,10 +17786,10 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>29</v>
@@ -17850,10 +17853,10 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>29</v>
@@ -17917,10 +17920,10 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>29</v>
@@ -17984,10 +17987,10 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>29</v>
@@ -18051,10 +18054,10 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>29</v>
@@ -18063,7 +18066,7 @@
         <v>30</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F208" s="5" t="n">
         <v>133.7</v>
@@ -18118,10 +18121,10 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>29</v>
@@ -18130,7 +18133,7 @@
         <v>30</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F209" s="5" t="n">
         <v>45.78</v>
@@ -18183,10 +18186,10 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>29</v>
@@ -18213,7 +18216,7 @@
         <v>32</v>
       </c>
       <c r="K210" s="4" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="L210" s="4" t="s">
         <v>34</v>
@@ -18250,10 +18253,10 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>29</v>
@@ -18317,10 +18320,10 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>29</v>
@@ -18384,10 +18387,10 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>29</v>
@@ -18451,10 +18454,10 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>60</v>
@@ -18504,10 +18507,10 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>29</v>
@@ -18571,10 +18574,10 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>29</v>
@@ -18635,15 +18638,15 @@
         <v>1</v>
       </c>
       <c r="U216" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>29</v>
@@ -18707,10 +18710,10 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>29</v>
@@ -18719,7 +18722,7 @@
         <v>30</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F218" s="5" t="n">
         <v>117.2</v>
@@ -18774,10 +18777,10 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>29</v>
@@ -18786,7 +18789,7 @@
         <v>30</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F219" s="5" t="n">
         <v>35.9</v>
@@ -18841,10 +18844,10 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>29</v>
@@ -18853,7 +18856,7 @@
         <v>30</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F220" s="5" t="n">
         <v>37.16</v>
@@ -18908,10 +18911,10 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C221" s="4" t="s">
         <v>29</v>
@@ -18975,10 +18978,10 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>29</v>
@@ -18987,7 +18990,7 @@
         <v>30</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F222" s="5" t="n">
         <v>14.71</v>
@@ -19042,10 +19045,10 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>29</v>
@@ -19109,10 +19112,10 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>29</v>
@@ -19176,10 +19179,10 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C225" s="4" t="s">
         <v>29</v>
@@ -19188,7 +19191,7 @@
         <v>30</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F225" s="5" t="n">
         <v>7.48</v>
@@ -19243,10 +19246,10 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>29</v>
@@ -19295,15 +19298,15 @@
         <v>1</v>
       </c>
       <c r="U226" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>29</v>
@@ -19367,10 +19370,10 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>29</v>
@@ -19419,15 +19422,15 @@
         <v>1</v>
       </c>
       <c r="U228" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>29</v>
@@ -19491,10 +19494,10 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>29</v>
@@ -19558,10 +19561,10 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>38</v>
@@ -19610,15 +19613,15 @@
         <v>1</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>38</v>
@@ -19670,10 +19673,10 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>29</v>
@@ -19737,10 +19740,10 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>29</v>
@@ -19749,7 +19752,7 @@
         <v>30</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F234" s="5" t="n">
         <v>2.42</v>
@@ -19802,10 +19805,10 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>29</v>
@@ -19869,10 +19872,10 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>29</v>
@@ -19881,7 +19884,7 @@
         <v>30</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F236" s="5" t="n">
         <v>270.25</v>
@@ -19936,10 +19939,10 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>29</v>
@@ -20003,10 +20006,10 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>29</v>
@@ -20015,7 +20018,7 @@
         <v>30</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F238" s="5" t="n">
         <v>0.98</v>
@@ -20070,10 +20073,10 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>29</v>
@@ -20137,10 +20140,10 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>29</v>
@@ -20201,15 +20204,15 @@
         <v>1</v>
       </c>
       <c r="U240" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>29</v>
@@ -20271,10 +20274,10 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>29</v>
@@ -20338,10 +20341,10 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>38</v>
@@ -20393,10 +20396,10 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>60</v>
@@ -20448,10 +20451,10 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>60</v>
@@ -20503,10 +20506,10 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>29</v>
@@ -20570,10 +20573,10 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>25</v>
@@ -20625,10 +20628,10 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>29</v>
@@ -20637,7 +20640,7 @@
         <v>30</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F248" s="5" t="n">
         <v>22.7</v>
@@ -20692,10 +20695,10 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>29</v>
@@ -20722,7 +20725,7 @@
         <v>32</v>
       </c>
       <c r="K249" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L249" s="4" t="s">
         <v>34</v>
@@ -20733,7 +20736,7 @@
       </c>
       <c r="N249" s="4" t="str">
         <f aca="false">IF(I249="",IF(K249="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I249&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K249="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O249" s="9" t="n">
         <f aca="false">IF(Q249="","",F249*R249/Q249-1)</f>
@@ -20759,10 +20762,10 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>29</v>
@@ -20824,10 +20827,10 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>29</v>
@@ -20836,7 +20839,7 @@
         <v>30</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F251" s="5" t="n">
         <v>4.33</v>
@@ -20891,10 +20894,10 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>29</v>
@@ -20903,13 +20906,13 @@
         <v>30</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F252" s="5" t="n">
         <v>19.69</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H252" s="6" t="n">
         <v>7334.04056693</v>
@@ -20958,10 +20961,10 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>29</v>
@@ -21025,10 +21028,10 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>29</v>
@@ -21055,7 +21058,7 @@
         <v>32</v>
       </c>
       <c r="K254" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L254" s="4" t="s">
         <v>57</v>
@@ -21066,7 +21069,7 @@
       </c>
       <c r="N254" s="4" t="str">
         <f aca="false">IF(I254="",IF(K254="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I254&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K254="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O254" s="9" t="n">
         <f aca="false">IF(Q254="","",F254*R254/Q254-1)</f>
@@ -21092,10 +21095,10 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>25</v>
@@ -21147,10 +21150,10 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>60</v>
@@ -21202,10 +21205,10 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>29</v>
@@ -21269,10 +21272,10 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>25</v>
@@ -21324,10 +21327,10 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>29</v>
@@ -21391,10 +21394,10 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>29</v>
@@ -21403,7 +21406,7 @@
         <v>30</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F260" s="5" t="n">
         <v>43.86</v>
@@ -21458,10 +21461,10 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>29</v>
@@ -21488,7 +21491,7 @@
         <v>32</v>
       </c>
       <c r="K261" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L261" s="4" t="s">
         <v>34</v>
@@ -21499,7 +21502,7 @@
       </c>
       <c r="N261" s="4" t="str">
         <f aca="false">IF(I261="",IF(K261="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I261&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K261="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O261" s="9" t="n">
         <f aca="false">IF(Q261="","",F261*R261/Q261-1)</f>
@@ -21525,10 +21528,10 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>29</v>
@@ -21588,10 +21591,10 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>29</v>
@@ -21655,10 +21658,10 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>29</v>
@@ -21667,7 +21670,7 @@
         <v>30</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F264" s="5" t="n">
         <v>2.18</v>
@@ -21719,15 +21722,15 @@
         <v>1</v>
       </c>
       <c r="U264" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>38</v>
@@ -21779,10 +21782,10 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>29</v>
@@ -21834,10 +21837,10 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>29</v>
@@ -21846,7 +21849,7 @@
         <v>30</v>
       </c>
       <c r="E267" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F267" s="5" t="n">
         <v>272.25</v>
@@ -21901,10 +21904,10 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>29</v>
@@ -21968,10 +21971,10 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>29</v>
@@ -21980,7 +21983,7 @@
         <v>30</v>
       </c>
       <c r="E269" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F269" s="5" t="n">
         <v>11.78</v>
@@ -22035,10 +22038,10 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>29</v>
@@ -22047,7 +22050,7 @@
         <v>30</v>
       </c>
       <c r="E270" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F270" s="5" t="n">
         <v>4.07</v>
@@ -22102,10 +22105,10 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>29</v>
@@ -22114,7 +22117,7 @@
         <v>30</v>
       </c>
       <c r="E271" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F271" s="5" t="n">
         <v>0.8</v>
@@ -22167,10 +22170,10 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>29</v>
@@ -22234,10 +22237,10 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>29</v>
@@ -22252,7 +22255,7 @@
         <v>151.7</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H273" s="6" t="n">
         <v>5916.3</v>
@@ -22301,10 +22304,10 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>29</v>
@@ -22368,10 +22371,10 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>29</v>
@@ -22380,7 +22383,7 @@
         <v>30</v>
       </c>
       <c r="E275" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F275" s="5" t="n">
         <v>30.66</v>
@@ -22435,10 +22438,10 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>60</v>
@@ -22490,10 +22493,10 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>29</v>
@@ -22557,10 +22560,10 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>29</v>
@@ -22624,10 +22627,10 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>38</v>
@@ -22679,10 +22682,10 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>25</v>
@@ -22731,15 +22734,15 @@
         <v>1</v>
       </c>
       <c r="U280" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C281" s="4" t="s">
         <v>29</v>
@@ -22803,10 +22806,10 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>29</v>
@@ -22815,7 +22818,7 @@
         <v>30</v>
       </c>
       <c r="E282" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F282" s="5" t="n">
         <v>11.66</v>
@@ -22870,10 +22873,10 @@
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>38</v>
@@ -22884,7 +22887,7 @@
         <v>4.22</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H283" s="6" t="n">
         <v>16204.8</v>
@@ -22925,10 +22928,10 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>29</v>
@@ -22937,7 +22940,7 @@
         <v>30</v>
       </c>
       <c r="E284" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F284" s="5" t="n">
         <v>44.24</v>
@@ -22992,10 +22995,10 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>29</v>
@@ -23056,15 +23059,15 @@
         <v>1</v>
       </c>
       <c r="U285" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>29</v>
@@ -23128,10 +23131,10 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>38</v>
@@ -23183,10 +23186,10 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>29</v>
@@ -23250,10 +23253,10 @@
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>29</v>
@@ -23317,10 +23320,10 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>60</v>
@@ -23372,10 +23375,10 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>38</v>
@@ -23386,7 +23389,7 @@
         <v>1.24</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H291" s="6" t="n">
         <v>430.9</v>
@@ -23427,10 +23430,10 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>38</v>
@@ -23441,7 +23444,7 @@
         <v>2.11</v>
       </c>
       <c r="G292" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H292" s="6" t="n">
         <v>316.5</v>
@@ -23482,10 +23485,10 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>29</v>
@@ -23500,7 +23503,7 @@
         <v>47.58</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H293" s="6" t="n">
         <v>25864.28497614</v>
@@ -23549,10 +23552,10 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>29</v>
@@ -23616,10 +23619,10 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>29</v>
@@ -23634,7 +23637,7 @@
         <v>1.64</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H295" s="6" t="n">
         <v>574.82</v>
@@ -23683,10 +23686,10 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>29</v>
@@ -23750,10 +23753,10 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>29</v>
@@ -23814,15 +23817,15 @@
         <v>1</v>
       </c>
       <c r="U297" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>29</v>
@@ -23874,10 +23877,10 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>29</v>
@@ -23941,10 +23944,10 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>29</v>
@@ -23953,7 +23956,7 @@
         <v>30</v>
       </c>
       <c r="E300" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F300" s="5" t="n">
         <v>1.61</v>
@@ -24008,10 +24011,10 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>29</v>
@@ -24075,10 +24078,10 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>25</v>
@@ -24127,15 +24130,15 @@
         <v>1</v>
       </c>
       <c r="U302" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>29</v>
@@ -24199,10 +24202,10 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>29</v>
@@ -24266,10 +24269,10 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>29</v>
@@ -24278,13 +24281,13 @@
         <v>30</v>
       </c>
       <c r="E305" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F305" s="5" t="n">
         <v>198.5</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H305" s="6" t="n">
         <v>3858.84</v>
@@ -24333,10 +24336,10 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>29</v>
@@ -24396,10 +24399,10 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>25</v>
@@ -24451,10 +24454,10 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>29</v>
@@ -24518,10 +24521,10 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>60</v>
@@ -24532,7 +24535,7 @@
         <v>4949952.5</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H309" s="6" t="n">
         <v>123748812500</v>
@@ -24571,10 +24574,10 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>29</v>
@@ -24638,10 +24641,10 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>60</v>
@@ -24652,7 +24655,7 @@
         <v>425000</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H311" s="6" t="n">
         <v>10625000000</v>
@@ -24693,10 +24696,10 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>60</v>
@@ -24748,10 +24751,10 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>29</v>
@@ -24760,7 +24763,7 @@
         <v>30</v>
       </c>
       <c r="E313" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F313" s="5" t="n">
         <v>62.45</v>
@@ -24815,10 +24818,10 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>60</v>
@@ -24870,10 +24873,10 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>38</v>
@@ -24922,15 +24925,15 @@
         <v>1</v>
       </c>
       <c r="U315" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>38</v>
@@ -24982,10 +24985,10 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>29</v>
@@ -25049,10 +25052,10 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>60</v>
@@ -25063,7 +25066,7 @@
         <v>4125000</v>
       </c>
       <c r="G318" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H318" s="6" t="n">
         <v>103125000000</v>
@@ -25102,10 +25105,10 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>25</v>
@@ -25157,10 +25160,10 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>29</v>
@@ -25224,10 +25227,10 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>29</v>
@@ -25236,7 +25239,7 @@
         <v>30</v>
       </c>
       <c r="E321" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F321" s="5" t="n">
         <v>24.54</v>
@@ -25287,10 +25290,10 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>29</v>
@@ -25342,10 +25345,10 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>29</v>
@@ -25409,10 +25412,10 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>29</v>
@@ -25476,10 +25479,10 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>29</v>
@@ -25494,7 +25497,7 @@
         <v>31.12</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H325" s="6" t="n">
         <v>544.98763072</v>
@@ -25543,10 +25546,10 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>29</v>
@@ -25555,7 +25558,7 @@
         <v>30</v>
       </c>
       <c r="E326" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F326" s="5" t="n">
         <v>6.73</v>
@@ -25610,10 +25613,10 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>29</v>
@@ -25622,7 +25625,7 @@
         <v>30</v>
       </c>
       <c r="E327" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F327" s="5" t="n">
         <v>13.39</v>
@@ -25677,10 +25680,10 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>29</v>
@@ -25689,7 +25692,7 @@
         <v>30</v>
       </c>
       <c r="E328" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F328" s="5" t="n">
         <v>141.3</v>
@@ -25744,10 +25747,10 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>29</v>
@@ -25756,7 +25759,7 @@
         <v>30</v>
       </c>
       <c r="E329" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F329" s="5" t="n">
         <v>48.2</v>
@@ -25774,7 +25777,7 @@
         <v>32</v>
       </c>
       <c r="K329" s="4" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="L329" s="4" t="s">
         <v>42</v>
@@ -25809,10 +25812,10 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>29</v>
@@ -25827,7 +25830,7 @@
         <v>6.21</v>
       </c>
       <c r="G330" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H330" s="6" t="n">
         <v>5004.5491413</v>
@@ -25876,10 +25879,10 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>29</v>
@@ -25943,10 +25946,10 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>29</v>
@@ -25955,13 +25958,13 @@
         <v>30</v>
       </c>
       <c r="E332" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F332" s="5" t="n">
         <v>91.3</v>
       </c>
       <c r="G332" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H332" s="6" t="n">
         <v>6847.5</v>
@@ -26010,10 +26013,10 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>29</v>
@@ -26022,7 +26025,7 @@
         <v>30</v>
       </c>
       <c r="E333" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F333" s="5" t="n">
         <v>1.53</v>
@@ -26077,10 +26080,10 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>29</v>
@@ -26142,10 +26145,10 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>29</v>
@@ -26154,7 +26157,7 @@
         <v>30</v>
       </c>
       <c r="E335" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F335" s="5" t="n">
         <v>12.09</v>
@@ -26209,10 +26212,10 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>29</v>
@@ -26221,7 +26224,7 @@
         <v>30</v>
       </c>
       <c r="E336" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F336" s="5" t="n">
         <v>10.35</v>
@@ -26276,10 +26279,10 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>29</v>
@@ -26306,7 +26309,7 @@
         <v>111</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L337" s="4" t="s">
         <v>34</v>
@@ -26343,10 +26346,10 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>29</v>
@@ -26410,10 +26413,10 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>29</v>
@@ -26477,10 +26480,10 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>29</v>
@@ -26544,10 +26547,10 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>38</v>
@@ -26599,10 +26602,10 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>29</v>
@@ -26611,13 +26614,13 @@
         <v>30</v>
       </c>
       <c r="E342" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F342" s="5" t="n">
         <v>10.83</v>
       </c>
       <c r="G342" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H342" s="6" t="n">
         <v>2599.2</v>
@@ -26666,10 +26669,10 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>38</v>
@@ -26721,10 +26724,10 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>29</v>
@@ -26788,10 +26791,10 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>29</v>
@@ -26855,10 +26858,10 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>60</v>
@@ -26910,10 +26913,10 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>29</v>
@@ -26974,15 +26977,15 @@
         <v>1.99964507542147</v>
       </c>
       <c r="U347" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>29</v>
@@ -26991,7 +26994,7 @@
         <v>30</v>
       </c>
       <c r="E348" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F348" s="5" t="n">
         <v>19.1</v>
@@ -27046,10 +27049,10 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>29</v>
@@ -27058,7 +27061,7 @@
         <v>30</v>
       </c>
       <c r="E349" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F349" s="5" t="n">
         <v>14.24</v>
@@ -27113,10 +27116,10 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>29</v>
@@ -27180,10 +27183,10 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>29</v>
@@ -27247,10 +27250,10 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>29</v>
@@ -27314,10 +27317,10 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>29</v>
@@ -27326,7 +27329,7 @@
         <v>30</v>
       </c>
       <c r="E353" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F353" s="5" t="n">
         <v>2.9</v>
@@ -27381,10 +27384,10 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>29</v>
@@ -27448,10 +27451,10 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>29</v>
@@ -27515,10 +27518,10 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>29</v>
@@ -27582,10 +27585,10 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>29</v>
@@ -27649,10 +27652,10 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>29</v>
@@ -27713,15 +27716,15 @@
         <v>1</v>
       </c>
       <c r="U358" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>29</v>
@@ -27730,7 +27733,7 @@
         <v>30</v>
       </c>
       <c r="E359" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F359" s="5" t="n">
         <v>9.94</v>
@@ -27785,10 +27788,10 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>29</v>
@@ -27848,10 +27851,10 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>29</v>
@@ -27860,7 +27863,7 @@
         <v>30</v>
       </c>
       <c r="E361" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F361" s="5" t="n">
         <v>41.04</v>
@@ -27915,11 +27918,11 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="B362" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="B362" s="4" t="s">
-        <v>822</v>
-      </c>
       <c r="C362" s="4" t="s">
         <v>29</v>
       </c>
@@ -27927,7 +27930,7 @@
         <v>30</v>
       </c>
       <c r="E362" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F362" s="5" t="n">
         <v>76.1</v>
@@ -27982,10 +27985,10 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="4" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>29</v>
@@ -27994,7 +27997,7 @@
         <v>30</v>
       </c>
       <c r="E363" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F363" s="5" t="n">
         <v>44.36</v>
@@ -28049,10 +28052,10 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="4" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>38</v>
@@ -28104,10 +28107,10 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>29</v>
@@ -28171,10 +28174,10 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>29</v>
@@ -28183,7 +28186,7 @@
         <v>30</v>
       </c>
       <c r="E366" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F366" s="5" t="n">
         <v>11.63</v>
@@ -28238,10 +28241,10 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>29</v>
@@ -28305,10 +28308,10 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>29</v>
@@ -28369,15 +28372,15 @@
         <v>1</v>
       </c>
       <c r="U368" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>29</v>
@@ -28441,10 +28444,10 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>29</v>
@@ -28453,7 +28456,7 @@
         <v>30</v>
       </c>
       <c r="E370" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F370" s="5" t="n">
         <v>1997</v>
@@ -28508,10 +28511,10 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="4" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>60</v>
@@ -28560,15 +28563,15 @@
         <v>1</v>
       </c>
       <c r="U371" s="4" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="4" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>29</v>
@@ -28632,10 +28635,10 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="4" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C373" s="4" t="s">
         <v>29</v>
@@ -28644,7 +28647,7 @@
         <v>30</v>
       </c>
       <c r="E373" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F373" s="5" t="n">
         <v>67</v>
@@ -28699,10 +28702,10 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>29</v>
@@ -28717,7 +28720,7 @@
         <v>79.25</v>
       </c>
       <c r="G374" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H374" s="6" t="n">
         <v>2460.07905475</v>
@@ -28766,10 +28769,10 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="4" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>29</v>
@@ -28821,10 +28824,10 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>38</v>
@@ -28876,10 +28879,10 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>38</v>
@@ -28931,10 +28934,10 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>29</v>
@@ -28943,7 +28946,7 @@
         <v>30</v>
       </c>
       <c r="E378" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F378" s="5" t="n">
         <v>7.99</v>
@@ -28998,10 +29001,10 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>60</v>
@@ -29050,15 +29053,15 @@
         <v>1</v>
       </c>
       <c r="U379" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>29</v>
@@ -29122,10 +29125,10 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>29</v>
@@ -29189,10 +29192,10 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>29</v>
@@ -29256,10 +29259,10 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="4" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C383" s="4" t="s">
         <v>29</v>
@@ -29323,10 +29326,10 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>29</v>
@@ -29390,10 +29393,10 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="4" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>29</v>
@@ -29457,10 +29460,10 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="4" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C386" s="4" t="s">
         <v>29</v>
@@ -29524,10 +29527,10 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C387" s="4" t="s">
         <v>38</v>
@@ -29577,10 +29580,10 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>29</v>
@@ -29589,7 +29592,7 @@
         <v>30</v>
       </c>
       <c r="E388" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F388" s="5" t="n">
         <v>47.2</v>
@@ -29644,10 +29647,10 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>29</v>
@@ -29711,10 +29714,10 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>29</v>
@@ -29723,7 +29726,7 @@
         <v>30</v>
       </c>
       <c r="E390" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F390" s="5" t="n">
         <v>848</v>
@@ -29778,10 +29781,10 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>29</v>
@@ -29845,10 +29848,10 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="4" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>29</v>
@@ -29912,10 +29915,10 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>29</v>
@@ -29924,7 +29927,7 @@
         <v>30</v>
       </c>
       <c r="E393" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F393" s="5" t="n">
         <v>13.93</v>
@@ -29979,10 +29982,10 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C394" s="4" t="s">
         <v>29</v>
@@ -29991,7 +29994,7 @@
         <v>30</v>
       </c>
       <c r="E394" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F394" s="5" t="n">
         <v>6.75</v>
@@ -30046,10 +30049,10 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C395" s="4" t="s">
         <v>29</v>
@@ -30113,10 +30116,10 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>29</v>
@@ -30180,10 +30183,10 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="4" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>29</v>
@@ -30247,10 +30250,10 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>29</v>
@@ -30259,7 +30262,7 @@
         <v>30</v>
       </c>
       <c r="E398" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F398" s="5" t="n">
         <v>1.4</v>
@@ -30314,10 +30317,10 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>25</v>
@@ -30367,10 +30370,10 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="4" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>29</v>
@@ -30434,10 +30437,10 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>29</v>
@@ -30497,10 +30500,10 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="4" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>29</v>
@@ -30564,10 +30567,10 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>29</v>
@@ -30629,10 +30632,10 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>29</v>
@@ -30641,7 +30644,7 @@
         <v>30</v>
       </c>
       <c r="E404" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F404" s="5" t="n">
         <v>3.93</v>
@@ -30693,15 +30696,15 @@
         <v>1</v>
       </c>
       <c r="U404" s="4" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>29</v>
@@ -30765,10 +30768,10 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>29</v>
@@ -30832,10 +30835,10 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="4" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>29</v>
@@ -30899,10 +30902,10 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="4" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C408" s="4" t="s">
         <v>29</v>
@@ -30911,7 +30914,7 @@
         <v>30</v>
       </c>
       <c r="E408" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F408" s="5" t="n">
         <v>14.04</v>
@@ -30966,10 +30969,10 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C409" s="4" t="s">
         <v>29</v>
@@ -31030,15 +31033,15 @@
         <v>1</v>
       </c>
       <c r="U409" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>29</v>
@@ -31100,10 +31103,10 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C411" s="4" t="s">
         <v>29</v>
@@ -31167,10 +31170,10 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C412" s="4" t="s">
         <v>29</v>
@@ -31232,10 +31235,10 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>29</v>
@@ -31244,7 +31247,7 @@
         <v>30</v>
       </c>
       <c r="E413" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F413" s="5" t="n">
         <v>512</v>
@@ -31299,10 +31302,10 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>38</v>
@@ -31351,15 +31354,15 @@
         <v>1</v>
       </c>
       <c r="U414" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="4" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C415" s="4" t="s">
         <v>29</v>
@@ -31423,10 +31426,10 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="4" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>29</v>
@@ -31490,10 +31493,10 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="4" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>29</v>
@@ -31557,10 +31560,10 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="4" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>29</v>
@@ -31569,13 +31572,13 @@
         <v>30</v>
       </c>
       <c r="E418" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F418" s="5" t="n">
         <v>4.13</v>
       </c>
       <c r="G418" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H418" s="6" t="n">
         <v>4332.53852465</v>
@@ -31624,10 +31627,10 @@
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>29</v>
@@ -31642,7 +31645,7 @@
         <v>10.23</v>
       </c>
       <c r="G419" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H419" s="6" t="n">
         <v>10485.75</v>
@@ -31691,10 +31694,10 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>29</v>
@@ -31758,10 +31761,10 @@
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="4" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>29</v>
@@ -31770,7 +31773,7 @@
         <v>30</v>
       </c>
       <c r="E421" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F421" s="5" t="n">
         <v>18.73</v>
@@ -31825,10 +31828,10 @@
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>29</v>
@@ -31892,10 +31895,10 @@
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>38</v>
@@ -31947,10 +31950,10 @@
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>29</v>
@@ -32014,10 +32017,10 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="4" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>38</v>
@@ -32028,7 +32031,7 @@
         <v>5.03</v>
       </c>
       <c r="G425" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H425" s="6" t="n">
         <v>2362.93363354</v>
@@ -32069,10 +32072,10 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>29</v>
@@ -32136,10 +32139,10 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>29</v>
@@ -32191,10 +32194,10 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="4" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>29</v>
@@ -32209,7 +32212,7 @@
         <v>4.23</v>
       </c>
       <c r="G428" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H428" s="6" t="n">
         <v>459.20457</v>
@@ -32258,10 +32261,10 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>29</v>
@@ -32325,10 +32328,10 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="4" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>29</v>
@@ -32392,10 +32395,10 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>29</v>
@@ -32457,11 +32460,11 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B432" s="4"/>
       <c r="C432" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>30</v>
@@ -32518,10 +32521,10 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>29</v>
@@ -32585,10 +32588,10 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>29</v>
@@ -32652,10 +32655,10 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>29</v>
@@ -32719,10 +32722,10 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>38</v>
@@ -32774,10 +32777,10 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C437" s="4" t="s">
         <v>29</v>
@@ -32838,15 +32841,15 @@
         <v>1</v>
       </c>
       <c r="U437" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>29</v>
@@ -32910,10 +32913,10 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>29</v>
@@ -32977,10 +32980,10 @@
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>29</v>
@@ -33044,10 +33047,10 @@
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>29</v>
@@ -33111,10 +33114,10 @@
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>29</v>
@@ -33178,10 +33181,10 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>29</v>
@@ -33245,10 +33248,10 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="4" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C444" s="4" t="s">
         <v>29</v>
@@ -33309,15 +33312,15 @@
         <v>1</v>
       </c>
       <c r="U444" s="4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>29</v>
@@ -33381,10 +33384,10 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="4" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>29</v>
@@ -33445,15 +33448,15 @@
         <v>1</v>
       </c>
       <c r="U446" s="4" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="4" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C447" s="4" t="s">
         <v>29</v>
@@ -33462,7 +33465,7 @@
         <v>30</v>
       </c>
       <c r="E447" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F447" s="5" t="n">
         <v>136</v>
@@ -33517,10 +33520,10 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="4" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C448" s="4" t="s">
         <v>29</v>
@@ -33580,10 +33583,10 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="4" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>25</v>
@@ -33635,10 +33638,10 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="4" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>29</v>
@@ -33699,15 +33702,15 @@
         <v>1</v>
       </c>
       <c r="U450" s="4" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="4" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>29</v>
@@ -33771,10 +33774,10 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="4" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>29</v>
@@ -33838,10 +33841,10 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C453" s="4" t="s">
         <v>29</v>
@@ -33868,7 +33871,7 @@
         <v>32</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L453" s="4" t="s">
         <v>34</v>
@@ -33879,7 +33882,7 @@
       </c>
       <c r="N453" s="4" t="str">
         <f aca="false">IF(I453="",IF(K453="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I453&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K453="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O453" s="9" t="n">
         <f aca="false">IF(Q453="","",F453*R453/Q453-1)</f>
@@ -33905,10 +33908,10 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>29</v>
@@ -33960,10 +33963,10 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="4" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>29</v>
@@ -33978,7 +33981,7 @@
         <v>6.75</v>
       </c>
       <c r="G455" s="4" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H455" s="6" t="n">
         <v>573.75</v>
@@ -34027,10 +34030,10 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="4" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>25</v>
@@ -34082,10 +34085,10 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="4" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>29</v>
@@ -34149,10 +34152,10 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="4" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>38</v>
@@ -34204,10 +34207,10 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="4" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>38</v>
@@ -34259,10 +34262,10 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C460" s="4" t="s">
         <v>29</v>
@@ -34326,10 +34329,10 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="4" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C461" s="4" t="s">
         <v>29</v>
@@ -34338,7 +34341,7 @@
         <v>30</v>
       </c>
       <c r="E461" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F461" s="5" t="n">
         <v>37.14</v>
@@ -34393,10 +34396,10 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="4" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C462" s="4" t="s">
         <v>29</v>
@@ -34405,7 +34408,7 @@
         <v>30</v>
       </c>
       <c r="E462" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F462" s="5" t="n">
         <v>11.71</v>
@@ -34457,15 +34460,15 @@
         <v>1</v>
       </c>
       <c r="U462" s="4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C463" s="4" t="s">
         <v>38</v>
@@ -34517,10 +34520,10 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C464" s="4" t="s">
         <v>29</v>
@@ -34582,10 +34585,10 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="4" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C465" s="4" t="s">
         <v>29</v>
@@ -34649,10 +34652,10 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C466" s="4" t="s">
         <v>29</v>
@@ -34716,10 +34719,10 @@
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C467" s="4" t="s">
         <v>29</v>
@@ -34728,7 +34731,7 @@
         <v>30</v>
       </c>
       <c r="E467" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F467" s="5" t="n">
         <v>60.55</v>
@@ -34783,10 +34786,10 @@
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C468" s="4" t="s">
         <v>29</v>
@@ -34795,7 +34798,7 @@
         <v>30</v>
       </c>
       <c r="E468" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F468" s="5" t="n">
         <v>41.4</v>
@@ -34850,10 +34853,10 @@
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="4" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C469" s="4" t="s">
         <v>29</v>
@@ -34917,10 +34920,10 @@
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C470" s="4" t="s">
         <v>29</v>
@@ -34984,10 +34987,10 @@
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="4" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C471" s="4" t="s">
         <v>38</v>
@@ -35039,10 +35042,10 @@
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>29</v>
@@ -35106,10 +35109,10 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="4" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C473" s="4" t="s">
         <v>29</v>
@@ -35173,10 +35176,10 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="4" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C474" s="4" t="s">
         <v>29</v>
@@ -35240,10 +35243,10 @@
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="4" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C475" s="4" t="s">
         <v>29</v>
@@ -35307,10 +35310,10 @@
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C476" s="4" t="s">
         <v>29</v>
@@ -35319,7 +35322,7 @@
         <v>30</v>
       </c>
       <c r="E476" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F476" s="5" t="n">
         <v>141.4</v>
@@ -35374,10 +35377,10 @@
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="4" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C477" s="4" t="s">
         <v>29</v>
@@ -35441,10 +35444,10 @@
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="4" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C478" s="4" t="s">
         <v>29</v>
@@ -35508,10 +35511,10 @@
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="4" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C479" s="4" t="s">
         <v>29</v>
@@ -35520,7 +35523,7 @@
         <v>30</v>
       </c>
       <c r="E479" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F479" s="5" t="n">
         <v>99.6</v>
@@ -35575,10 +35578,10 @@
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C480" s="4" t="s">
         <v>29</v>
@@ -35587,7 +35590,7 @@
         <v>30</v>
       </c>
       <c r="E480" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F480" s="5" t="n">
         <v>15.48</v>
@@ -35642,10 +35645,10 @@
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C481" s="4" t="s">
         <v>29</v>
@@ -35672,7 +35675,7 @@
         <v>32</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L481" s="4" t="s">
         <v>34</v>
@@ -35709,10 +35712,10 @@
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="4" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>29</v>
@@ -35776,10 +35779,10 @@
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="4" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>29</v>
@@ -35843,10 +35846,10 @@
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="4" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C484" s="4" t="s">
         <v>29</v>
@@ -35855,7 +35858,7 @@
         <v>30</v>
       </c>
       <c r="E484" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F484" s="5" t="n">
         <v>3000</v>
@@ -35910,10 +35913,10 @@
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="4" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>38</v>
@@ -35965,10 +35968,10 @@
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="4" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>29</v>
@@ -35977,7 +35980,7 @@
         <v>30</v>
       </c>
       <c r="E486" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F486" s="5" t="n">
         <v>24.56</v>
@@ -36032,10 +36035,10 @@
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="4" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>29</v>
@@ -36099,10 +36102,10 @@
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="4" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>29</v>
@@ -36166,10 +36169,10 @@
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C489" s="4" t="s">
         <v>29</v>
@@ -36178,7 +36181,7 @@
         <v>30</v>
       </c>
       <c r="E489" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F489" s="5" t="n">
         <v>93.5</v>
@@ -36233,10 +36236,10 @@
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C490" s="4" t="s">
         <v>38</v>
@@ -36288,10 +36291,10 @@
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="4" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C491" s="4" t="s">
         <v>60</v>
@@ -36343,10 +36346,10 @@
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="4" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C492" s="4" t="s">
         <v>60</v>
@@ -36398,10 +36401,10 @@
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="4" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C493" s="4" t="s">
         <v>29</v>
@@ -36410,7 +36413,7 @@
         <v>30</v>
       </c>
       <c r="E493" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F493" s="5" t="n">
         <v>2</v>
@@ -36428,7 +36431,7 @@
         <v>32</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="L493" s="4" t="s">
         <v>34</v>
@@ -36465,10 +36468,10 @@
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C494" s="4" t="s">
         <v>60</v>
@@ -36518,10 +36521,10 @@
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="4" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B495" s="4" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C495" s="4" t="s">
         <v>25</v>
@@ -36573,10 +36576,10 @@
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C496" s="4" t="s">
         <v>60</v>
@@ -36628,10 +36631,10 @@
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C497" s="4" t="s">
         <v>29</v>
@@ -36695,10 +36698,10 @@
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C498" s="4" t="s">
         <v>29</v>
@@ -36750,10 +36753,10 @@
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C499" s="4" t="s">
         <v>29</v>
@@ -36817,10 +36820,10 @@
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="4" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C500" s="4" t="s">
         <v>29</v>
@@ -36884,10 +36887,10 @@
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="4" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C501" s="4" t="s">
         <v>29</v>
@@ -36951,10 +36954,10 @@
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C502" s="4" t="s">
         <v>29</v>
@@ -37018,10 +37021,10 @@
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B503" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C503" s="4" t="s">
         <v>29</v>
@@ -37030,7 +37033,7 @@
         <v>30</v>
       </c>
       <c r="E503" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F503" s="5" t="n">
         <v>4.85</v>
@@ -37085,10 +37088,10 @@
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C504" s="4" t="s">
         <v>38</v>
@@ -37140,10 +37143,10 @@
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C505" s="4" t="s">
         <v>29</v>
@@ -37152,7 +37155,7 @@
         <v>30</v>
       </c>
       <c r="E505" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F505" s="5" t="n">
         <v>25.46</v>
@@ -37207,10 +37210,10 @@
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C506" s="4" t="s">
         <v>29</v>
@@ -37219,7 +37222,7 @@
         <v>30</v>
       </c>
       <c r="E506" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F506" s="5" t="n">
         <v>14.34</v>
@@ -37274,10 +37277,10 @@
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C507" s="4" t="s">
         <v>29</v>
@@ -37304,7 +37307,7 @@
         <v>111</v>
       </c>
       <c r="K507" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L507" s="4" t="s">
         <v>34</v>
@@ -37341,10 +37344,10 @@
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="4" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C508" s="4" t="s">
         <v>29</v>
@@ -37359,7 +37362,7 @@
         <v>3.95</v>
       </c>
       <c r="G508" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H508" s="6" t="n">
         <v>443.98</v>
@@ -37408,10 +37411,10 @@
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="4" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C509" s="4" t="s">
         <v>29</v>
@@ -37475,10 +37478,10 @@
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="4" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B510" s="4" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C510" s="4" t="s">
         <v>29</v>
@@ -37542,10 +37545,10 @@
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="4" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B511" s="4" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C511" s="4" t="s">
         <v>29</v>
@@ -37609,10 +37612,10 @@
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="4" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B512" s="4" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C512" s="4" t="s">
         <v>29</v>
@@ -37672,10 +37675,10 @@
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="4" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B513" s="4" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C513" s="4" t="s">
         <v>29</v>
@@ -37684,7 +37687,7 @@
         <v>30</v>
       </c>
       <c r="E513" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F513" s="5" t="n">
         <v>21.2</v>
@@ -37739,10 +37742,10 @@
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="4" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C514" s="4" t="s">
         <v>29</v>
@@ -37806,10 +37809,10 @@
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="4" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C515" s="4" t="s">
         <v>29</v>
@@ -37836,7 +37839,7 @@
         <v>32</v>
       </c>
       <c r="K515" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L515" s="4" t="s">
         <v>34</v>
@@ -37847,7 +37850,7 @@
       </c>
       <c r="N515" s="4" t="str">
         <f aca="false">IF(I515="",IF(K515="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I515&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K515="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O515" s="9" t="n">
         <f aca="false">IF(Q515="","",F515*R515/Q515-1)</f>
@@ -37873,10 +37876,10 @@
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="4" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B516" s="4" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C516" s="4" t="s">
         <v>29</v>
@@ -37937,15 +37940,15 @@
         <v>1</v>
       </c>
       <c r="U516" s="4" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="4" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B517" s="4" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C517" s="4" t="s">
         <v>29</v>
@@ -37960,7 +37963,7 @@
         <v>21.78</v>
       </c>
       <c r="G517" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H517" s="6" t="n">
         <v>3898.62</v>
@@ -38009,10 +38012,10 @@
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="4" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B518" s="4" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C518" s="4" t="s">
         <v>38</v>
@@ -38023,7 +38026,7 @@
         <v>2.81</v>
       </c>
       <c r="G518" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H518" s="6" t="n">
         <v>2286.09034523</v>
@@ -38064,10 +38067,10 @@
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="4" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B519" s="4" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C519" s="4" t="s">
         <v>60</v>
@@ -38116,15 +38119,15 @@
         <v>1</v>
       </c>
       <c r="U519" s="4" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="4" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B520" s="4" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C520" s="4" t="s">
         <v>29</v>
@@ -38133,7 +38136,7 @@
         <v>30</v>
       </c>
       <c r="E520" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F520" s="5" t="n">
         <v>4.02</v>
@@ -38188,10 +38191,10 @@
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="4" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B521" s="4" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C521" s="4" t="s">
         <v>29</v>
@@ -38255,10 +38258,10 @@
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="4" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B522" s="4" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C522" s="4" t="s">
         <v>29</v>
@@ -38322,10 +38325,10 @@
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="4" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B523" s="4" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C523" s="4" t="s">
         <v>29</v>
@@ -38334,7 +38337,7 @@
         <v>30</v>
       </c>
       <c r="E523" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F523" s="5" t="n">
         <v>5.01</v>
@@ -38389,10 +38392,10 @@
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="4" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B524" s="4" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C524" s="4" t="s">
         <v>29</v>
@@ -38456,10 +38459,10 @@
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="4" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C525" s="4" t="s">
         <v>29</v>
@@ -38474,7 +38477,7 @@
         <v>1.68</v>
       </c>
       <c r="G525" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H525" s="6" t="n">
         <v>588</v>
@@ -38523,10 +38526,10 @@
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="4" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C526" s="4" t="s">
         <v>29</v>
@@ -38535,7 +38538,7 @@
         <v>30</v>
       </c>
       <c r="E526" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F526" s="5" t="n">
         <v>38.14</v>
@@ -38590,10 +38593,10 @@
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="4" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B527" s="4" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C527" s="4" t="s">
         <v>60</v>
@@ -38645,10 +38648,10 @@
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="4" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B528" s="4" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C528" s="4" t="s">
         <v>29</v>
@@ -38712,10 +38715,10 @@
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="4" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B529" s="4" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C529" s="4" t="s">
         <v>29</v>
@@ -38779,10 +38782,10 @@
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="4" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B530" s="4" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C530" s="4" t="s">
         <v>25</v>
@@ -38834,10 +38837,10 @@
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="4" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C531" s="4" t="s">
         <v>29</v>
@@ -38901,10 +38904,10 @@
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="4" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B532" s="4" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C532" s="4" t="s">
         <v>29</v>
@@ -38968,10 +38971,10 @@
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="4" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B533" s="4" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C533" s="4" t="s">
         <v>60</v>
@@ -39020,15 +39023,15 @@
         <v>1</v>
       </c>
       <c r="U533" s="4" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="4" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B534" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C534" s="4" t="s">
         <v>38</v>
@@ -39080,10 +39083,10 @@
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="4" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C535" s="4" t="s">
         <v>29</v>
@@ -39092,7 +39095,7 @@
         <v>30</v>
       </c>
       <c r="E535" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F535" s="5" t="n">
         <v>2.28</v>
@@ -39147,10 +39150,10 @@
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="4" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B536" s="4" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C536" s="4" t="s">
         <v>29</v>
@@ -39214,10 +39217,10 @@
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="4" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B537" s="4" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C537" s="4" t="s">
         <v>29</v>
@@ -39281,10 +39284,10 @@
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="4" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C538" s="4" t="s">
         <v>29</v>
@@ -39344,10 +39347,10 @@
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="4" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B539" s="4" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C539" s="4" t="s">
         <v>29</v>
@@ -39411,10 +39414,10 @@
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="4" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B540" s="4" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C540" s="4" t="s">
         <v>29</v>
@@ -39423,7 +39426,7 @@
         <v>30</v>
       </c>
       <c r="E540" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F540" s="5" t="n">
         <v>56.5</v>
@@ -39478,10 +39481,10 @@
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="4" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C541" s="4" t="s">
         <v>29</v>
@@ -39496,7 +39499,7 @@
         <v>123.5</v>
       </c>
       <c r="G541" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H541" s="6" t="n">
         <v>9139</v>
@@ -39508,7 +39511,7 @@
         <v>32</v>
       </c>
       <c r="K541" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L541" s="4" t="s">
         <v>34</v>
@@ -39519,7 +39522,7 @@
       </c>
       <c r="N541" s="4" t="str">
         <f aca="false">IF(I541="",IF(K541="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I541&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K541="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O541" s="9" t="n">
         <f aca="false">IF(Q541="","",F541*R541/Q541-1)</f>
@@ -39545,10 +39548,10 @@
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="4" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C542" s="4" t="s">
         <v>38</v>
@@ -39600,10 +39603,10 @@
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="4" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B543" s="4" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C543" s="4" t="s">
         <v>29</v>
@@ -39612,7 +39615,7 @@
         <v>30</v>
       </c>
       <c r="E543" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F543" s="5" t="n">
         <v>27.06</v>
@@ -39663,10 +39666,10 @@
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="4" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C544" s="4" t="s">
         <v>29</v>
@@ -39675,7 +39678,7 @@
         <v>30</v>
       </c>
       <c r="E544" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F544" s="5" t="n">
         <v>204.9</v>
@@ -39730,10 +39733,10 @@
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="4" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B545" s="4" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C545" s="4" t="s">
         <v>29</v>
@@ -39748,7 +39751,7 @@
         <v>25.46</v>
       </c>
       <c r="G545" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H545" s="6" t="n">
         <v>12083.316</v>
@@ -39760,7 +39763,7 @@
         <v>32</v>
       </c>
       <c r="K545" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L545" s="4" t="s">
         <v>34</v>
@@ -39771,7 +39774,7 @@
       </c>
       <c r="N545" s="4" t="str">
         <f aca="false">IF(I545="",IF(K545="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I545&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K545="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O545" s="9" t="n">
         <f aca="false">IF(Q545="","",F545*R545/Q545-1)</f>
@@ -39797,10 +39800,10 @@
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="4" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B546" s="4" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C546" s="4" t="s">
         <v>38</v>
@@ -39852,10 +39855,10 @@
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="4" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C547" s="4" t="s">
         <v>29</v>
@@ -39919,10 +39922,10 @@
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="4" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C548" s="4" t="s">
         <v>38</v>
@@ -39972,10 +39975,10 @@
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="4" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B549" s="4" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C549" s="4" t="s">
         <v>29</v>
@@ -40039,10 +40042,10 @@
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="4" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B550" s="4" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C550" s="4" t="s">
         <v>29</v>
@@ -40106,10 +40109,10 @@
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="4" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B551" s="4" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C551" s="4" t="s">
         <v>29</v>
@@ -40173,10 +40176,10 @@
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="4" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B552" s="4" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C552" s="4" t="s">
         <v>29</v>
@@ -40240,10 +40243,10 @@
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="4" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B553" s="4" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="C553" s="4" t="s">
         <v>29</v>
@@ -40252,7 +40255,7 @@
         <v>30</v>
       </c>
       <c r="E553" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F553" s="5" t="n">
         <v>278.5</v>
@@ -40307,10 +40310,10 @@
     </row>
     <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="4" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B554" s="4" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C554" s="4" t="s">
         <v>29</v>
@@ -40374,10 +40377,10 @@
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="4" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B555" s="4" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C555" s="4" t="s">
         <v>29</v>
@@ -40441,10 +40444,10 @@
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="4" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B556" s="4" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C556" s="4" t="s">
         <v>29</v>
@@ -40508,10 +40511,10 @@
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="4" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B557" s="4" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C557" s="4" t="s">
         <v>38</v>
@@ -40563,10 +40566,10 @@
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="4" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B558" s="4" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C558" s="4" t="s">
         <v>29</v>
@@ -40581,7 +40584,7 @@
         <v>9.89</v>
       </c>
       <c r="G558" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H558" s="6" t="n">
         <v>19738.8576</v>
@@ -40630,10 +40633,10 @@
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="4" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B559" s="4" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C559" s="4" t="s">
         <v>29</v>
@@ -40642,7 +40645,7 @@
         <v>30</v>
       </c>
       <c r="E559" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F559" s="5" t="n">
         <v>4.42</v>
@@ -40697,10 +40700,10 @@
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="4" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B560" s="4" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C560" s="4" t="s">
         <v>25</v>
@@ -40752,10 +40755,10 @@
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="4" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B561" s="4" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C561" s="4" t="s">
         <v>29</v>
@@ -40782,7 +40785,7 @@
         <v>32</v>
       </c>
       <c r="K561" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L561" s="4" t="s">
         <v>34</v>
@@ -40793,7 +40796,7 @@
       </c>
       <c r="N561" s="4" t="str">
         <f aca="false">IF(I561="",IF(K561="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I561&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K561="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O561" s="9" t="n">
         <f aca="false">IF(Q561="","",F561*R561/Q561-1)</f>
@@ -40819,10 +40822,10 @@
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="4" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B562" s="4" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C562" s="4" t="s">
         <v>29</v>
@@ -40831,7 +40834,7 @@
         <v>30</v>
       </c>
       <c r="E562" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F562" s="5" t="n">
         <v>137</v>
@@ -40886,10 +40889,10 @@
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="4" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B563" s="4" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C563" s="4" t="s">
         <v>29</v>
@@ -40898,7 +40901,7 @@
         <v>30</v>
       </c>
       <c r="E563" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F563" s="5" t="n">
         <v>292.5</v>
@@ -40953,10 +40956,10 @@
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="4" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B564" s="4" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C564" s="4" t="s">
         <v>29</v>
@@ -41020,10 +41023,10 @@
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="4" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B565" s="4" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C565" s="4" t="s">
         <v>29</v>
@@ -41083,10 +41086,10 @@
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="4" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B566" s="4" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C566" s="4" t="s">
         <v>29</v>
@@ -41150,10 +41153,10 @@
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="4" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B567" s="4" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C567" s="4" t="s">
         <v>29</v>
@@ -41162,7 +41165,7 @@
         <v>30</v>
       </c>
       <c r="E567" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F567" s="5" t="n">
         <v>63.95</v>
@@ -41217,10 +41220,10 @@
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="4" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B568" s="4" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C568" s="4" t="s">
         <v>29</v>
@@ -41284,10 +41287,10 @@
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="4" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B569" s="4" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C569" s="4" t="s">
         <v>29</v>
@@ -41351,10 +41354,10 @@
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="4" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B570" s="4" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C570" s="4" t="s">
         <v>29</v>
@@ -41418,10 +41421,10 @@
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="4" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B571" s="4" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C571" s="4" t="s">
         <v>29</v>
@@ -41485,10 +41488,10 @@
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="4" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B572" s="4" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C572" s="4" t="s">
         <v>29</v>
@@ -41497,7 +41500,7 @@
         <v>30</v>
       </c>
       <c r="E572" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F572" s="5" t="n">
         <v>43.36</v>
@@ -41552,10 +41555,10 @@
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="4" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B573" s="4" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C573" s="4" t="s">
         <v>29</v>
@@ -41619,10 +41622,10 @@
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="4" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B574" s="4" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C574" s="4" t="s">
         <v>29</v>
@@ -41631,7 +41634,7 @@
         <v>30</v>
       </c>
       <c r="E574" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F574" s="5" t="n">
         <v>96.35</v>
@@ -41686,10 +41689,10 @@
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="4" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B575" s="4" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C575" s="4" t="s">
         <v>38</v>
@@ -41741,10 +41744,10 @@
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="4" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B576" s="4" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C576" s="4" t="s">
         <v>29</v>
@@ -41759,7 +41762,7 @@
         <v>930</v>
       </c>
       <c r="G576" s="4" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H576" s="6" t="n">
         <v>27900</v>
@@ -41808,10 +41811,10 @@
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="4" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B577" s="4" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C577" s="4" t="s">
         <v>29</v>
@@ -41870,15 +41873,15 @@
         <v>1</v>
       </c>
       <c r="U577" s="4" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="4" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B578" s="4" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C578" s="4" t="s">
         <v>29</v>
@@ -41887,7 +41890,7 @@
         <v>30</v>
       </c>
       <c r="E578" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F578" s="5" t="n">
         <v>129.4</v>
@@ -41942,10 +41945,10 @@
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="4" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B579" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C579" s="4" t="s">
         <v>38</v>
@@ -41997,10 +42000,10 @@
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="4" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B580" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C580" s="4" t="s">
         <v>60</v>
@@ -42052,10 +42055,10 @@
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="4" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B581" s="4" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C581" s="4" t="s">
         <v>29</v>
@@ -42064,7 +42067,7 @@
         <v>30</v>
       </c>
       <c r="E581" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F581" s="5" t="n">
         <v>0.83</v>
@@ -42117,10 +42120,10 @@
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="4" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B582" s="4" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C582" s="4" t="s">
         <v>29</v>
@@ -42184,10 +42187,10 @@
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="4" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B583" s="4" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C583" s="4" t="s">
         <v>29</v>
@@ -42251,10 +42254,10 @@
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="4" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B584" s="4" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C584" s="4" t="s">
         <v>29</v>
@@ -42263,7 +42266,7 @@
         <v>30</v>
       </c>
       <c r="E584" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F584" s="5" t="n">
         <v>3.65</v>
@@ -42318,10 +42321,10 @@
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="4" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B585" s="4" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C585" s="4" t="s">
         <v>29</v>
@@ -42385,10 +42388,10 @@
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="4" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B586" s="4" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C586" s="4" t="s">
         <v>29</v>
@@ -42452,10 +42455,10 @@
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="4" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B587" s="4" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C587" s="4" t="s">
         <v>29</v>
@@ -42464,7 +42467,7 @@
         <v>30</v>
       </c>
       <c r="E587" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F587" s="5" t="n">
         <v>5.78</v>
@@ -42519,10 +42522,10 @@
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A588" s="4" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B588" s="4" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C588" s="4" t="s">
         <v>29</v>
@@ -42586,10 +42589,10 @@
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="4" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B589" s="4" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C589" s="4" t="s">
         <v>60</v>
@@ -42638,15 +42641,15 @@
         <v>1</v>
       </c>
       <c r="U589" s="4" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="4" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B590" s="4" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C590" s="4" t="s">
         <v>29</v>
@@ -42708,10 +42711,10 @@
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="4" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B591" s="4" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="C591" s="4" t="s">
         <v>29</v>
@@ -42775,10 +42778,10 @@
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="4" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B592" s="4" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C592" s="4" t="s">
         <v>29</v>
@@ -42787,7 +42790,7 @@
         <v>30</v>
       </c>
       <c r="E592" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F592" s="5" t="n">
         <v>15.97</v>
@@ -42842,10 +42845,10 @@
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="4" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B593" s="4" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C593" s="4" t="s">
         <v>29</v>
@@ -42909,10 +42912,10 @@
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="4" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C594" s="4" t="s">
         <v>60</v>
@@ -42961,15 +42964,15 @@
         <v>1</v>
       </c>
       <c r="U594" s="4" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="4" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B595" s="4" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C595" s="4" t="s">
         <v>29</v>
@@ -42978,7 +42981,7 @@
         <v>30</v>
       </c>
       <c r="E595" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F595" s="5" t="n">
         <v>151.7</v>
@@ -43033,10 +43036,10 @@
     </row>
     <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="4" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B596" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C596" s="4" t="s">
         <v>29</v>
@@ -43100,7 +43103,7 @@
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="4" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
@@ -43110,7 +43113,7 @@
         <v>9.3</v>
       </c>
       <c r="G597" s="4" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H597" s="6" t="n">
         <v>390.6</v>
@@ -43147,10 +43150,10 @@
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="4" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B598" s="4" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C598" s="4" t="s">
         <v>29</v>
@@ -43214,10 +43217,10 @@
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="4" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B599" s="4" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C599" s="4" t="s">
         <v>29</v>
@@ -43226,7 +43229,7 @@
         <v>30</v>
       </c>
       <c r="E599" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F599" s="5" t="n">
         <v>0.43</v>
@@ -43281,10 +43284,10 @@
     </row>
     <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="4" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B600" s="4" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C600" s="4" t="s">
         <v>29</v>
@@ -43346,10 +43349,10 @@
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A601" s="4" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B601" s="4" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C601" s="4" t="s">
         <v>60</v>
@@ -43401,10 +43404,10 @@
     </row>
     <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="4" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B602" s="4" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C602" s="4" t="s">
         <v>60</v>
@@ -43454,10 +43457,10 @@
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="4" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B603" s="4" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C603" s="4" t="s">
         <v>60</v>
@@ -43506,15 +43509,15 @@
         <v>1</v>
       </c>
       <c r="U603" s="4" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A604" s="4" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B604" s="4" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C604" s="4" t="s">
         <v>29</v>
@@ -43541,7 +43544,7 @@
         <v>32</v>
       </c>
       <c r="K604" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L604" s="4" t="s">
         <v>34</v>
@@ -43552,7 +43555,7 @@
       </c>
       <c r="N604" s="4" t="str">
         <f aca="false">IF(I604="",IF(K604="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I604&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K604="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O604" s="9" t="n">
         <f aca="false">IF(Q604="","",F604*R604/Q604-1)</f>
@@ -43578,10 +43581,10 @@
     </row>
     <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A605" s="4" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B605" s="4" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C605" s="4" t="s">
         <v>29</v>
@@ -43608,7 +43611,7 @@
         <v>32</v>
       </c>
       <c r="K605" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L605" s="4" t="s">
         <v>57</v>
@@ -43619,7 +43622,7 @@
       </c>
       <c r="N605" s="4" t="str">
         <f aca="false">IF(I605="",IF(K605="NULL","FCF yok (NULL)","FCF kapsamı dışı"),IF(I605&lt;=0,"anlamsız (FCF ≤ 0)",IF(OR(K605="KOŞULLU"),"FCF KOŞULLU — yorum yapılmaz","")))</f>
-        <v>FCF KOŞULLU — yorum yapılmaz</v>
+        <v/>
       </c>
       <c r="O605" s="9" t="n">
         <f aca="false">IF(Q605="","",F605*R605/Q605-1)</f>
@@ -43645,10 +43648,10 @@
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A606" s="4" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B606" s="4" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C606" s="4" t="s">
         <v>29</v>
@@ -43712,10 +43715,10 @@
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="4" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B607" s="4" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C607" s="4" t="s">
         <v>38</v>
@@ -43767,10 +43770,10 @@
     </row>
     <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="4" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B608" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C608" s="4" t="s">
         <v>29</v>
@@ -43834,10 +43837,10 @@
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A609" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B609" s="4" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C609" s="4" t="s">
         <v>29</v>
@@ -43901,10 +43904,10 @@
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A610" s="4" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B610" s="4" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C610" s="4" t="s">
         <v>29</v>
@@ -43968,10 +43971,10 @@
     </row>
     <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="4" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B611" s="4" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C611" s="4" t="s">
         <v>29</v>
@@ -44031,10 +44034,10 @@
     </row>
     <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A612" s="4" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B612" s="4" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="C612" s="4" t="s">
         <v>38</v>
@@ -44086,10 +44089,10 @@
     </row>
     <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A613" s="4" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B613" s="4" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C613" s="4" t="s">
         <v>38</v>
@@ -44138,15 +44141,15 @@
         <v>1</v>
       </c>
       <c r="U613" s="4" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A614" s="4" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B614" s="4" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="C614" s="4" t="s">
         <v>29</v>
@@ -44210,10 +44213,10 @@
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="4" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B615" s="4" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="C615" s="4" t="s">
         <v>38</v>
@@ -44265,10 +44268,10 @@
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="4" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B616" s="4" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C616" s="4" t="s">
         <v>29</v>
@@ -44277,7 +44280,7 @@
         <v>30</v>
       </c>
       <c r="E616" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F616" s="5" t="n">
         <v>27.7</v>
@@ -44329,15 +44332,15 @@
         <v>1</v>
       </c>
       <c r="U616" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="4" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B617" s="4" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C617" s="4" t="s">
         <v>29</v>
@@ -44346,7 +44349,7 @@
         <v>30</v>
       </c>
       <c r="E617" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F617" s="5" t="n">
         <v>9.2</v>
@@ -44401,10 +44404,10 @@
     </row>
     <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="4" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B618" s="4" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C618" s="4" t="s">
         <v>29</v>
@@ -44413,7 +44416,7 @@
         <v>30</v>
       </c>
       <c r="E618" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F618" s="5" t="n">
         <v>26.68</v>
@@ -44468,10 +44471,10 @@
     </row>
     <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="4" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B619" s="4" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C619" s="4" t="s">
         <v>29</v>
@@ -44498,7 +44501,7 @@
         <v>32</v>
       </c>
       <c r="K619" s="4" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="L619" s="4" t="s">
         <v>34</v>
@@ -44535,10 +44538,10 @@
     </row>
     <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="4" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B620" s="4" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C620" s="4" t="s">
         <v>29</v>
@@ -44602,10 +44605,10 @@
     </row>
     <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A621" s="4" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B621" s="4" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C621" s="4" t="s">
         <v>29</v>
@@ -44666,15 +44669,15 @@
         <v>1</v>
       </c>
       <c r="U621" s="4" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="4" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B622" s="4" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C622" s="4" t="s">
         <v>29</v>
@@ -44738,10 +44741,10 @@
     </row>
     <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A623" s="4" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B623" s="4" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C623" s="4" t="s">
         <v>38</v>
@@ -44793,10 +44796,10 @@
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="4" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B624" s="4" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C624" s="4" t="s">
         <v>29</v>
@@ -44805,7 +44808,7 @@
         <v>30</v>
       </c>
       <c r="E624" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F624" s="5" t="n">
         <v>16.77</v>
@@ -44860,10 +44863,10 @@
     </row>
     <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A625" s="4" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B625" s="4" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C625" s="4" t="s">
         <v>60</v>
@@ -44915,10 +44918,10 @@
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A626" s="4" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B626" s="4" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="C626" s="4" t="s">
         <v>29</v>
@@ -44927,7 +44930,7 @@
         <v>30</v>
       </c>
       <c r="E626" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F626" s="5" t="n">
         <v>2.5</v>
@@ -44982,10 +44985,10 @@
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="4" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B627" s="4" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="C627" s="4" t="s">
         <v>29</v>
@@ -44994,7 +44997,7 @@
         <v>30</v>
       </c>
       <c r="E627" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F627" s="5" t="n">
         <v>35.9</v>
@@ -45049,10 +45052,10 @@
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="4" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B628" s="4" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="C628" s="4" t="s">
         <v>29</v>
@@ -45116,10 +45119,10 @@
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A629" s="4" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B629" s="4" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C629" s="4" t="s">
         <v>29</v>
@@ -45183,10 +45186,10 @@
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="4" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B630" s="4" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C630" s="4" t="s">
         <v>29</v>
@@ -45250,10 +45253,10 @@
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="4" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B631" s="4" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C631" s="4" t="s">
         <v>29</v>
@@ -45317,10 +45320,10 @@
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="4" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B632" s="4" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="C632" s="4" t="s">
         <v>38</v>
@@ -45370,10 +45373,10 @@
     </row>
     <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="4" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B633" s="4" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C633" s="4" t="s">
         <v>38</v>
@@ -45423,10 +45426,10 @@
     </row>
     <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A634" s="4" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B634" s="4" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C634" s="4" t="s">
         <v>29</v>
@@ -45490,10 +45493,10 @@
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="4" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B635" s="4" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="C635" s="4" t="s">
         <v>38</v>
@@ -45577,18 +45580,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45596,31 +45599,31 @@
         <v>14</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45628,7 +45631,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
   </sheetData>
